--- a/public/downloads/MamunHighT2019.xlsx
+++ b/public/downloads/MamunHighT2019.xlsx
@@ -29,17 +29,16 @@
     <sheet name="PET-OAM-XL" sheetId="20" r:id="rId20"/>
     <sheet name="SevenNet-MF-OMPA" sheetId="21" r:id="rId21"/>
     <sheet name="SevenNet-Omni" sheetId="22" r:id="rId22"/>
-    <sheet name="SevenNet-Omni_basic" sheetId="23" r:id="rId23"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="24" r:id="rId24"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="25" r:id="rId25"/>
-    <sheet name="UMA-s-1p2_oc20" sheetId="26" r:id="rId26"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="23" r:id="rId23"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="24" r:id="rId24"/>
+    <sheet name="UMA-s-1p2_oc20" sheetId="25" r:id="rId25"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="65">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -71,10 +70,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -150,9 +149,6 @@
   </si>
   <si>
     <t>SevenNet-Omni</t>
-  </si>
-  <si>
-    <t>SevenNet-Omni_basic</t>
   </si>
   <si>
     <t>UMA-m-1p1_oc20</t>
@@ -596,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.7109375" customWidth="1"/>
@@ -722,10 +718,10 @@
         <v>45130</v>
       </c>
       <c r="N3" s="5">
-        <v>60228.35167980194</v>
+        <v>60228351.67980194</v>
       </c>
       <c r="O3" s="4">
-        <v>0.008447107803894099</v>
+        <v>8.447107803894099</v>
       </c>
       <c r="P3" s="5">
         <v>7130056</v>
@@ -772,10 +768,10 @@
         <v>45130</v>
       </c>
       <c r="N4" s="5">
-        <v>299167.4986884594</v>
+        <v>299167498.6884594</v>
       </c>
       <c r="O4" s="4">
-        <v>0.03225683833422118</v>
+        <v>32.25683833422118</v>
       </c>
       <c r="P4" s="5">
         <v>9274545</v>
@@ -822,10 +818,10 @@
         <v>45130</v>
       </c>
       <c r="N5" s="5">
-        <v>253732.7615115643</v>
+        <v>253732761.5115643</v>
       </c>
       <c r="O5" s="4">
-        <v>0.03547603495854639</v>
+        <v>35.47603495854639</v>
       </c>
       <c r="P5" s="5">
         <v>7152230</v>
@@ -872,10 +868,10 @@
         <v>45130</v>
       </c>
       <c r="N6" s="5">
-        <v>719059.7328717709</v>
+        <v>719059732.8717709</v>
       </c>
       <c r="O6" s="4">
-        <v>0.1266571701417176</v>
+        <v>126.6571701417176</v>
       </c>
       <c r="P6" s="5">
         <v>5677213</v>
@@ -922,10 +918,10 @@
         <v>45130</v>
       </c>
       <c r="N7" s="5">
-        <v>564568.7889437675</v>
+        <v>564568788.9437675</v>
       </c>
       <c r="O7" s="4">
-        <v>0.08346539645353984</v>
+        <v>83.46539645353984</v>
       </c>
       <c r="P7" s="5">
         <v>6764106</v>
@@ -936,49 +932,49 @@
         <v>22</v>
       </c>
       <c r="B8" s="3">
-        <v>79.83034647550777</v>
+        <v>78.77021936627521</v>
       </c>
       <c r="C8" s="3">
-        <v>5.376344086021505</v>
+        <v>5.342344338577442</v>
       </c>
       <c r="D8" s="3">
-        <v>14.79330943847073</v>
+        <v>15.88743629514735</v>
       </c>
       <c r="E8" s="3">
-        <v>2.27479091995221</v>
+        <v>2.346554398404609</v>
       </c>
       <c r="F8" s="3">
-        <v>7.949820788530467</v>
+        <v>9.067139375138488</v>
       </c>
       <c r="G8" s="3">
-        <v>4.568697729988052</v>
+        <v>4.473742521604255</v>
       </c>
       <c r="H8" s="4">
-        <v>1.850635685589274</v>
+        <v>1.806917729574381</v>
       </c>
       <c r="I8" s="4">
-        <v>0.5078627583610356</v>
+        <v>0.5093673982496593</v>
       </c>
       <c r="J8" s="4">
-        <v>1.93867432226769</v>
+        <v>1.887335085962168</v>
       </c>
       <c r="K8" s="4">
-        <v>83.04783523923307</v>
+        <v>82.28331758140882</v>
       </c>
       <c r="L8" s="4">
-        <v>88.87171826513681</v>
+        <v>88.35964236550538</v>
       </c>
       <c r="M8" s="5">
-        <v>41850</v>
+        <v>45130</v>
       </c>
       <c r="N8" s="5">
-        <v>560208.2621715069</v>
+        <v>621329751.6198158</v>
       </c>
       <c r="O8" s="4">
-        <v>0.1179619255540058</v>
+        <v>118.0007478188219</v>
       </c>
       <c r="P8" s="5">
-        <v>4749060</v>
+        <v>5265473</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="25" customHeight="1">
@@ -1022,10 +1018,10 @@
         <v>45130</v>
       </c>
       <c r="N9" s="5">
-        <v>904910.0726923943</v>
+        <v>904910072.6923943</v>
       </c>
       <c r="O9" s="4">
-        <v>0.1351447727590948</v>
+        <v>135.1447727590948</v>
       </c>
       <c r="P9" s="5">
         <v>6695857</v>
@@ -1072,10 +1068,10 @@
         <v>45130</v>
       </c>
       <c r="N10" s="5">
-        <v>57568.76570892334</v>
+        <v>57568765.70892334</v>
       </c>
       <c r="O10" s="4">
-        <v>0.009527558305856131</v>
+        <v>9.527558305856131</v>
       </c>
       <c r="P10" s="5">
         <v>6042342</v>
@@ -1122,10 +1118,10 @@
         <v>45130</v>
       </c>
       <c r="N11" s="5">
-        <v>213838.1435055733</v>
+        <v>213838143.5055733</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04437701438002346</v>
+        <v>44.37701438002346</v>
       </c>
       <c r="P11" s="5">
         <v>4818669</v>
@@ -1172,10 +1168,10 @@
         <v>45130</v>
       </c>
       <c r="N12" s="5">
-        <v>264606.4773356915</v>
+        <v>264606477.3356915</v>
       </c>
       <c r="O12" s="4">
-        <v>0.04773793011087187</v>
+        <v>47.73793011087186</v>
       </c>
       <c r="P12" s="5">
         <v>5542898</v>
@@ -1222,10 +1218,10 @@
         <v>45130</v>
       </c>
       <c r="N13" s="5">
-        <v>210743.725738287</v>
+        <v>210743725.738287</v>
       </c>
       <c r="O13" s="4">
-        <v>0.03681129831127389</v>
+        <v>36.81129831127389</v>
       </c>
       <c r="P13" s="5">
         <v>5724974</v>
@@ -1272,10 +1268,10 @@
         <v>45130</v>
       </c>
       <c r="N14" s="5">
-        <v>686361.7560591698</v>
+        <v>686361756.0591698</v>
       </c>
       <c r="O14" s="4">
-        <v>0.1213852333743756</v>
+        <v>121.3852333743756</v>
       </c>
       <c r="P14" s="5">
         <v>5654409</v>
@@ -1322,10 +1318,10 @@
         <v>45130</v>
       </c>
       <c r="N15" s="5">
-        <v>345355.9894137383</v>
+        <v>345355989.4137383</v>
       </c>
       <c r="O15" s="4">
-        <v>0.03815847524026255</v>
+        <v>38.15847524026255</v>
       </c>
       <c r="P15" s="5">
         <v>9050571</v>
@@ -1372,10 +1368,10 @@
         <v>45130</v>
       </c>
       <c r="N16" s="5">
-        <v>54054.57987594604</v>
+        <v>54054579.87594604</v>
       </c>
       <c r="O16" s="4">
-        <v>0.007489337759766009</v>
+        <v>7.489337759766009</v>
       </c>
       <c r="P16" s="5">
         <v>7217538</v>
@@ -1422,10 +1418,10 @@
         <v>45130</v>
       </c>
       <c r="N17" s="5">
-        <v>66994.38772177696</v>
+        <v>66994387.72177696</v>
       </c>
       <c r="O17" s="4">
-        <v>0.007998070240851257</v>
+        <v>7.998070240851257</v>
       </c>
       <c r="P17" s="5">
         <v>8376319</v>
@@ -1472,10 +1468,10 @@
         <v>45130</v>
       </c>
       <c r="N18" s="5">
-        <v>72668.41213035583</v>
+        <v>72668412.13035583</v>
       </c>
       <c r="O18" s="4">
-        <v>0.01045621010295367</v>
+        <v>10.45621010295367</v>
       </c>
       <c r="P18" s="5">
         <v>6949785</v>
@@ -1522,10 +1518,10 @@
         <v>45130</v>
       </c>
       <c r="N19" s="5">
-        <v>106680.2183094025</v>
+        <v>106680218.3094025</v>
       </c>
       <c r="O19" s="4">
-        <v>0.01747288347838119</v>
+        <v>17.4728834783812</v>
       </c>
       <c r="P19" s="5">
         <v>6105473</v>
@@ -1572,10 +1568,10 @@
         <v>45130</v>
       </c>
       <c r="N20" s="5">
-        <v>391556.1912102699</v>
+        <v>391556191.2102699</v>
       </c>
       <c r="O20" s="4">
-        <v>0.05686998137579605</v>
+        <v>56.86998137579605</v>
       </c>
       <c r="P20" s="5">
         <v>6885112</v>
@@ -1622,10 +1618,10 @@
         <v>45130</v>
       </c>
       <c r="N21" s="5">
-        <v>593762.7350678444</v>
+        <v>593762735.0678444</v>
       </c>
       <c r="O21" s="4">
-        <v>0.07432713138950442</v>
+        <v>74.32713138950442</v>
       </c>
       <c r="P21" s="5">
         <v>7988506</v>
@@ -1636,49 +1632,49 @@
         <v>36</v>
       </c>
       <c r="B22" s="3">
-        <v>79.69230769230769</v>
+        <v>81.6042543762464</v>
       </c>
       <c r="C22" s="3">
-        <v>8.307692307692308</v>
+        <v>6.388211832483935</v>
       </c>
       <c r="D22" s="3">
-        <v>12</v>
+        <v>12.00753379126967</v>
       </c>
       <c r="E22" s="3">
-        <v>1.846153846153846</v>
+        <v>1.914469310879681</v>
       </c>
       <c r="F22" s="3">
-        <v>8</v>
+        <v>7.476179924662087</v>
       </c>
       <c r="G22" s="3">
-        <v>2.153846153846154</v>
+        <v>2.616884555727897</v>
       </c>
       <c r="H22" s="4">
-        <v>0.6618829100742866</v>
+        <v>0.6899684919599562</v>
       </c>
       <c r="I22" s="4">
-        <v>0.1506194844002569</v>
+        <v>0.1910129935362078</v>
       </c>
       <c r="J22" s="4">
-        <v>0.7342298412684918</v>
+        <v>0.7279865628858957</v>
       </c>
       <c r="K22" s="4">
-        <v>81.718315018315</v>
+        <v>81.98544265922636</v>
       </c>
       <c r="L22" s="4">
-        <v>87.69509550851765</v>
+        <v>88.02211557860927</v>
       </c>
       <c r="M22" s="5">
-        <v>650</v>
+        <v>45130</v>
       </c>
       <c r="N22" s="5">
-        <v>3899.30046081543</v>
+        <v>249831930.1786423</v>
       </c>
       <c r="O22" s="4">
-        <v>0.04715279594673717</v>
+        <v>47.95831388345167</v>
       </c>
       <c r="P22" s="5">
-        <v>82695</v>
+        <v>5209356</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="25" customHeight="1">
@@ -1686,49 +1682,49 @@
         <v>37</v>
       </c>
       <c r="B23" s="3">
-        <v>81.57323288278307</v>
+        <v>84.81719477066252</v>
       </c>
       <c r="C23" s="3">
-        <v>6.363837801905606</v>
+        <v>4.230002215820962</v>
       </c>
       <c r="D23" s="3">
-        <v>12.06292931531132</v>
+        <v>10.95280301351651</v>
       </c>
       <c r="E23" s="3">
-        <v>1.947706625304676</v>
+        <v>1.644139153556393</v>
       </c>
       <c r="F23" s="3">
-        <v>7.493906492355418</v>
+        <v>8.949700864170175</v>
       </c>
       <c r="G23" s="3">
-        <v>2.62131619765123</v>
+        <v>0.3589629957899402</v>
       </c>
       <c r="H23" s="4">
-        <v>0.6900231099385666</v>
+        <v>0.3172306584688681</v>
       </c>
       <c r="I23" s="4">
-        <v>0.1910690842475573</v>
+        <v>0.2205260530262842</v>
       </c>
       <c r="J23" s="4">
-        <v>0.727986918902471</v>
+        <v>0.2494851766100147</v>
       </c>
       <c r="K23" s="4">
-        <v>81.97110991527123</v>
+        <v>84.21236835084136</v>
       </c>
       <c r="L23" s="4">
-        <v>88.0118055669155</v>
+        <v>89.53055974016884</v>
       </c>
       <c r="M23" s="5">
         <v>45130</v>
       </c>
       <c r="N23" s="5">
-        <v>337758.0337195396</v>
+        <v>885124575.6862164</v>
       </c>
       <c r="O23" s="4">
-        <v>0.06469534603372652</v>
+        <v>209.7100262316755</v>
       </c>
       <c r="P23" s="5">
-        <v>5220747</v>
+        <v>4220707</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="25" customHeight="1">
@@ -1736,49 +1732,49 @@
         <v>38</v>
       </c>
       <c r="B24" s="3">
-        <v>84.81719477066252</v>
+        <v>84.32528251717261</v>
       </c>
       <c r="C24" s="3">
-        <v>4.230002215820962</v>
+        <v>4.504764015067583</v>
       </c>
       <c r="D24" s="3">
-        <v>10.95280301351651</v>
+        <v>11.16995346775981</v>
       </c>
       <c r="E24" s="3">
-        <v>1.644139153556393</v>
+        <v>1.945490804343009</v>
       </c>
       <c r="F24" s="3">
-        <v>8.949700864170175</v>
+        <v>9.131398183026812</v>
       </c>
       <c r="G24" s="3">
-        <v>0.3589629957899402</v>
+        <v>0.09306448038998449</v>
       </c>
       <c r="H24" s="4">
-        <v>0.3172306584688681</v>
+        <v>0.2951501815163014</v>
       </c>
       <c r="I24" s="4">
-        <v>0.2205260530262842</v>
+        <v>0.2002371139157273</v>
       </c>
       <c r="J24" s="4">
-        <v>0.2494851766100147</v>
+        <v>0.2256951253715775</v>
       </c>
       <c r="K24" s="4">
-        <v>84.21236835084136</v>
+        <v>83.19692166696072</v>
       </c>
       <c r="L24" s="4">
-        <v>89.53055974016884</v>
+        <v>88.61214408685618</v>
       </c>
       <c r="M24" s="5">
         <v>45130</v>
       </c>
       <c r="N24" s="5">
-        <v>885124.5756862164</v>
+        <v>441328099.8268127</v>
       </c>
       <c r="O24" s="4">
-        <v>0.2097100262316755</v>
+        <v>99.38183610873449</v>
       </c>
       <c r="P24" s="5">
-        <v>4220707</v>
+        <v>4440732</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="25" customHeight="1">
@@ -1786,98 +1782,48 @@
         <v>39</v>
       </c>
       <c r="B25" s="3">
-        <v>84.32528251717261</v>
+        <v>83.90649235541768</v>
       </c>
       <c r="C25" s="3">
-        <v>4.504764015067583</v>
+        <v>4.515843119875914</v>
       </c>
       <c r="D25" s="3">
-        <v>11.16995346775981</v>
+        <v>11.5776645247064</v>
       </c>
       <c r="E25" s="3">
-        <v>1.945490804343009</v>
+        <v>1.781520053179703</v>
       </c>
       <c r="F25" s="3">
-        <v>9.131398183026812</v>
+        <v>9.703079991136716</v>
       </c>
       <c r="G25" s="3">
         <v>0.09306448038998449</v>
       </c>
       <c r="H25" s="4">
-        <v>0.2951501815163014</v>
+        <v>0.303810238336374</v>
       </c>
       <c r="I25" s="4">
-        <v>0.2002371139157273</v>
+        <v>0.2060942391224967</v>
       </c>
       <c r="J25" s="4">
-        <v>0.2256951253715775</v>
+        <v>0.2326742503520012</v>
       </c>
       <c r="K25" s="4">
-        <v>83.19692166696072</v>
+        <v>83.37541735063185</v>
       </c>
       <c r="L25" s="4">
-        <v>88.61214408685618</v>
+        <v>88.77416124732385</v>
       </c>
       <c r="M25" s="5">
         <v>45130</v>
       </c>
       <c r="N25" s="5">
-        <v>441328.0998268127</v>
+        <v>431954365.7140732</v>
       </c>
       <c r="O25" s="4">
-        <v>0.09938183610873449</v>
+        <v>95.07910684742554</v>
       </c>
       <c r="P25" s="5">
-        <v>4440732</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="25" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="3">
-        <v>83.90649235541768</v>
-      </c>
-      <c r="C26" s="3">
-        <v>4.515843119875914</v>
-      </c>
-      <c r="D26" s="3">
-        <v>11.5776645247064</v>
-      </c>
-      <c r="E26" s="3">
-        <v>1.781520053179703</v>
-      </c>
-      <c r="F26" s="3">
-        <v>9.703079991136716</v>
-      </c>
-      <c r="G26" s="3">
-        <v>0.09306448038998449</v>
-      </c>
-      <c r="H26" s="4">
-        <v>0.303810238336374</v>
-      </c>
-      <c r="I26" s="4">
-        <v>0.2060942391224967</v>
-      </c>
-      <c r="J26" s="4">
-        <v>0.2326742503520012</v>
-      </c>
-      <c r="K26" s="4">
-        <v>83.37541735063185</v>
-      </c>
-      <c r="L26" s="4">
-        <v>88.77416124732385</v>
-      </c>
-      <c r="M26" s="5">
-        <v>45130</v>
-      </c>
-      <c r="N26" s="5">
-        <v>431954.3657140732</v>
-      </c>
-      <c r="O26" s="4">
-        <v>0.09507910684742553</v>
-      </c>
-      <c r="P26" s="5">
         <v>4543105</v>
       </c>
     </row>
@@ -1918,7 +1864,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -1939,13 +1885,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -1976,7 +1922,7 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.2543609925893247</v>
@@ -2017,7 +1963,7 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.408214485057632</v>
@@ -2058,7 +2004,7 @@
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>2.690728044107069</v>
@@ -2099,7 +2045,7 @@
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.3120819202741996</v>
@@ -2140,7 +2086,7 @@
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>0.4864272626598378</v>
@@ -2181,7 +2127,7 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.3618213018766708</v>
@@ -2222,7 +2168,7 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
         <v>0.6297638264938237</v>
@@ -2263,7 +2209,7 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
         <v>0.1288677939436727</v>
@@ -2304,7 +2250,7 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
         <v>0.6752836286463526</v>
@@ -2345,7 +2291,7 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
         <v>0.7375189414479927</v>
@@ -2386,7 +2332,7 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
         <v>0.6394419688011382</v>
@@ -2427,7 +2373,7 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>0.356853316967273</v>
@@ -2500,7 +2446,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -2521,13 +2467,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -2558,7 +2504,7 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.2150029311977388</v>
@@ -2599,7 +2545,7 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.3703042144479732</v>
@@ -2640,7 +2586,7 @@
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>0.6079711221649293</v>
@@ -2681,7 +2627,7 @@
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.3679569401017643</v>
@@ -2722,7 +2668,7 @@
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>0.3446241704243772</v>
@@ -2763,7 +2709,7 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.3156623554858318</v>
@@ -2804,7 +2750,7 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
         <v>0.3660926941654216</v>
@@ -2845,7 +2791,7 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
         <v>0.1435702268506802</v>
@@ -2886,7 +2832,7 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
         <v>0.3363873279188916</v>
@@ -2927,7 +2873,7 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
         <v>0.2652723260826504</v>
@@ -2968,7 +2914,7 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
         <v>0.1553804570729722</v>
@@ -3009,7 +2955,7 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>0.2512364179038574</v>
@@ -3082,7 +3028,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -3103,13 +3049,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -3140,7 +3086,7 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.2201193653290429</v>
@@ -3181,7 +3127,7 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.3270538405791061</v>
@@ -3222,7 +3168,7 @@
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>2.543888462614536</v>
@@ -3263,7 +3209,7 @@
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.2586044300886566</v>
@@ -3304,7 +3250,7 @@
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>0.3021607420311009</v>
@@ -3345,7 +3291,7 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.2901936344956321</v>
@@ -3386,7 +3332,7 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
         <v>0.4558675211410887</v>
@@ -3427,7 +3373,7 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
         <v>0.1132881083762008</v>
@@ -3468,7 +3414,7 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
         <v>0.2292068502737136</v>
@@ -3509,7 +3455,7 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
         <v>0.2328428030504347</v>
@@ -3550,7 +3496,7 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
         <v>0.1568272079532697</v>
@@ -3591,7 +3537,7 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>0.2485007458454349</v>
@@ -3664,7 +3610,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -3685,13 +3631,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -3722,7 +3668,7 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.3217171267417804</v>
@@ -3763,7 +3709,7 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.5012141374148795</v>
@@ -3804,7 +3750,7 @@
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>1.976273670819163</v>
@@ -3845,7 +3791,7 @@
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.3050940349184276</v>
@@ -3886,7 +3832,7 @@
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>0.5097683849482726</v>
@@ -3927,7 +3873,7 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.5141074036915714</v>
@@ -3968,7 +3914,7 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
         <v>0.7578022871165134</v>
@@ -4009,7 +3955,7 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
         <v>0.2912234879452174</v>
@@ -4050,7 +3996,7 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
         <v>0.8539335485913655</v>
@@ -4091,7 +4037,7 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
         <v>0.9562788116303899</v>
@@ -4132,7 +4078,7 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
         <v>0.7521872026910883</v>
@@ -4173,7 +4119,7 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>15.13277795394877</v>
@@ -4246,7 +4192,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -4267,13 +4213,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -4304,7 +4250,7 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.2479748399126805</v>
@@ -4345,7 +4291,7 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.4969664653200008</v>
@@ -4386,7 +4332,7 @@
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>0.4164899123525089</v>
@@ -4427,7 +4373,7 @@
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.3261880986601637</v>
@@ -4468,7 +4414,7 @@
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>0.4889672520474617</v>
@@ -4509,7 +4455,7 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.323843699334817</v>
@@ -4550,7 +4496,7 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
         <v>0.4847792115446831</v>
@@ -4591,7 +4537,7 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
         <v>0.119209595847965</v>
@@ -4632,7 +4578,7 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
         <v>0.3453566373693228</v>
@@ -4673,7 +4619,7 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
         <v>0.2627031870345533</v>
@@ -4714,7 +4660,7 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
         <v>0.1732499115540963</v>
@@ -4755,7 +4701,7 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>0.2656095176619323</v>
@@ -4828,7 +4774,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -4849,13 +4795,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -4886,7 +4832,7 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.5047137981379931</v>
@@ -4927,7 +4873,7 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.5199239654346745</v>
@@ -4968,7 +4914,7 @@
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>6.185776809531876</v>
@@ -5009,7 +4955,7 @@
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.377648902095942</v>
@@ -5050,7 +4996,7 @@
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>0.4894554196811319</v>
@@ -5091,7 +5037,7 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.4228677256356394</v>
@@ -5132,7 +5078,7 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
         <v>0.7265098766512994</v>
@@ -5173,7 +5119,7 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
         <v>0.5163760718758073</v>
@@ -5214,7 +5160,7 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
         <v>0.3470810412871119</v>
@@ -5255,7 +5201,7 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
         <v>0.535454034532176</v>
@@ -5296,7 +5242,7 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
         <v>0.417261100121559</v>
@@ -5337,7 +5283,7 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>0.5870845968862931</v>
@@ -5410,7 +5356,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -5431,13 +5377,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -5468,7 +5414,7 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.3110208353815564</v>
@@ -5509,7 +5455,7 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.3757231524436251</v>
@@ -5550,7 +5496,7 @@
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>6.929194594495745</v>
@@ -5591,7 +5537,7 @@
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.3252451498721427</v>
@@ -5632,7 +5578,7 @@
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>0.4241780054622526</v>
@@ -5673,7 +5619,7 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.3008722868945552</v>
@@ -5714,7 +5660,7 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
         <v>0.7015601744522553</v>
@@ -5755,7 +5701,7 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
         <v>1.623944621409722</v>
@@ -5796,7 +5742,7 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
         <v>0.2531973788779494</v>
@@ -5837,7 +5783,7 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
         <v>0.2924860519583405</v>
@@ -5878,7 +5824,7 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
         <v>0.2953266511411577</v>
@@ -5919,7 +5865,7 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>1.450951454298008</v>
@@ -5992,7 +5938,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -6013,13 +5959,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -6050,7 +5996,7 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.3277160622877415</v>
@@ -6091,7 +6037,7 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.3202326401782247</v>
@@ -6132,7 +6078,7 @@
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>5.935768001705558</v>
@@ -6173,7 +6119,7 @@
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.4080334619178823</v>
@@ -6214,7 +6160,7 @@
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>0.5883472469764049</v>
@@ -6255,7 +6201,7 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.344099859841999</v>
@@ -6296,7 +6242,7 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
         <v>0.6012748277334344</v>
@@ -6337,7 +6283,7 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
         <v>0.8245219971806279</v>
@@ -6378,7 +6324,7 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
         <v>0.3322598119365677</v>
@@ -6419,7 +6365,7 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
         <v>0.2419289819701935</v>
@@ -6460,7 +6406,7 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
         <v>0.1606890924745972</v>
@@ -6501,7 +6447,7 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>0.6914801508117381</v>
@@ -6574,7 +6520,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -6595,13 +6541,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -6632,7 +6578,7 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.4348795469072685</v>
@@ -6673,7 +6619,7 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.7988958583671345</v>
@@ -6714,7 +6660,7 @@
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>2.123459912598063</v>
@@ -6755,7 +6701,7 @@
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.4471184609624402</v>
@@ -6796,7 +6742,7 @@
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>0.521909263651007</v>
@@ -6837,7 +6783,7 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.808888949023653</v>
@@ -6878,7 +6824,7 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
         <v>1.183688262591509</v>
@@ -6919,7 +6865,7 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
         <v>0.1987781327174244</v>
@@ -6960,7 +6906,7 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
         <v>0.7991762091609673</v>
@@ -7001,7 +6947,7 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
         <v>1.045874637832018</v>
@@ -7042,7 +6988,7 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
         <v>0.9525642068277907</v>
@@ -7083,7 +7029,7 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>0.5603389958720534</v>
@@ -7156,7 +7102,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -7177,13 +7123,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -7214,7 +7160,7 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.2639032629564261</v>
@@ -7255,7 +7201,7 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.4225974083342193</v>
@@ -7296,7 +7242,7 @@
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>4.076461454234895</v>
@@ -7337,7 +7283,7 @@
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.31554948173113</v>
@@ -7378,7 +7324,7 @@
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>0.3677979488408422</v>
@@ -7419,7 +7365,7 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.3813957713532453</v>
@@ -7460,7 +7406,7 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
         <v>0.7915243484441417</v>
@@ -7501,7 +7447,7 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
         <v>0.674847693880942</v>
@@ -7542,7 +7488,7 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
         <v>0.4061681588204284</v>
@@ -7583,7 +7529,7 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
         <v>0.4382666884439956</v>
@@ -7624,7 +7570,7 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
         <v>0.3167142397666264</v>
@@ -7665,7 +7611,7 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>0.4962845007829031</v>
@@ -7723,7 +7669,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -7742,24 +7688,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -7782,25 +7728,25 @@
         <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="25" customHeight="1">
@@ -7835,16 +7781,16 @@
         <v>15</v>
       </c>
       <c r="K3" s="5">
-        <v>1327</v>
+        <v>433</v>
       </c>
       <c r="L3" s="5">
-        <v>4010</v>
+        <v>3197</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
       <c r="N3" s="5">
-        <v>226</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="25" customHeight="1">
@@ -7879,16 +7825,16 @@
         <v>23</v>
       </c>
       <c r="K4" s="5">
-        <v>1929</v>
+        <v>575</v>
       </c>
       <c r="L4" s="5">
-        <v>4642</v>
+        <v>3313</v>
       </c>
       <c r="M4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="5">
-        <v>356</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -7923,16 +7869,16 @@
         <v>193</v>
       </c>
       <c r="K5" s="5">
-        <v>599</v>
+        <v>153</v>
       </c>
       <c r="L5" s="5">
-        <v>5512</v>
+        <v>4699</v>
       </c>
       <c r="M5" s="5">
-        <v>198</v>
+        <v>88</v>
       </c>
       <c r="N5" s="5">
-        <v>2268</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="25" customHeight="1">
@@ -7967,16 +7913,16 @@
         <v>55</v>
       </c>
       <c r="K6" s="5">
-        <v>623</v>
+        <v>246</v>
       </c>
       <c r="L6" s="5">
-        <v>3753</v>
+        <v>3236</v>
       </c>
       <c r="M6" s="5">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="N6" s="5">
-        <v>632</v>
+        <v>562</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="25" customHeight="1">
@@ -8011,16 +7957,16 @@
         <v>51</v>
       </c>
       <c r="K7" s="5">
-        <v>703</v>
+        <v>273</v>
       </c>
       <c r="L7" s="5">
-        <v>5486</v>
+        <v>4834</v>
       </c>
       <c r="M7" s="5">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="N7" s="5">
-        <v>1359</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="25" customHeight="1">
@@ -8028,43 +7974,43 @@
         <v>22</v>
       </c>
       <c r="B8" s="5">
-        <v>33409</v>
+        <v>35549</v>
       </c>
       <c r="C8" s="5">
-        <v>2250</v>
+        <v>2411</v>
       </c>
       <c r="D8" s="5">
-        <v>6191</v>
+        <v>7170</v>
       </c>
       <c r="E8" s="5">
-        <v>952</v>
+        <v>1059</v>
       </c>
       <c r="F8" s="5">
-        <v>3327</v>
+        <v>4092</v>
       </c>
       <c r="G8" s="5">
-        <v>1912</v>
+        <v>2019</v>
       </c>
       <c r="H8" s="5">
-        <v>952</v>
+        <v>1059</v>
       </c>
       <c r="I8" s="5">
-        <v>871</v>
+        <v>951</v>
       </c>
       <c r="J8" s="5">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="K8" s="5">
-        <v>552</v>
+        <v>187</v>
       </c>
       <c r="L8" s="5">
-        <v>3344</v>
+        <v>3666</v>
       </c>
       <c r="M8" s="5">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="N8" s="5">
-        <v>925</v>
+        <v>985</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="25" customHeight="1">
@@ -8099,16 +8045,16 @@
         <v>117</v>
       </c>
       <c r="K9" s="5">
-        <v>1011</v>
+        <v>327</v>
       </c>
       <c r="L9" s="5">
-        <v>4807</v>
+        <v>4017</v>
       </c>
       <c r="M9" s="5">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="N9" s="5">
-        <v>1437</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25" customHeight="1">
@@ -8143,16 +8089,16 @@
         <v>0</v>
       </c>
       <c r="K10" s="5">
-        <v>740</v>
+        <v>360</v>
       </c>
       <c r="L10" s="5">
-        <v>3909</v>
+        <v>3458</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
       </c>
       <c r="N10" s="5">
-        <v>282</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="25" customHeight="1">
@@ -8187,16 +8133,16 @@
         <v>25</v>
       </c>
       <c r="K11" s="5">
-        <v>406</v>
+        <v>248</v>
       </c>
       <c r="L11" s="5">
-        <v>3938</v>
+        <v>3741</v>
       </c>
       <c r="M11" s="5">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="N11" s="5">
-        <v>835</v>
+        <v>789</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="25" customHeight="1">
@@ -8231,16 +8177,16 @@
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>567</v>
+        <v>301</v>
       </c>
       <c r="L12" s="5">
-        <v>3727</v>
+        <v>3374</v>
       </c>
       <c r="M12" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N12" s="5">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25" customHeight="1">
@@ -8275,16 +8221,16 @@
         <v>25</v>
       </c>
       <c r="K13" s="5">
-        <v>581</v>
+        <v>346</v>
       </c>
       <c r="L13" s="5">
-        <v>3902</v>
+        <v>3643</v>
       </c>
       <c r="M13" s="5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N13" s="5">
-        <v>532</v>
+        <v>489</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="25" customHeight="1">
@@ -8319,16 +8265,16 @@
         <v>97</v>
       </c>
       <c r="K14" s="5">
-        <v>483</v>
+        <v>187</v>
       </c>
       <c r="L14" s="5">
-        <v>5696</v>
+        <v>5315</v>
       </c>
       <c r="M14" s="5">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="N14" s="5">
-        <v>3065</v>
+        <v>2852</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="25" customHeight="1">
@@ -8363,16 +8309,16 @@
         <v>3</v>
       </c>
       <c r="K15" s="5">
-        <v>1750</v>
+        <v>662</v>
       </c>
       <c r="L15" s="5">
-        <v>4263</v>
+        <v>3179</v>
       </c>
       <c r="M15" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N15" s="5">
-        <v>349</v>
+        <v>327</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="25" customHeight="1">
@@ -8407,16 +8353,16 @@
         <v>14</v>
       </c>
       <c r="K16" s="5">
-        <v>1358</v>
+        <v>491</v>
       </c>
       <c r="L16" s="5">
-        <v>3470</v>
+        <v>2799</v>
       </c>
       <c r="M16" s="5">
         <v>0</v>
       </c>
       <c r="N16" s="5">
-        <v>244</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -8451,16 +8397,16 @@
         <v>40</v>
       </c>
       <c r="K17" s="5">
-        <v>1784</v>
+        <v>650</v>
       </c>
       <c r="L17" s="5">
-        <v>3457</v>
+        <v>2615</v>
       </c>
       <c r="M17" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="5">
-        <v>381</v>
+        <v>329</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="25" customHeight="1">
@@ -8495,16 +8441,16 @@
         <v>121</v>
       </c>
       <c r="K18" s="5">
-        <v>784</v>
+        <v>320</v>
       </c>
       <c r="L18" s="5">
-        <v>5430</v>
+        <v>4887</v>
       </c>
       <c r="M18" s="5">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="N18" s="5">
-        <v>1376</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="25" customHeight="1">
@@ -8539,16 +8485,16 @@
         <v>120</v>
       </c>
       <c r="K19" s="5">
-        <v>864</v>
+        <v>245</v>
       </c>
       <c r="L19" s="5">
-        <v>3367</v>
+        <v>2699</v>
       </c>
       <c r="M19" s="5">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="N19" s="5">
-        <v>602</v>
+        <v>516</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="25" customHeight="1">
@@ -8583,16 +8529,16 @@
         <v>70</v>
       </c>
       <c r="K20" s="5">
-        <v>1023</v>
+        <v>359</v>
       </c>
       <c r="L20" s="5">
-        <v>4069</v>
+        <v>3248</v>
       </c>
       <c r="M20" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N20" s="5">
-        <v>1070</v>
+        <v>935</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="25" customHeight="1">
@@ -8627,16 +8573,16 @@
         <v>0</v>
       </c>
       <c r="K21" s="5">
-        <v>1529</v>
+        <v>515</v>
       </c>
       <c r="L21" s="5">
-        <v>4134</v>
+        <v>3166</v>
       </c>
       <c r="M21" s="5">
         <v>0</v>
       </c>
       <c r="N21" s="5">
-        <v>262</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="25" customHeight="1">
@@ -8644,43 +8590,43 @@
         <v>36</v>
       </c>
       <c r="B22" s="5">
-        <v>518</v>
+        <v>36828</v>
       </c>
       <c r="C22" s="5">
-        <v>54</v>
+        <v>2883</v>
       </c>
       <c r="D22" s="5">
-        <v>78</v>
+        <v>5419</v>
       </c>
       <c r="E22" s="5">
-        <v>12</v>
+        <v>864</v>
       </c>
       <c r="F22" s="5">
-        <v>52</v>
+        <v>3374</v>
       </c>
       <c r="G22" s="5">
-        <v>14</v>
+        <v>1181</v>
       </c>
       <c r="H22" s="5">
-        <v>12</v>
+        <v>864</v>
       </c>
       <c r="I22" s="5">
-        <v>12</v>
+        <v>843</v>
       </c>
       <c r="J22" s="5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K22" s="5">
-        <v>12</v>
+        <v>239</v>
       </c>
       <c r="L22" s="5">
-        <v>47</v>
+        <v>3018</v>
       </c>
       <c r="M22" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N22" s="5">
-        <v>15</v>
+        <v>368</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="25" customHeight="1">
@@ -8688,43 +8634,43 @@
         <v>37</v>
       </c>
       <c r="B23" s="5">
-        <v>36814</v>
+        <v>38278</v>
       </c>
       <c r="C23" s="5">
-        <v>2872</v>
+        <v>1909</v>
       </c>
       <c r="D23" s="5">
-        <v>5444</v>
+        <v>4943</v>
       </c>
       <c r="E23" s="5">
-        <v>879</v>
+        <v>742</v>
       </c>
       <c r="F23" s="5">
-        <v>3382</v>
+        <v>4039</v>
       </c>
       <c r="G23" s="5">
-        <v>1183</v>
+        <v>162</v>
       </c>
       <c r="H23" s="5">
-        <v>879</v>
+        <v>742</v>
       </c>
       <c r="I23" s="5">
-        <v>862</v>
+        <v>621</v>
       </c>
       <c r="J23" s="5">
-        <v>10</v>
+        <v>128</v>
       </c>
       <c r="K23" s="5">
-        <v>640</v>
+        <v>86</v>
       </c>
       <c r="L23" s="5">
-        <v>3487</v>
+        <v>3756</v>
       </c>
       <c r="M23" s="5">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="N23" s="5">
-        <v>387</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="25" customHeight="1">
@@ -8732,43 +8678,43 @@
         <v>38</v>
       </c>
       <c r="B24" s="5">
-        <v>38278</v>
+        <v>38056</v>
       </c>
       <c r="C24" s="5">
-        <v>1909</v>
+        <v>2033</v>
       </c>
       <c r="D24" s="5">
-        <v>4943</v>
+        <v>5041</v>
       </c>
       <c r="E24" s="5">
-        <v>742</v>
+        <v>878</v>
       </c>
       <c r="F24" s="5">
-        <v>4039</v>
+        <v>4121</v>
       </c>
       <c r="G24" s="5">
-        <v>162</v>
+        <v>42</v>
       </c>
       <c r="H24" s="5">
-        <v>742</v>
+        <v>877</v>
       </c>
       <c r="I24" s="5">
-        <v>621</v>
+        <v>695</v>
       </c>
       <c r="J24" s="5">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="K24" s="5">
-        <v>341</v>
+        <v>87</v>
       </c>
       <c r="L24" s="5">
-        <v>4138</v>
+        <v>3855</v>
       </c>
       <c r="M24" s="5">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="N24" s="5">
-        <v>1279</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="25" customHeight="1">
@@ -8776,87 +8722,43 @@
         <v>39</v>
       </c>
       <c r="B25" s="5">
-        <v>38056</v>
+        <v>37867</v>
       </c>
       <c r="C25" s="5">
-        <v>2033</v>
+        <v>2038</v>
       </c>
       <c r="D25" s="5">
-        <v>5041</v>
+        <v>5225</v>
       </c>
       <c r="E25" s="5">
-        <v>878</v>
+        <v>804</v>
       </c>
       <c r="F25" s="5">
-        <v>4121</v>
+        <v>4379</v>
       </c>
       <c r="G25" s="5">
         <v>42</v>
       </c>
       <c r="H25" s="5">
-        <v>877</v>
+        <v>804</v>
       </c>
       <c r="I25" s="5">
-        <v>695</v>
+        <v>673</v>
       </c>
       <c r="J25" s="5">
-        <v>192</v>
+        <v>129</v>
       </c>
       <c r="K25" s="5">
-        <v>360</v>
+        <v>107</v>
       </c>
       <c r="L25" s="5">
-        <v>4388</v>
+        <v>4104</v>
       </c>
       <c r="M25" s="5">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="N25" s="5">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="25" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="5">
-        <v>37867</v>
-      </c>
-      <c r="C26" s="5">
-        <v>2038</v>
-      </c>
-      <c r="D26" s="5">
-        <v>5225</v>
-      </c>
-      <c r="E26" s="5">
-        <v>804</v>
-      </c>
-      <c r="F26" s="5">
-        <v>4379</v>
-      </c>
-      <c r="G26" s="5">
-        <v>42</v>
-      </c>
-      <c r="H26" s="5">
-        <v>804</v>
-      </c>
-      <c r="I26" s="5">
-        <v>673</v>
-      </c>
-      <c r="J26" s="5">
-        <v>129</v>
-      </c>
-      <c r="K26" s="5">
-        <v>369</v>
-      </c>
-      <c r="L26" s="5">
-        <v>4539</v>
-      </c>
-      <c r="M26" s="5">
-        <v>73</v>
-      </c>
-      <c r="N26" s="5">
-        <v>1246</v>
+        <v>1051</v>
       </c>
     </row>
   </sheetData>
@@ -8889,7 +8791,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -8910,13 +8812,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -8947,7 +8849,7 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.6538837405196216</v>
@@ -8988,7 +8890,7 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>1.216125320467224</v>
@@ -9029,7 +8931,7 @@
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>7.054566200632533</v>
@@ -9070,7 +8972,7 @@
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.4297750427552216</v>
@@ -9111,7 +9013,7 @@
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>1.049430247915275</v>
@@ -9152,7 +9054,7 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.475821615381528</v>
@@ -9193,7 +9095,7 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
         <v>1.759015955446807</v>
@@ -9234,7 +9136,7 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
         <v>2.239852263916253</v>
@@ -9275,7 +9177,7 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
         <v>0.6055668109775951</v>
@@ -9316,7 +9218,7 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
         <v>0.2220153773698241</v>
@@ -9357,7 +9259,7 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
         <v>0.4971709870490208</v>
@@ -9398,7 +9300,7 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>0.7258708253084393</v>
@@ -9471,7 +9373,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -9492,13 +9394,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -9529,7 +9431,7 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.438327806556961</v>
@@ -9570,7 +9472,7 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.3931011518370522</v>
@@ -9611,7 +9513,7 @@
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>4.153883992391868</v>
@@ -9652,7 +9554,7 @@
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.22455499821074</v>
@@ -9693,7 +9595,7 @@
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>0.3736854402641472</v>
@@ -9734,7 +9636,7 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.40641626441913</v>
@@ -9775,7 +9677,7 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
         <v>0.7388211838053166</v>
@@ -9816,7 +9718,7 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
         <v>0.3710650911662046</v>
@@ -9857,7 +9759,7 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
         <v>0.2891133869480136</v>
@@ -9898,7 +9800,7 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
         <v>0.4485884136318289</v>
@@ -9939,7 +9841,7 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
         <v>0.5697008901464218</v>
@@ -9980,7 +9882,7 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>0.4836996759558918</v>
@@ -10053,7 +9955,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -10074,13 +9976,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -10111,245 +10013,245 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1692073444767985</v>
+        <v>0.2197444476472248</v>
       </c>
       <c r="C3" s="4">
-        <v>0.122876312200305</v>
+        <v>0.1699020463952488</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1174340692640113</v>
+        <v>0.166101648526105</v>
       </c>
       <c r="E3" s="4">
-        <v>82.21596101127058</v>
+        <v>84.37294569962613</v>
       </c>
       <c r="F3" s="4">
-        <v>89.24914020501562</v>
+        <v>90.46646973599584</v>
       </c>
       <c r="G3" s="5">
-        <v>134</v>
+        <v>8854</v>
       </c>
       <c r="H3" s="5">
-        <v>115</v>
+        <v>7859</v>
       </c>
       <c r="I3" s="5">
-        <v>5</v>
+        <v>420</v>
       </c>
       <c r="J3" s="5">
-        <v>14</v>
+        <v>575</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="L3" s="5">
-        <v>13</v>
+        <v>487</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3155175879819075</v>
+        <v>0.3467969574443166</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1549957098823236</v>
+        <v>0.2363182052913548</v>
       </c>
       <c r="D4" s="4">
-        <v>0.153154410489033</v>
+        <v>0.2260218231832498</v>
       </c>
       <c r="E4" s="4">
-        <v>84.94992441421</v>
+        <v>83.38568792140707</v>
       </c>
       <c r="F4" s="4">
-        <v>90.79107631120921</v>
+        <v>89.77848088923838</v>
       </c>
       <c r="G4" s="5">
-        <v>108</v>
+        <v>7457</v>
       </c>
       <c r="H4" s="5">
-        <v>97</v>
+        <v>6592</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>222</v>
       </c>
       <c r="J4" s="5">
+        <v>643</v>
+      </c>
+      <c r="K4" s="5">
+        <v>110</v>
+      </c>
+      <c r="L4" s="5">
+        <v>524</v>
+      </c>
+      <c r="M4" s="5">
         <v>9</v>
-      </c>
-      <c r="K4" s="5">
-        <v>2</v>
-      </c>
-      <c r="L4" s="5">
-        <v>7</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>3.133843155346561</v>
+        <v>2.848803673187659</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1892819136707242</v>
+        <v>0.2368046438588772</v>
       </c>
       <c r="D5" s="4">
-        <v>3.724555648120663</v>
+        <v>3.417043293129018</v>
       </c>
       <c r="E5" s="4">
-        <v>76.14821686250275</v>
+        <v>77.30888175598638</v>
       </c>
       <c r="F5" s="4">
-        <v>81.88348812509788</v>
+        <v>83.90069894955695</v>
       </c>
       <c r="G5" s="5">
-        <v>99</v>
+        <v>7369</v>
       </c>
       <c r="H5" s="5">
-        <v>49</v>
+        <v>4377</v>
       </c>
       <c r="I5" s="5">
-        <v>13</v>
+        <v>435</v>
       </c>
       <c r="J5" s="5">
-        <v>37</v>
+        <v>2557</v>
       </c>
       <c r="K5" s="5">
-        <v>6</v>
+        <v>349</v>
       </c>
       <c r="L5" s="5">
-        <v>17</v>
+        <v>1063</v>
       </c>
       <c r="M5" s="5">
-        <v>14</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
-        <v>0.2186308901601706</v>
+        <v>0.2339432345578204</v>
       </c>
       <c r="C6" s="4">
-        <v>0.1731496501543053</v>
+        <v>0.1926125700173235</v>
       </c>
       <c r="D6" s="4">
-        <v>0.1948916024715543</v>
+        <v>0.2162391549353226</v>
       </c>
       <c r="E6" s="4">
-        <v>87.89519197509551</v>
+        <v>83.93135712647066</v>
       </c>
       <c r="F6" s="4">
-        <v>92.82286808478442</v>
+        <v>90.0477989687307</v>
       </c>
       <c r="G6" s="5">
-        <v>118</v>
+        <v>5812</v>
       </c>
       <c r="H6" s="5">
-        <v>109</v>
+        <v>5157</v>
       </c>
       <c r="I6" s="5">
+        <v>230</v>
+      </c>
+      <c r="J6" s="5">
+        <v>425</v>
+      </c>
+      <c r="K6" s="5">
+        <v>69</v>
+      </c>
+      <c r="L6" s="5">
+        <v>353</v>
+      </c>
+      <c r="M6" s="5">
         <v>3</v>
-      </c>
-      <c r="J6" s="5">
-        <v>6</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>6</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
-        <v>0.2012042995141167</v>
+        <v>0.2806475646395986</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1683160667686693</v>
+        <v>0.1899593535238477</v>
       </c>
       <c r="D7" s="4">
-        <v>0.1957006040512776</v>
+        <v>0.2177244725473816</v>
       </c>
       <c r="E7" s="4">
-        <v>85.66074577979353</v>
+        <v>83.64573007430148</v>
       </c>
       <c r="F7" s="4">
-        <v>91.96557295550616</v>
+        <v>89.46924349608925</v>
       </c>
       <c r="G7" s="5">
-        <v>108</v>
+        <v>5291</v>
       </c>
       <c r="H7" s="5">
-        <v>98</v>
+        <v>4593</v>
       </c>
       <c r="I7" s="5">
-        <v>3</v>
+        <v>219</v>
       </c>
       <c r="J7" s="5">
-        <v>7</v>
+        <v>479</v>
       </c>
       <c r="K7" s="5">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L7" s="5">
-        <v>7</v>
+        <v>375</v>
       </c>
       <c r="M7" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
-        <v>0.3507263867173151</v>
+        <v>0.3174254802538551</v>
       </c>
       <c r="C8" s="4">
-        <v>0.09285206511128763</v>
+        <v>0.1219379539215307</v>
       </c>
       <c r="D8" s="4">
-        <v>0.08456036268570036</v>
+        <v>0.122852702088359</v>
       </c>
       <c r="E8" s="4">
-        <v>72.25056689342362</v>
+        <v>76.54904108536059</v>
       </c>
       <c r="F8" s="4">
-        <v>71.02199850857626</v>
+        <v>80.7916556073762</v>
       </c>
       <c r="G8" s="5">
-        <v>30</v>
+        <v>1770</v>
       </c>
       <c r="H8" s="5">
-        <v>13</v>
+        <v>1223</v>
       </c>
       <c r="I8" s="5">
-        <v>13</v>
+        <v>369</v>
       </c>
       <c r="J8" s="5">
-        <v>4</v>
+        <v>178</v>
       </c>
       <c r="K8" s="5">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="L8" s="5">
-        <v>1</v>
+        <v>111</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
@@ -10357,40 +10259,40 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
-        <v>0.227309713712566</v>
+        <v>0.4897510591668289</v>
       </c>
       <c r="C9" s="4">
-        <v>0.227309713712566</v>
+        <v>0.3450972668407669</v>
       </c>
       <c r="D9" s="4">
-        <v>0.2137750724466969</v>
+        <v>0.3260783029349208</v>
       </c>
       <c r="E9" s="4">
-        <v>70.32653061224489</v>
+        <v>83.46408268056891</v>
       </c>
       <c r="F9" s="4">
-        <v>87.08053691275168</v>
+        <v>89.5056402259537</v>
       </c>
       <c r="G9" s="5">
-        <v>5</v>
+        <v>1558</v>
       </c>
       <c r="H9" s="5">
-        <v>5</v>
+        <v>1358</v>
       </c>
       <c r="I9" s="5">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="J9" s="5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="K9" s="5">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L9" s="5">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
@@ -10398,40 +10300,40 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
-        <v>0.09457433763589052</v>
+        <v>0.1207316924283993</v>
       </c>
       <c r="C10" s="4">
-        <v>0.04891074240894492</v>
+        <v>0.07311761088873286</v>
       </c>
       <c r="D10" s="4">
-        <v>0.9279180391263606</v>
+        <v>0.407321552153517</v>
       </c>
       <c r="E10" s="4">
-        <v>65.62162796152921</v>
+        <v>72.46962279044617</v>
       </c>
       <c r="F10" s="4">
-        <v>70.50528427061523</v>
+        <v>77.63230314219965</v>
       </c>
       <c r="G10" s="5">
-        <v>29</v>
+        <v>1534</v>
       </c>
       <c r="H10" s="5">
-        <v>15</v>
+        <v>967</v>
       </c>
       <c r="I10" s="5">
-        <v>14</v>
+        <v>511</v>
       </c>
       <c r="J10" s="5">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="K10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="5">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
@@ -10439,40 +10341,40 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
-        <v>0.05668997651869745</v>
+        <v>0.2237036698119513</v>
       </c>
       <c r="C11" s="4">
-        <v>0.05195506978161006</v>
+        <v>0.1313783706111831</v>
       </c>
       <c r="D11" s="4">
-        <v>0.1046030510121057</v>
+        <v>0.1222838900979079</v>
       </c>
       <c r="E11" s="4">
-        <v>65.28911564625882</v>
+        <v>85.22929861599819</v>
       </c>
       <c r="F11" s="4">
-        <v>85.1789709172261</v>
+        <v>90.80399687868977</v>
       </c>
       <c r="G11" s="5">
-        <v>6</v>
+        <v>1508</v>
       </c>
       <c r="H11" s="5">
-        <v>5</v>
+        <v>1337</v>
       </c>
       <c r="I11" s="5">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="J11" s="5">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="K11" s="5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L11" s="5">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
@@ -10480,40 +10382,40 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
-        <v>0.0549348135024843</v>
+        <v>0.2435919524554757</v>
       </c>
       <c r="C12" s="4">
-        <v>0.0549348135024843</v>
+        <v>0.1238107464759692</v>
       </c>
       <c r="D12" s="4">
-        <v>0.04547468217517311</v>
+        <v>0.1062292919938244</v>
       </c>
       <c r="E12" s="4">
-        <v>76.76870748299319</v>
+        <v>82.22875432751985</v>
       </c>
       <c r="F12" s="4">
-        <v>88.73601789709174</v>
+        <v>87.8371892482425</v>
       </c>
       <c r="G12" s="5">
-        <v>3</v>
+        <v>1458</v>
       </c>
       <c r="H12" s="5">
-        <v>3</v>
+        <v>1206</v>
       </c>
       <c r="I12" s="5">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="J12" s="5">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="K12" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L12" s="5">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M12" s="5">
         <v>0</v>
@@ -10521,40 +10423,40 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
-        <v>0.06340776088481448</v>
+        <v>0.1567585514546952</v>
       </c>
       <c r="C13" s="4">
-        <v>0.06340776088481448</v>
+        <v>0.1087813409758709</v>
       </c>
       <c r="D13" s="4">
-        <v>0.04589639308696292</v>
+        <v>0.09217392064645709</v>
       </c>
       <c r="E13" s="4">
-        <v>73.80102040816327</v>
+        <v>83.23208722741433</v>
       </c>
       <c r="F13" s="4">
-        <v>87.18120805369128</v>
+        <v>89.21110449030256</v>
       </c>
       <c r="G13" s="5">
+        <v>1284</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1132</v>
+      </c>
+      <c r="I13" s="5">
+        <v>93</v>
+      </c>
+      <c r="J13" s="5">
+        <v>59</v>
+      </c>
+      <c r="K13" s="5">
         <v>4</v>
       </c>
-      <c r="H13" s="5">
-        <v>4</v>
-      </c>
-      <c r="I13" s="5">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5">
-        <v>0</v>
-      </c>
-      <c r="K13" s="5">
-        <v>0</v>
-      </c>
       <c r="L13" s="5">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M13" s="5">
         <v>0</v>
@@ -10562,43 +10464,43 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
-        <v>0.08927580265549295</v>
+        <v>0.2958051273710561</v>
       </c>
       <c r="C14" s="4">
-        <v>0.09138711871994473</v>
+        <v>0.09999066998915512</v>
       </c>
       <c r="D14" s="4">
-        <v>0.1076224024640927</v>
+        <v>0.2437428371948458</v>
       </c>
       <c r="E14" s="4">
-        <v>70.71428571428568</v>
+        <v>80.24905670770333</v>
       </c>
       <c r="F14" s="4">
-        <v>84.73713646532407</v>
+        <v>85.73353621534497</v>
       </c>
       <c r="G14" s="5">
-        <v>6</v>
+        <v>1235</v>
       </c>
       <c r="H14" s="5">
+        <v>1027</v>
+      </c>
+      <c r="I14" s="5">
+        <v>85</v>
+      </c>
+      <c r="J14" s="5">
+        <v>123</v>
+      </c>
+      <c r="K14" s="5">
+        <v>25</v>
+      </c>
+      <c r="L14" s="5">
+        <v>93</v>
+      </c>
+      <c r="M14" s="5">
         <v>5</v>
-      </c>
-      <c r="I14" s="5">
-        <v>1</v>
-      </c>
-      <c r="J14" s="5">
-        <v>0</v>
-      </c>
-      <c r="K14" s="5">
-        <v>0</v>
-      </c>
-      <c r="L14" s="5">
-        <v>0</v>
-      </c>
-      <c r="M14" s="5">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -10635,7 +10537,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -10656,13 +10558,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -10693,245 +10595,245 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2212160618450288</v>
+        <v>0.1498682668308317</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1700188473478469</v>
+        <v>0.07275628196009409</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1661019030744253</v>
+        <v>0.08938334339504721</v>
       </c>
       <c r="E3" s="4">
-        <v>84.3430579821718</v>
+        <v>85.22783045904163</v>
       </c>
       <c r="F3" s="4">
-        <v>90.43456009468036</v>
+        <v>90.50211762375399</v>
       </c>
       <c r="G3" s="5">
         <v>8854</v>
       </c>
       <c r="H3" s="5">
-        <v>7852</v>
+        <v>7577</v>
       </c>
       <c r="I3" s="5">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="J3" s="5">
-        <v>572</v>
+        <v>851</v>
       </c>
       <c r="K3" s="5">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="L3" s="5">
-        <v>477</v>
+        <v>749</v>
       </c>
       <c r="M3" s="5">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3500145417058187</v>
+        <v>0.2865562213397593</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2363412134538259</v>
+        <v>0.1759633875741794</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2260219368772913</v>
+        <v>0.2125511454920036</v>
       </c>
       <c r="E4" s="4">
-        <v>83.35426513370535</v>
+        <v>84.74118734257821</v>
       </c>
       <c r="F4" s="4">
-        <v>89.74698787590285</v>
+        <v>90.27643650591502</v>
       </c>
       <c r="G4" s="5">
         <v>7457</v>
       </c>
       <c r="H4" s="5">
-        <v>6589</v>
+        <v>6450</v>
       </c>
       <c r="I4" s="5">
-        <v>217</v>
+        <v>134</v>
       </c>
       <c r="J4" s="5">
-        <v>651</v>
+        <v>873</v>
       </c>
       <c r="K4" s="5">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="L4" s="5">
-        <v>529</v>
+        <v>713</v>
       </c>
       <c r="M4" s="5">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>2.842158451246128</v>
+        <v>0.6344960776293731</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2371638556458561</v>
+        <v>0.5092354300092027</v>
       </c>
       <c r="D5" s="4">
-        <v>3.417043673744591</v>
+        <v>0.5628895403897124</v>
       </c>
       <c r="E5" s="4">
-        <v>77.30584457965577</v>
+        <v>84.65319415865144</v>
       </c>
       <c r="F5" s="4">
-        <v>83.91516185920619</v>
+        <v>90.29986705902328</v>
       </c>
       <c r="G5" s="5">
         <v>7369</v>
       </c>
       <c r="H5" s="5">
-        <v>4377</v>
+        <v>6250</v>
       </c>
       <c r="I5" s="5">
-        <v>420</v>
+        <v>148</v>
       </c>
       <c r="J5" s="5">
-        <v>2572</v>
+        <v>971</v>
       </c>
       <c r="K5" s="5">
-        <v>376</v>
+        <v>126</v>
       </c>
       <c r="L5" s="5">
-        <v>1049</v>
+        <v>711</v>
       </c>
       <c r="M5" s="5">
-        <v>1147</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
-        <v>0.2319316894388594</v>
+        <v>0.3395055396326073</v>
       </c>
       <c r="C6" s="4">
-        <v>0.192368970227657</v>
+        <v>0.2947214046058921</v>
       </c>
       <c r="D6" s="4">
-        <v>0.2162395605586726</v>
+        <v>0.3199744929124465</v>
       </c>
       <c r="E6" s="4">
-        <v>83.94419708695588</v>
+        <v>84.61411061327492</v>
       </c>
       <c r="F6" s="4">
-        <v>90.0628569141064</v>
+        <v>89.97084447667464</v>
       </c>
       <c r="G6" s="5">
         <v>5812</v>
       </c>
       <c r="H6" s="5">
-        <v>5158</v>
+        <v>4974</v>
       </c>
       <c r="I6" s="5">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="J6" s="5">
-        <v>420</v>
+        <v>629</v>
       </c>
       <c r="K6" s="5">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="L6" s="5">
-        <v>362</v>
+        <v>539</v>
       </c>
       <c r="M6" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
-        <v>0.283190840844276</v>
+        <v>0.2720679239865053</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1901915333541864</v>
+        <v>0.1505896430334469</v>
       </c>
       <c r="D7" s="4">
-        <v>0.2177264012550026</v>
+        <v>0.1838700974618941</v>
       </c>
       <c r="E7" s="4">
-        <v>83.6674779531923</v>
+        <v>84.0349354635069</v>
       </c>
       <c r="F7" s="4">
-        <v>89.50377091316678</v>
+        <v>89.40403420269188</v>
       </c>
       <c r="G7" s="5">
         <v>5291</v>
       </c>
       <c r="H7" s="5">
-        <v>4595</v>
+        <v>4488</v>
       </c>
       <c r="I7" s="5">
-        <v>215</v>
+        <v>137</v>
       </c>
       <c r="J7" s="5">
-        <v>481</v>
+        <v>666</v>
       </c>
       <c r="K7" s="5">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="L7" s="5">
-        <v>390</v>
+        <v>549</v>
       </c>
       <c r="M7" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
-        <v>0.3162027237233069</v>
+        <v>0.3631293060267505</v>
       </c>
       <c r="C8" s="4">
-        <v>0.121749068787875</v>
+        <v>0.2591855468839788</v>
       </c>
       <c r="D8" s="4">
-        <v>0.1228527058599523</v>
+        <v>0.2719801476436401</v>
       </c>
       <c r="E8" s="4">
-        <v>76.53626196241204</v>
+        <v>79.30764057035236</v>
       </c>
       <c r="F8" s="4">
-        <v>80.76376723669406</v>
+        <v>83.55705961905507</v>
       </c>
       <c r="G8" s="5">
         <v>1770</v>
       </c>
       <c r="H8" s="5">
-        <v>1221</v>
+        <v>1315</v>
       </c>
       <c r="I8" s="5">
-        <v>368</v>
+        <v>266</v>
       </c>
       <c r="J8" s="5">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="K8" s="5">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="L8" s="5">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
@@ -10939,40 +10841,40 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
-        <v>0.4960080037277111</v>
+        <v>0.3349089119647184</v>
       </c>
       <c r="C9" s="4">
-        <v>0.3448118716630564</v>
+        <v>0.1455267494158514</v>
       </c>
       <c r="D9" s="4">
-        <v>0.3260785526776173</v>
+        <v>0.1590752068683805</v>
       </c>
       <c r="E9" s="4">
-        <v>83.41467780950646</v>
+        <v>82.55567053522307</v>
       </c>
       <c r="F9" s="4">
-        <v>89.45833441026029</v>
+        <v>88.02840502795682</v>
       </c>
       <c r="G9" s="5">
         <v>1558</v>
       </c>
       <c r="H9" s="5">
-        <v>1356</v>
+        <v>1277</v>
       </c>
       <c r="I9" s="5">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J9" s="5">
-        <v>132</v>
+        <v>201</v>
       </c>
       <c r="K9" s="5">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L9" s="5">
-        <v>104</v>
+        <v>163</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
@@ -10980,40 +10882,40 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
-        <v>0.1204841903190259</v>
+        <v>0.131291632465652</v>
       </c>
       <c r="C10" s="4">
-        <v>0.07313036870627858</v>
+        <v>0.114452209043751</v>
       </c>
       <c r="D10" s="4">
-        <v>0.407321531637707</v>
+        <v>0.1321805247381784</v>
       </c>
       <c r="E10" s="4">
-        <v>72.46206174777618</v>
+        <v>84.33782117801478</v>
       </c>
       <c r="F10" s="4">
-        <v>77.62836554868193</v>
+        <v>89.01804438688757</v>
       </c>
       <c r="G10" s="5">
         <v>1534</v>
       </c>
       <c r="H10" s="5">
-        <v>967</v>
+        <v>1348</v>
       </c>
       <c r="I10" s="5">
-        <v>511</v>
+        <v>112</v>
       </c>
       <c r="J10" s="5">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="K10" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L10" s="5">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
@@ -11021,40 +10923,40 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
-        <v>0.2256699034151969</v>
+        <v>0.2861976020570335</v>
       </c>
       <c r="C11" s="4">
-        <v>0.1314297184762287</v>
+        <v>0.1633441667904302</v>
       </c>
       <c r="D11" s="4">
-        <v>0.1222831093877331</v>
+        <v>0.1837904824193713</v>
       </c>
       <c r="E11" s="4">
-        <v>85.19093181039025</v>
+        <v>83.88756563633412</v>
       </c>
       <c r="F11" s="4">
-        <v>90.77569888261758</v>
+        <v>89.53859802158824</v>
       </c>
       <c r="G11" s="5">
         <v>1508</v>
       </c>
       <c r="H11" s="5">
-        <v>1336</v>
+        <v>1291</v>
       </c>
       <c r="I11" s="5">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="J11" s="5">
-        <v>101</v>
+        <v>166</v>
       </c>
       <c r="K11" s="5">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="L11" s="5">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
@@ -11062,40 +10964,40 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
-        <v>0.2427674614046499</v>
+        <v>0.2878866412841499</v>
       </c>
       <c r="C12" s="4">
-        <v>0.1238243962824101</v>
+        <v>0.1531587268858774</v>
       </c>
       <c r="D12" s="4">
-        <v>0.10622855678811</v>
+        <v>0.167716983430375</v>
       </c>
       <c r="E12" s="4">
-        <v>82.17220495880103</v>
+        <v>81.21210212480059</v>
       </c>
       <c r="F12" s="4">
-        <v>87.78080052046403</v>
+        <v>85.98471596959483</v>
       </c>
       <c r="G12" s="5">
         <v>1458</v>
       </c>
       <c r="H12" s="5">
-        <v>1205</v>
+        <v>1141</v>
       </c>
       <c r="I12" s="5">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="J12" s="5">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="K12" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L12" s="5">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="M12" s="5">
         <v>0</v>
@@ -11103,40 +11005,40 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
-        <v>0.1570673191121089</v>
+        <v>0.203393533897513</v>
       </c>
       <c r="C13" s="4">
-        <v>0.1087894286732539</v>
+        <v>0.1704409460091469</v>
       </c>
       <c r="D13" s="4">
-        <v>0.09217334576801403</v>
+        <v>0.184161619260823</v>
       </c>
       <c r="E13" s="4">
-        <v>83.19568949074954</v>
+        <v>82.94363383982864</v>
       </c>
       <c r="F13" s="4">
-        <v>89.16880971795355</v>
+        <v>88.56522716343606</v>
       </c>
       <c r="G13" s="5">
         <v>1284</v>
       </c>
       <c r="H13" s="5">
-        <v>1132</v>
+        <v>1112</v>
       </c>
       <c r="I13" s="5">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="J13" s="5">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="K13" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L13" s="5">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="M13" s="5">
         <v>0</v>
@@ -11144,43 +11046,43 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
-        <v>0.2984619495768797</v>
+        <v>0.2316653735317337</v>
       </c>
       <c r="C14" s="4">
-        <v>0.1000544543290736</v>
+        <v>0.1653422254604998</v>
       </c>
       <c r="D14" s="4">
-        <v>0.2437430165396717</v>
+        <v>0.1718466861596706</v>
       </c>
       <c r="E14" s="4">
-        <v>80.23531355862175</v>
+        <v>84.19975763584776</v>
       </c>
       <c r="F14" s="4">
-        <v>85.72025831227545</v>
+        <v>88.21409486545467</v>
       </c>
       <c r="G14" s="5">
         <v>1235</v>
       </c>
       <c r="H14" s="5">
-        <v>1026</v>
+        <v>1055</v>
       </c>
       <c r="I14" s="5">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="J14" s="5">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="K14" s="5">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L14" s="5">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M14" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11217,7 +11119,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -11238,13 +11140,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -11275,40 +11177,40 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1498682668308317</v>
+        <v>0.1678222330956704</v>
       </c>
       <c r="C3" s="4">
-        <v>0.07275628196009409</v>
+        <v>0.081963032306311</v>
       </c>
       <c r="D3" s="4">
-        <v>0.08938334339504721</v>
+        <v>0.1003773378060972</v>
       </c>
       <c r="E3" s="4">
-        <v>85.22783045904163</v>
+        <v>84.49004946455658</v>
       </c>
       <c r="F3" s="4">
-        <v>90.50211762375399</v>
+        <v>89.79869182851439</v>
       </c>
       <c r="G3" s="5">
         <v>8854</v>
       </c>
       <c r="H3" s="5">
-        <v>7577</v>
+        <v>7561</v>
       </c>
       <c r="I3" s="5">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="J3" s="5">
-        <v>851</v>
+        <v>864</v>
       </c>
       <c r="K3" s="5">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="L3" s="5">
-        <v>749</v>
+        <v>722</v>
       </c>
       <c r="M3" s="5">
         <v>4</v>
@@ -11316,163 +11218,163 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2865562213397593</v>
+        <v>0.3065475219088689</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1759633875741794</v>
+        <v>0.1956919004329768</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2125511454920036</v>
+        <v>0.2365989292142728</v>
       </c>
       <c r="E4" s="4">
-        <v>84.74118734257821</v>
+        <v>83.21075754963364</v>
       </c>
       <c r="F4" s="4">
-        <v>90.27643650591502</v>
+        <v>89.01439243459643</v>
       </c>
       <c r="G4" s="5">
         <v>7457</v>
       </c>
       <c r="H4" s="5">
-        <v>6450</v>
+        <v>6365</v>
       </c>
       <c r="I4" s="5">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="J4" s="5">
-        <v>873</v>
+        <v>941</v>
       </c>
       <c r="K4" s="5">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="L4" s="5">
-        <v>713</v>
+        <v>768</v>
       </c>
       <c r="M4" s="5">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6344960776293731</v>
+        <v>0.4369099233162749</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5092354300092027</v>
+        <v>0.3400299799215908</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5628895403897124</v>
+        <v>0.3676445440716815</v>
       </c>
       <c r="E5" s="4">
-        <v>84.65319415865144</v>
+        <v>83.58618518651858</v>
       </c>
       <c r="F5" s="4">
-        <v>90.29986705902328</v>
+        <v>89.29686245329708</v>
       </c>
       <c r="G5" s="5">
         <v>7369</v>
       </c>
       <c r="H5" s="5">
-        <v>6250</v>
+        <v>6320</v>
       </c>
       <c r="I5" s="5">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="J5" s="5">
-        <v>971</v>
+        <v>886</v>
       </c>
       <c r="K5" s="5">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="L5" s="5">
-        <v>711</v>
+        <v>732</v>
       </c>
       <c r="M5" s="5">
-        <v>134</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
-        <v>0.3395055396326073</v>
+        <v>0.3452001802593515</v>
       </c>
       <c r="C6" s="4">
-        <v>0.2947214046058921</v>
+        <v>0.2926860576201246</v>
       </c>
       <c r="D6" s="4">
-        <v>0.3199744929124465</v>
+        <v>0.321951288432609</v>
       </c>
       <c r="E6" s="4">
-        <v>84.61411061327492</v>
+        <v>83.40038320903037</v>
       </c>
       <c r="F6" s="4">
-        <v>89.97084447667464</v>
+        <v>88.86560398835393</v>
       </c>
       <c r="G6" s="5">
         <v>5812</v>
       </c>
       <c r="H6" s="5">
-        <v>4974</v>
+        <v>4902</v>
       </c>
       <c r="I6" s="5">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="J6" s="5">
-        <v>629</v>
+        <v>665</v>
       </c>
       <c r="K6" s="5">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="L6" s="5">
-        <v>539</v>
+        <v>567</v>
       </c>
       <c r="M6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
-        <v>0.2720679239865053</v>
+        <v>0.2867383940148957</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1505896430334469</v>
+        <v>0.1575023559804229</v>
       </c>
       <c r="D7" s="4">
-        <v>0.1838700974618941</v>
+        <v>0.1911472141797629</v>
       </c>
       <c r="E7" s="4">
-        <v>84.0349354635069</v>
+        <v>82.46366889224029</v>
       </c>
       <c r="F7" s="4">
-        <v>89.40403420269188</v>
+        <v>88.18055183826991</v>
       </c>
       <c r="G7" s="5">
         <v>5291</v>
       </c>
       <c r="H7" s="5">
-        <v>4488</v>
+        <v>4415</v>
       </c>
       <c r="I7" s="5">
         <v>137</v>
       </c>
       <c r="J7" s="5">
-        <v>666</v>
+        <v>739</v>
       </c>
       <c r="K7" s="5">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="L7" s="5">
-        <v>549</v>
+        <v>606</v>
       </c>
       <c r="M7" s="5">
         <v>1</v>
@@ -11480,40 +11382,40 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
-        <v>0.3631293060267505</v>
+        <v>0.3680515211771396</v>
       </c>
       <c r="C8" s="4">
-        <v>0.2591855468839788</v>
+        <v>0.2681429577911167</v>
       </c>
       <c r="D8" s="4">
-        <v>0.2719801476436401</v>
+        <v>0.2832992532343568</v>
       </c>
       <c r="E8" s="4">
-        <v>79.30764057035236</v>
+        <v>78.89793996694729</v>
       </c>
       <c r="F8" s="4">
-        <v>83.55705961905507</v>
+        <v>82.99003399941867</v>
       </c>
       <c r="G8" s="5">
         <v>1770</v>
       </c>
       <c r="H8" s="5">
-        <v>1315</v>
+        <v>1304</v>
       </c>
       <c r="I8" s="5">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J8" s="5">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="K8" s="5">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="L8" s="5">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
@@ -11521,40 +11423,40 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
-        <v>0.3349089119647184</v>
+        <v>0.3350293684006022</v>
       </c>
       <c r="C9" s="4">
-        <v>0.1455267494158514</v>
+        <v>0.1517552593400343</v>
       </c>
       <c r="D9" s="4">
-        <v>0.1590752068683805</v>
+        <v>0.1611633946758805</v>
       </c>
       <c r="E9" s="4">
-        <v>82.55567053522307</v>
+        <v>81.89685887191835</v>
       </c>
       <c r="F9" s="4">
-        <v>88.02840502795682</v>
+        <v>87.34312044639375</v>
       </c>
       <c r="G9" s="5">
         <v>1558</v>
       </c>
       <c r="H9" s="5">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="I9" s="5">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="J9" s="5">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="K9" s="5">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="L9" s="5">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
@@ -11562,40 +11464,40 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
-        <v>0.131291632465652</v>
+        <v>0.1515865214681973</v>
       </c>
       <c r="C10" s="4">
-        <v>0.114452209043751</v>
+        <v>0.1418197834310556</v>
       </c>
       <c r="D10" s="4">
-        <v>0.1321805247381784</v>
+        <v>0.1607119122153549</v>
       </c>
       <c r="E10" s="4">
-        <v>84.33782117801478</v>
+        <v>83.28836619393525</v>
       </c>
       <c r="F10" s="4">
-        <v>89.01804438688757</v>
+        <v>87.85950958001933</v>
       </c>
       <c r="G10" s="5">
         <v>1534</v>
       </c>
       <c r="H10" s="5">
-        <v>1348</v>
+        <v>1318</v>
       </c>
       <c r="I10" s="5">
-        <v>112</v>
+        <v>157</v>
       </c>
       <c r="J10" s="5">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="K10" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L10" s="5">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
@@ -11603,40 +11505,40 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
-        <v>0.2861976020570335</v>
+        <v>0.2938325955664572</v>
       </c>
       <c r="C11" s="4">
-        <v>0.1633441667904302</v>
+        <v>0.1700126831806813</v>
       </c>
       <c r="D11" s="4">
-        <v>0.1837904824193713</v>
+        <v>0.1781262103348235</v>
       </c>
       <c r="E11" s="4">
-        <v>83.88756563633412</v>
+        <v>83.59982587199319</v>
       </c>
       <c r="F11" s="4">
-        <v>89.53859802158824</v>
+        <v>89.02026626077772</v>
       </c>
       <c r="G11" s="5">
         <v>1508</v>
       </c>
       <c r="H11" s="5">
-        <v>1291</v>
+        <v>1286</v>
       </c>
       <c r="I11" s="5">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="J11" s="5">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="K11" s="5">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L11" s="5">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
@@ -11644,40 +11546,40 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
-        <v>0.2878866412841499</v>
+        <v>0.2804592988193587</v>
       </c>
       <c r="C12" s="4">
-        <v>0.1531587268858774</v>
+        <v>0.1449672381285011</v>
       </c>
       <c r="D12" s="4">
-        <v>0.167716983430375</v>
+        <v>0.1529811262208443</v>
       </c>
       <c r="E12" s="4">
-        <v>81.21210212480059</v>
+        <v>81.2383705196756</v>
       </c>
       <c r="F12" s="4">
-        <v>85.98471596959483</v>
+        <v>86.11160211499983</v>
       </c>
       <c r="G12" s="5">
         <v>1458</v>
       </c>
       <c r="H12" s="5">
-        <v>1141</v>
+        <v>1148</v>
       </c>
       <c r="I12" s="5">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J12" s="5">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="K12" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L12" s="5">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="M12" s="5">
         <v>0</v>
@@ -11685,40 +11587,40 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
-        <v>0.203393533897513</v>
+        <v>0.1870925043279126</v>
       </c>
       <c r="C13" s="4">
-        <v>0.1704409460091469</v>
+        <v>0.1551472626168532</v>
       </c>
       <c r="D13" s="4">
-        <v>0.184161619260823</v>
+        <v>0.1687476482264652</v>
       </c>
       <c r="E13" s="4">
-        <v>82.94363383982864</v>
+        <v>83.26265708775709</v>
       </c>
       <c r="F13" s="4">
-        <v>88.56522716343606</v>
+        <v>88.91620843700116</v>
       </c>
       <c r="G13" s="5">
         <v>1284</v>
       </c>
       <c r="H13" s="5">
-        <v>1112</v>
+        <v>1128</v>
       </c>
       <c r="I13" s="5">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="J13" s="5">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="K13" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L13" s="5">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="M13" s="5">
         <v>0</v>
@@ -11726,40 +11628,40 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
-        <v>0.2316653735317337</v>
+        <v>0.2486498737454398</v>
       </c>
       <c r="C14" s="4">
-        <v>0.1653422254604998</v>
+        <v>0.1795774517283885</v>
       </c>
       <c r="D14" s="4">
-        <v>0.1718466861596706</v>
+        <v>0.1890293862896607</v>
       </c>
       <c r="E14" s="4">
-        <v>84.19975763584776</v>
+        <v>83.14357321876102</v>
       </c>
       <c r="F14" s="4">
-        <v>88.21409486545467</v>
+        <v>86.97832604226103</v>
       </c>
       <c r="G14" s="5">
         <v>1235</v>
       </c>
       <c r="H14" s="5">
-        <v>1055</v>
+        <v>1034</v>
       </c>
       <c r="I14" s="5">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="J14" s="5">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="K14" s="5">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="L14" s="5">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="M14" s="5">
         <v>0</v>
@@ -11799,7 +11701,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -11820,13 +11722,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -11857,40 +11759,40 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1678222330956704</v>
+        <v>0.1753890890990819</v>
       </c>
       <c r="C3" s="4">
-        <v>0.081963032306311</v>
+        <v>0.08599268611762723</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1003773378060972</v>
+        <v>0.1021239565015965</v>
       </c>
       <c r="E3" s="4">
-        <v>84.49004946455658</v>
+        <v>84.38994866073827</v>
       </c>
       <c r="F3" s="4">
-        <v>89.79869182851439</v>
+        <v>89.89816278894661</v>
       </c>
       <c r="G3" s="5">
         <v>8854</v>
       </c>
       <c r="H3" s="5">
-        <v>7561</v>
+        <v>7518</v>
       </c>
       <c r="I3" s="5">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="J3" s="5">
-        <v>864</v>
+        <v>925</v>
       </c>
       <c r="K3" s="5">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="L3" s="5">
-        <v>722</v>
+        <v>806</v>
       </c>
       <c r="M3" s="5">
         <v>4</v>
@@ -11898,122 +11800,122 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3065475219088689</v>
+        <v>0.3173178345074229</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1956919004329768</v>
+        <v>0.1980461432681556</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2365989292142728</v>
+        <v>0.2381383217467092</v>
       </c>
       <c r="E4" s="4">
-        <v>83.21075754963364</v>
+        <v>83.44520830995668</v>
       </c>
       <c r="F4" s="4">
-        <v>89.01439243459643</v>
+        <v>89.20199599253479</v>
       </c>
       <c r="G4" s="5">
         <v>7457</v>
       </c>
       <c r="H4" s="5">
-        <v>6365</v>
+        <v>6314</v>
       </c>
       <c r="I4" s="5">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J4" s="5">
-        <v>941</v>
+        <v>993</v>
       </c>
       <c r="K4" s="5">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="L4" s="5">
-        <v>768</v>
+        <v>812</v>
       </c>
       <c r="M4" s="5">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4369099233162749</v>
+        <v>0.4422148092753599</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3400299799215908</v>
+        <v>0.3440190785687459</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3676445440716815</v>
+        <v>0.3726681734376111</v>
       </c>
       <c r="E5" s="4">
-        <v>83.58618518651858</v>
+        <v>83.81191477812452</v>
       </c>
       <c r="F5" s="4">
-        <v>89.29686245329708</v>
+        <v>89.6465436712173</v>
       </c>
       <c r="G5" s="5">
         <v>7369</v>
       </c>
       <c r="H5" s="5">
-        <v>6320</v>
+        <v>6293</v>
       </c>
       <c r="I5" s="5">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="J5" s="5">
-        <v>886</v>
+        <v>905</v>
       </c>
       <c r="K5" s="5">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="L5" s="5">
-        <v>732</v>
+        <v>779</v>
       </c>
       <c r="M5" s="5">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
-        <v>0.3452001802593515</v>
+        <v>0.3559215003393052</v>
       </c>
       <c r="C6" s="4">
-        <v>0.2926860576201246</v>
+        <v>0.3063220968416379</v>
       </c>
       <c r="D6" s="4">
-        <v>0.321951288432609</v>
+        <v>0.3368170155525154</v>
       </c>
       <c r="E6" s="4">
-        <v>83.40038320903037</v>
+        <v>83.66469678029499</v>
       </c>
       <c r="F6" s="4">
-        <v>88.86560398835393</v>
+        <v>89.16299263577181</v>
       </c>
       <c r="G6" s="5">
         <v>5812</v>
       </c>
       <c r="H6" s="5">
-        <v>4902</v>
+        <v>4885</v>
       </c>
       <c r="I6" s="5">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="J6" s="5">
-        <v>665</v>
+        <v>706</v>
       </c>
       <c r="K6" s="5">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="L6" s="5">
-        <v>567</v>
+        <v>596</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
@@ -12021,40 +11923,40 @@
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
-        <v>0.2867383940148957</v>
+        <v>0.3061429334147152</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1575023559804229</v>
+        <v>0.1800618423058074</v>
       </c>
       <c r="D7" s="4">
-        <v>0.1911472141797629</v>
+        <v>0.2185586987717159</v>
       </c>
       <c r="E7" s="4">
-        <v>82.46366889224029</v>
+        <v>82.79829565543854</v>
       </c>
       <c r="F7" s="4">
-        <v>88.18055183826991</v>
+        <v>88.41422921959837</v>
       </c>
       <c r="G7" s="5">
         <v>5291</v>
       </c>
       <c r="H7" s="5">
-        <v>4415</v>
+        <v>4402</v>
       </c>
       <c r="I7" s="5">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="J7" s="5">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="K7" s="5">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="L7" s="5">
-        <v>606</v>
+        <v>622</v>
       </c>
       <c r="M7" s="5">
         <v>1</v>
@@ -12062,40 +11964,40 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
-        <v>0.3680515211771396</v>
+        <v>0.3780627488478996</v>
       </c>
       <c r="C8" s="4">
-        <v>0.2681429577911167</v>
+        <v>0.2500913424206281</v>
       </c>
       <c r="D8" s="4">
-        <v>0.2832992532343568</v>
+        <v>0.2743368040300056</v>
       </c>
       <c r="E8" s="4">
-        <v>78.89793996694729</v>
+        <v>78.28194780737154</v>
       </c>
       <c r="F8" s="4">
-        <v>82.99003399941867</v>
+        <v>81.9472819423907</v>
       </c>
       <c r="G8" s="5">
         <v>1770</v>
       </c>
       <c r="H8" s="5">
-        <v>1304</v>
+        <v>1263</v>
       </c>
       <c r="I8" s="5">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="J8" s="5">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="K8" s="5">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="L8" s="5">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
@@ -12103,40 +12005,40 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
-        <v>0.3350293684006022</v>
+        <v>0.3384764396386602</v>
       </c>
       <c r="C9" s="4">
-        <v>0.1517552593400343</v>
+        <v>0.1554568687657341</v>
       </c>
       <c r="D9" s="4">
-        <v>0.1611633946758805</v>
+        <v>0.1614809435974536</v>
       </c>
       <c r="E9" s="4">
-        <v>81.89685887191835</v>
+        <v>82.35835669312658</v>
       </c>
       <c r="F9" s="4">
-        <v>87.34312044639375</v>
+        <v>87.65934212680176</v>
       </c>
       <c r="G9" s="5">
         <v>1558</v>
       </c>
       <c r="H9" s="5">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="I9" s="5">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J9" s="5">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="K9" s="5">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L9" s="5">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
@@ -12144,40 +12046,40 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
-        <v>0.1515865214681973</v>
+        <v>0.1404471542161385</v>
       </c>
       <c r="C10" s="4">
-        <v>0.1418197834310556</v>
+        <v>0.1268978735797099</v>
       </c>
       <c r="D10" s="4">
-        <v>0.1607119122153549</v>
+        <v>0.1470623916488105</v>
       </c>
       <c r="E10" s="4">
-        <v>83.28836619393525</v>
+        <v>83.68597504190718</v>
       </c>
       <c r="F10" s="4">
-        <v>87.85950958001933</v>
+        <v>88.0550256818604</v>
       </c>
       <c r="G10" s="5">
         <v>1534</v>
       </c>
       <c r="H10" s="5">
-        <v>1318</v>
+        <v>1324</v>
       </c>
       <c r="I10" s="5">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="J10" s="5">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K10" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L10" s="5">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
@@ -12185,40 +12087,40 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
-        <v>0.2938325955664572</v>
+        <v>0.2964446699145949</v>
       </c>
       <c r="C11" s="4">
-        <v>0.1700126831806813</v>
+        <v>0.1737804754894592</v>
       </c>
       <c r="D11" s="4">
-        <v>0.1781262103348235</v>
+        <v>0.1899437948369821</v>
       </c>
       <c r="E11" s="4">
-        <v>83.59982587199319</v>
+        <v>84.0496039264512</v>
       </c>
       <c r="F11" s="4">
-        <v>89.02026626077772</v>
+        <v>89.20063167951334</v>
       </c>
       <c r="G11" s="5">
         <v>1508</v>
       </c>
       <c r="H11" s="5">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="I11" s="5">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="J11" s="5">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="K11" s="5">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L11" s="5">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
@@ -12226,40 +12128,40 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
-        <v>0.2804592988193587</v>
+        <v>0.2890382921100689</v>
       </c>
       <c r="C12" s="4">
-        <v>0.1449672381285011</v>
+        <v>0.1559829286171532</v>
       </c>
       <c r="D12" s="4">
-        <v>0.1529811262208443</v>
+        <v>0.1672934394932305</v>
       </c>
       <c r="E12" s="4">
-        <v>81.2383705196756</v>
+        <v>81.36789283614689</v>
       </c>
       <c r="F12" s="4">
-        <v>86.11160211499983</v>
+        <v>86.05426973912373</v>
       </c>
       <c r="G12" s="5">
         <v>1458</v>
       </c>
       <c r="H12" s="5">
-        <v>1148</v>
+        <v>1142</v>
       </c>
       <c r="I12" s="5">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="J12" s="5">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="K12" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L12" s="5">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M12" s="5">
         <v>0</v>
@@ -12267,40 +12169,40 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
-        <v>0.1870925043279126</v>
+        <v>0.2010885495357042</v>
       </c>
       <c r="C13" s="4">
-        <v>0.1551472626168532</v>
+        <v>0.1649902378437638</v>
       </c>
       <c r="D13" s="4">
-        <v>0.1687476482264652</v>
+        <v>0.1782918604833364</v>
       </c>
       <c r="E13" s="4">
-        <v>83.26265708775709</v>
+        <v>83.33857842202309</v>
       </c>
       <c r="F13" s="4">
-        <v>88.91620843700116</v>
+        <v>88.77716273948208</v>
       </c>
       <c r="G13" s="5">
         <v>1284</v>
       </c>
       <c r="H13" s="5">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="I13" s="5">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J13" s="5">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="K13" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L13" s="5">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="M13" s="5">
         <v>0</v>
@@ -12308,589 +12210,7 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="4">
-        <v>0.2486498737454398</v>
-      </c>
-      <c r="C14" s="4">
-        <v>0.1795774517283885</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0.1890293862896607</v>
-      </c>
-      <c r="E14" s="4">
-        <v>83.14357321876102</v>
-      </c>
-      <c r="F14" s="4">
-        <v>86.97832604226103</v>
-      </c>
-      <c r="G14" s="5">
-        <v>1235</v>
-      </c>
-      <c r="H14" s="5">
-        <v>1034</v>
-      </c>
-      <c r="I14" s="5">
-        <v>69</v>
-      </c>
-      <c r="J14" s="5">
-        <v>132</v>
-      </c>
-      <c r="K14" s="5">
-        <v>36</v>
-      </c>
-      <c r="L14" s="5">
-        <v>96</v>
-      </c>
-      <c r="M14" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.1753890890990819</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.08599268611762723</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.1021239565015965</v>
-      </c>
-      <c r="E3" s="4">
-        <v>84.38994866073827</v>
-      </c>
-      <c r="F3" s="4">
-        <v>89.89816278894661</v>
-      </c>
-      <c r="G3" s="5">
-        <v>8854</v>
-      </c>
-      <c r="H3" s="5">
-        <v>7518</v>
-      </c>
-      <c r="I3" s="5">
-        <v>411</v>
-      </c>
-      <c r="J3" s="5">
-        <v>925</v>
-      </c>
-      <c r="K3" s="5">
-        <v>115</v>
-      </c>
-      <c r="L3" s="5">
-        <v>806</v>
-      </c>
-      <c r="M3" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3173178345074229</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1980461432681556</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2381383217467092</v>
-      </c>
-      <c r="E4" s="4">
-        <v>83.44520830995668</v>
-      </c>
-      <c r="F4" s="4">
-        <v>89.20199599253479</v>
-      </c>
-      <c r="G4" s="5">
-        <v>7457</v>
-      </c>
-      <c r="H4" s="5">
-        <v>6314</v>
-      </c>
-      <c r="I4" s="5">
-        <v>150</v>
-      </c>
-      <c r="J4" s="5">
-        <v>993</v>
-      </c>
-      <c r="K4" s="5">
-        <v>158</v>
-      </c>
-      <c r="L4" s="5">
-        <v>812</v>
-      </c>
-      <c r="M4" s="5">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.4422148092753599</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.3440190785687459</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3726681734376111</v>
-      </c>
-      <c r="E5" s="4">
-        <v>83.81191477812452</v>
-      </c>
-      <c r="F5" s="4">
-        <v>89.6465436712173</v>
-      </c>
-      <c r="G5" s="5">
-        <v>7369</v>
-      </c>
-      <c r="H5" s="5">
-        <v>6293</v>
-      </c>
-      <c r="I5" s="5">
-        <v>171</v>
-      </c>
-      <c r="J5" s="5">
-        <v>905</v>
-      </c>
-      <c r="K5" s="5">
-        <v>112</v>
-      </c>
-      <c r="L5" s="5">
-        <v>779</v>
-      </c>
-      <c r="M5" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.3559215003393052</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.3063220968416379</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.3368170155525154</v>
-      </c>
-      <c r="E6" s="4">
-        <v>83.66469678029499</v>
-      </c>
-      <c r="F6" s="4">
-        <v>89.16299263577181</v>
-      </c>
-      <c r="G6" s="5">
-        <v>5812</v>
-      </c>
-      <c r="H6" s="5">
-        <v>4885</v>
-      </c>
-      <c r="I6" s="5">
-        <v>221</v>
-      </c>
-      <c r="J6" s="5">
-        <v>706</v>
-      </c>
-      <c r="K6" s="5">
-        <v>110</v>
-      </c>
-      <c r="L6" s="5">
-        <v>596</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.3061429334147152</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0.1800618423058074</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.2185586987717159</v>
-      </c>
-      <c r="E7" s="4">
-        <v>82.79829565543854</v>
-      </c>
-      <c r="F7" s="4">
-        <v>88.41422921959837</v>
-      </c>
-      <c r="G7" s="5">
-        <v>5291</v>
-      </c>
-      <c r="H7" s="5">
-        <v>4402</v>
-      </c>
-      <c r="I7" s="5">
-        <v>157</v>
-      </c>
-      <c r="J7" s="5">
-        <v>732</v>
-      </c>
-      <c r="K7" s="5">
-        <v>109</v>
-      </c>
-      <c r="L7" s="5">
-        <v>622</v>
-      </c>
-      <c r="M7" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="4">
-        <v>0.3780627488478996</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0.2500913424206281</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0.2743368040300056</v>
-      </c>
-      <c r="E8" s="4">
-        <v>78.28194780737154</v>
-      </c>
-      <c r="F8" s="4">
-        <v>81.9472819423907</v>
-      </c>
-      <c r="G8" s="5">
-        <v>1770</v>
-      </c>
-      <c r="H8" s="5">
-        <v>1263</v>
-      </c>
-      <c r="I8" s="5">
-        <v>299</v>
-      </c>
-      <c r="J8" s="5">
-        <v>208</v>
-      </c>
-      <c r="K8" s="5">
-        <v>79</v>
-      </c>
-      <c r="L8" s="5">
-        <v>129</v>
-      </c>
-      <c r="M8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="4">
-        <v>0.3384764396386602</v>
-      </c>
-      <c r="C9" s="4">
-        <v>0.1554568687657341</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0.1614809435974536</v>
-      </c>
-      <c r="E9" s="4">
-        <v>82.35835669312658</v>
-      </c>
-      <c r="F9" s="4">
-        <v>87.65934212680176</v>
-      </c>
-      <c r="G9" s="5">
-        <v>1558</v>
-      </c>
-      <c r="H9" s="5">
-        <v>1274</v>
-      </c>
-      <c r="I9" s="5">
-        <v>81</v>
-      </c>
-      <c r="J9" s="5">
-        <v>203</v>
-      </c>
-      <c r="K9" s="5">
-        <v>37</v>
-      </c>
-      <c r="L9" s="5">
-        <v>166</v>
-      </c>
-      <c r="M9" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="25" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="4">
-        <v>0.1404471542161385</v>
-      </c>
-      <c r="C10" s="4">
-        <v>0.1268978735797099</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0.1470623916488105</v>
-      </c>
-      <c r="E10" s="4">
-        <v>83.68597504190718</v>
-      </c>
-      <c r="F10" s="4">
-        <v>88.0550256818604</v>
-      </c>
-      <c r="G10" s="5">
-        <v>1534</v>
-      </c>
-      <c r="H10" s="5">
-        <v>1324</v>
-      </c>
-      <c r="I10" s="5">
-        <v>143</v>
-      </c>
-      <c r="J10" s="5">
-        <v>67</v>
-      </c>
-      <c r="K10" s="5">
-        <v>3</v>
-      </c>
-      <c r="L10" s="5">
         <v>64</v>
-      </c>
-      <c r="M10" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="4">
-        <v>0.2964446699145949</v>
-      </c>
-      <c r="C11" s="4">
-        <v>0.1737804754894592</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0.1899437948369821</v>
-      </c>
-      <c r="E11" s="4">
-        <v>84.0496039264512</v>
-      </c>
-      <c r="F11" s="4">
-        <v>89.20063167951334</v>
-      </c>
-      <c r="G11" s="5">
-        <v>1508</v>
-      </c>
-      <c r="H11" s="5">
-        <v>1284</v>
-      </c>
-      <c r="I11" s="5">
-        <v>67</v>
-      </c>
-      <c r="J11" s="5">
-        <v>157</v>
-      </c>
-      <c r="K11" s="5">
-        <v>24</v>
-      </c>
-      <c r="L11" s="5">
-        <v>133</v>
-      </c>
-      <c r="M11" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="25" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="4">
-        <v>0.2890382921100689</v>
-      </c>
-      <c r="C12" s="4">
-        <v>0.1559829286171532</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0.1672934394932305</v>
-      </c>
-      <c r="E12" s="4">
-        <v>81.36789283614689</v>
-      </c>
-      <c r="F12" s="4">
-        <v>86.05426973912373</v>
-      </c>
-      <c r="G12" s="5">
-        <v>1458</v>
-      </c>
-      <c r="H12" s="5">
-        <v>1142</v>
-      </c>
-      <c r="I12" s="5">
-        <v>176</v>
-      </c>
-      <c r="J12" s="5">
-        <v>140</v>
-      </c>
-      <c r="K12" s="5">
-        <v>30</v>
-      </c>
-      <c r="L12" s="5">
-        <v>110</v>
-      </c>
-      <c r="M12" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="25" customHeight="1">
-      <c r="A13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" s="4">
-        <v>0.2010885495357042</v>
-      </c>
-      <c r="C13" s="4">
-        <v>0.1649902378437638</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0.1782918604833364</v>
-      </c>
-      <c r="E13" s="4">
-        <v>83.33857842202309</v>
-      </c>
-      <c r="F13" s="4">
-        <v>88.77716273948208</v>
-      </c>
-      <c r="G13" s="5">
-        <v>1284</v>
-      </c>
-      <c r="H13" s="5">
-        <v>1125</v>
-      </c>
-      <c r="I13" s="5">
-        <v>91</v>
-      </c>
-      <c r="J13" s="5">
-        <v>68</v>
-      </c>
-      <c r="K13" s="5">
-        <v>5</v>
-      </c>
-      <c r="L13" s="5">
-        <v>63</v>
-      </c>
-      <c r="M13" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="25" customHeight="1">
-      <c r="A14" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="B14" s="4">
         <v>0.2478588148818643</v>
@@ -12963,7 +12283,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -12984,13 +12304,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -13021,7 +12341,7 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.5456699015817817</v>
@@ -13062,7 +12382,7 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.909741877465414</v>
@@ -13103,7 +12423,7 @@
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>7.555933886159199</v>
@@ -13144,7 +12464,7 @@
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.2410718263699454</v>
@@ -13185,7 +12505,7 @@
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>1.168155459495127</v>
@@ -13226,7 +12546,7 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.464014917588268</v>
@@ -13267,7 +12587,7 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
         <v>1.306438782848979</v>
@@ -13308,7 +12628,7 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
         <v>1.828459706104764</v>
@@ -13349,7 +12669,7 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
         <v>0.6941850567413145</v>
@@ -13390,7 +12710,7 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
         <v>0.3736594407788086</v>
@@ -13431,7 +12751,7 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
         <v>0.2130600916591527</v>
@@ -13472,7 +12792,7 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>1.483407223212576</v>
@@ -13545,7 +12865,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -13566,13 +12886,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -13603,7 +12923,7 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.3297593906926983</v>
@@ -13644,7 +12964,7 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.4915865126607711</v>
@@ -13685,7 +13005,7 @@
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>4.680589473990097</v>
@@ -13726,7 +13046,7 @@
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.3430928926353332</v>
@@ -13767,7 +13087,7 @@
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>0.413562065831421</v>
@@ -13808,7 +13128,7 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.4091561460393824</v>
@@ -13849,7 +13169,7 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
         <v>0.8165031638698755</v>
@@ -13890,7 +13210,7 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
         <v>0.220084260385705</v>
@@ -13931,7 +13251,7 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
         <v>0.4585768578700469</v>
@@ -13972,7 +13292,7 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
         <v>0.6653143601790936</v>
@@ -14013,7 +13333,7 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
         <v>0.5030248785475541</v>
@@ -14054,7 +13374,7 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>0.4647548352479283</v>
@@ -14127,7 +13447,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -14148,13 +13468,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -14185,7 +13505,7 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.4599372616914481</v>
@@ -14226,7 +13546,7 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.7028616228310324</v>
@@ -14267,7 +13587,7 @@
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>1.095469270611332</v>
@@ -14308,7 +13628,7 @@
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.408321055331489</v>
@@ -14349,7 +13669,7 @@
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>0.5923068673200381</v>
@@ -14390,7 +13710,7 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.4588603111564893</v>
@@ -14431,7 +13751,7 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
         <v>1.108922034163337</v>
@@ -14472,7 +13792,7 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
         <v>0.2682757544186098</v>
@@ -14513,7 +13833,7 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
         <v>0.736267967980843</v>
@@ -14554,7 +13874,7 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
         <v>1.037823918011065</v>
@@ -14595,7 +13915,7 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
         <v>0.8638898654743816</v>
@@ -14636,7 +13956,7 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>0.4086389515310969</v>
@@ -14709,7 +14029,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -14730,13 +14050,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -14767,7 +14087,7 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.2845341964045634</v>
@@ -14808,7 +14128,7 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.3877773201399883</v>
@@ -14849,7 +14169,7 @@
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>3.95027624193769</v>
@@ -14890,7 +14210,7 @@
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.2324234446350305</v>
@@ -14931,7 +14251,7 @@
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>0.3398812719138264</v>
@@ -14972,7 +14292,7 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.3387138065547756</v>
@@ -15013,7 +14333,7 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
         <v>0.6407871855890107</v>
@@ -15054,7 +14374,7 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
         <v>0.315450454387093</v>
@@ -15095,7 +14415,7 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
         <v>0.2870617630046627</v>
@@ -15136,7 +14456,7 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
         <v>0.2991879310621084</v>
@@ -15177,7 +14497,7 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
         <v>0.2407276706421793</v>
@@ -15218,7 +14538,7 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>0.3639600394542515</v>
@@ -15291,7 +14611,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -15312,13 +14632,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -15349,7 +14669,7 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.4266269873662853</v>
@@ -15390,7 +14710,7 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.6891556419191361</v>
@@ -15431,7 +14751,7 @@
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>1.862344029655626</v>
@@ -15472,7 +14792,7 @@
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.3747773793953842</v>
@@ -15513,7 +14833,7 @@
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>0.5070041918295203</v>
@@ -15554,7 +14874,7 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.4407849243452983</v>
@@ -15595,7 +14915,7 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
         <v>0.8289249695858255</v>
@@ -15636,7 +14956,7 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
         <v>0.1853329163962733</v>
@@ -15677,7 +14997,7 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
         <v>0.5322430720304657</v>
@@ -15718,7 +15038,7 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
         <v>0.7990407677208313</v>
@@ -15759,7 +15079,7 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
         <v>0.7336224154694835</v>
@@ -15800,7 +15120,7 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>0.4541836868613861</v>
@@ -15873,7 +15193,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -15894,13 +15214,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -15931,40 +15251,40 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5234137142086968</v>
+        <v>0.5146962606986267</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4676999759521925</v>
+        <v>0.4570008239937774</v>
       </c>
       <c r="D3" s="4">
-        <v>0.463228609639571</v>
+        <v>0.4501028557587347</v>
       </c>
       <c r="E3" s="4">
-        <v>84.68395499312344</v>
+        <v>84.23009931327391</v>
       </c>
       <c r="F3" s="4">
-        <v>90.48283183340072</v>
+        <v>90.14457248054322</v>
       </c>
       <c r="G3" s="5">
-        <v>8107</v>
+        <v>8854</v>
       </c>
       <c r="H3" s="5">
-        <v>7024</v>
+        <v>7580</v>
       </c>
       <c r="I3" s="5">
-        <v>396</v>
+        <v>460</v>
       </c>
       <c r="J3" s="5">
-        <v>687</v>
+        <v>814</v>
       </c>
       <c r="K3" s="5">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="L3" s="5">
-        <v>566</v>
+        <v>685</v>
       </c>
       <c r="M3" s="5">
         <v>33</v>
@@ -15972,40 +15292,40 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>0.574902222146449</v>
+        <v>0.5645511156459136</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4773277164663736</v>
+        <v>0.4633127968324338</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4494007543932508</v>
+        <v>0.4334752800990501</v>
       </c>
       <c r="E4" s="4">
-        <v>84.30181027634934</v>
+        <v>83.77275517958282</v>
       </c>
       <c r="F4" s="4">
-        <v>90.36453965204892</v>
+        <v>89.99773346305534</v>
       </c>
       <c r="G4" s="5">
-        <v>6834</v>
+        <v>7457</v>
       </c>
       <c r="H4" s="5">
-        <v>5992</v>
+        <v>6461</v>
       </c>
       <c r="I4" s="5">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="J4" s="5">
-        <v>720</v>
+        <v>851</v>
       </c>
       <c r="K4" s="5">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="L4" s="5">
-        <v>586</v>
+        <v>702</v>
       </c>
       <c r="M4" s="5">
         <v>14</v>
@@ -16013,81 +15333,81 @@
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>7.879568648263586</v>
+        <v>7.640726333724813</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3575959340429602</v>
+        <v>0.3671766401321506</v>
       </c>
       <c r="D5" s="4">
-        <v>8.507662498657275</v>
+        <v>8.243688365929827</v>
       </c>
       <c r="E5" s="4">
-        <v>80.13878326429216</v>
+        <v>79.92805400081046</v>
       </c>
       <c r="F5" s="4">
-        <v>87.53039651552007</v>
+        <v>87.36670762062376</v>
       </c>
       <c r="G5" s="5">
-        <v>6843</v>
+        <v>7369</v>
       </c>
       <c r="H5" s="5">
-        <v>3915</v>
+        <v>4208</v>
       </c>
       <c r="I5" s="5">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="J5" s="5">
-        <v>2783</v>
+        <v>2997</v>
       </c>
       <c r="K5" s="5">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="L5" s="5">
-        <v>917</v>
+        <v>1006</v>
       </c>
       <c r="M5" s="5">
-        <v>1597</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
-        <v>0.550041312580936</v>
+        <v>0.5576848620467325</v>
       </c>
       <c r="C6" s="4">
-        <v>0.5491689137637019</v>
+        <v>0.5590585122752598</v>
       </c>
       <c r="D6" s="4">
-        <v>0.577157701517745</v>
+        <v>0.5877917553799411</v>
       </c>
       <c r="E6" s="4">
-        <v>84.8256608874553</v>
+        <v>84.29144954609502</v>
       </c>
       <c r="F6" s="4">
-        <v>90.58762868634558</v>
+        <v>90.17855713166146</v>
       </c>
       <c r="G6" s="5">
-        <v>5264</v>
+        <v>5812</v>
       </c>
       <c r="H6" s="5">
-        <v>4651</v>
+        <v>5065</v>
       </c>
       <c r="I6" s="5">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="J6" s="5">
-        <v>439</v>
+        <v>535</v>
       </c>
       <c r="K6" s="5">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="L6" s="5">
-        <v>378</v>
+        <v>466</v>
       </c>
       <c r="M6" s="5">
         <v>6</v>
@@ -16095,40 +15415,40 @@
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
-        <v>0.9810904715316323</v>
+        <v>0.9826773624608929</v>
       </c>
       <c r="C7" s="4">
-        <v>0.9864453960405115</v>
+        <v>0.9934589642246952</v>
       </c>
       <c r="D7" s="4">
-        <v>1.026071450500963</v>
+        <v>1.034581148135367</v>
       </c>
       <c r="E7" s="4">
-        <v>84.26044279221367</v>
+        <v>83.55522855522848</v>
       </c>
       <c r="F7" s="4">
-        <v>89.73665847453263</v>
+        <v>89.18973885416837</v>
       </c>
       <c r="G7" s="5">
-        <v>4809</v>
+        <v>5291</v>
       </c>
       <c r="H7" s="5">
-        <v>4115</v>
+        <v>4458</v>
       </c>
       <c r="I7" s="5">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="J7" s="5">
-        <v>523</v>
+        <v>647</v>
       </c>
       <c r="K7" s="5">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="L7" s="5">
-        <v>374</v>
+        <v>477</v>
       </c>
       <c r="M7" s="5">
         <v>21</v>
@@ -16136,40 +15456,40 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
-        <v>0.3535505302909376</v>
+        <v>0.3559931267042513</v>
       </c>
       <c r="C8" s="4">
-        <v>0.2126781910884002</v>
+        <v>0.2135792998056631</v>
       </c>
       <c r="D8" s="4">
-        <v>0.2347477238575547</v>
+        <v>0.2372221232083967</v>
       </c>
       <c r="E8" s="4">
-        <v>76.75698670996729</v>
+        <v>76.13853337945353</v>
       </c>
       <c r="F8" s="4">
-        <v>81.0313621689596</v>
+        <v>80.59147613089134</v>
       </c>
       <c r="G8" s="5">
-        <v>1747</v>
+        <v>1770</v>
       </c>
       <c r="H8" s="5">
-        <v>1220</v>
+        <v>1225</v>
       </c>
       <c r="I8" s="5">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J8" s="5">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="K8" s="5">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L8" s="5">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
@@ -16177,40 +15497,40 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
-        <v>0.9337424252370758</v>
+        <v>0.961008754452648</v>
       </c>
       <c r="C9" s="4">
-        <v>0.7822867806149272</v>
+        <v>0.7829349668894003</v>
       </c>
       <c r="D9" s="4">
-        <v>0.759606222618005</v>
+        <v>0.753560592971384</v>
       </c>
       <c r="E9" s="4">
-        <v>86.44291537074112</v>
+        <v>81.55801088086081</v>
       </c>
       <c r="F9" s="4">
-        <v>90.69436076588885</v>
+        <v>87.48556199797244</v>
       </c>
       <c r="G9" s="5">
-        <v>1437</v>
+        <v>1558</v>
       </c>
       <c r="H9" s="5">
-        <v>1250</v>
+        <v>1272</v>
       </c>
       <c r="I9" s="5">
         <v>89</v>
       </c>
       <c r="J9" s="5">
-        <v>98</v>
+        <v>197</v>
       </c>
       <c r="K9" s="5">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="L9" s="5">
-        <v>50</v>
+        <v>138</v>
       </c>
       <c r="M9" s="5">
         <v>5</v>
@@ -16218,40 +15538,40 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
-        <v>2.297448281989426</v>
+        <v>2.267713174800695</v>
       </c>
       <c r="C10" s="4">
-        <v>0.2012873295861529</v>
+        <v>0.2010978898027275</v>
       </c>
       <c r="D10" s="4">
-        <v>2.861654809590476</v>
+        <v>2.820098214449567</v>
       </c>
       <c r="E10" s="4">
-        <v>74.79882609107257</v>
+        <v>74.21999308197849</v>
       </c>
       <c r="F10" s="4">
-        <v>80.60339677075527</v>
+        <v>80.32759319700523</v>
       </c>
       <c r="G10" s="5">
-        <v>1509</v>
+        <v>1534</v>
       </c>
       <c r="H10" s="5">
-        <v>786</v>
+        <v>799</v>
       </c>
       <c r="I10" s="5">
         <v>320</v>
       </c>
       <c r="J10" s="5">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="K10" s="5">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L10" s="5">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="M10" s="5">
         <v>228</v>
@@ -16259,40 +15579,40 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
-        <v>0.6432105981387288</v>
+        <v>0.6367271523781378</v>
       </c>
       <c r="C11" s="4">
-        <v>0.6256144667513808</v>
+        <v>0.6259505559228266</v>
       </c>
       <c r="D11" s="4">
-        <v>0.6489440882228071</v>
+        <v>0.6532460640301061</v>
       </c>
       <c r="E11" s="4">
-        <v>87.85575999301292</v>
+        <v>83.44561431999848</v>
       </c>
       <c r="F11" s="4">
-        <v>92.22971657619173</v>
+        <v>89.22421210664614</v>
       </c>
       <c r="G11" s="5">
-        <v>1402</v>
+        <v>1508</v>
       </c>
       <c r="H11" s="5">
-        <v>1262</v>
+        <v>1280</v>
       </c>
       <c r="I11" s="5">
         <v>64</v>
       </c>
       <c r="J11" s="5">
-        <v>76</v>
+        <v>164</v>
       </c>
       <c r="K11" s="5">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="L11" s="5">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
@@ -16300,40 +15620,40 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
-        <v>0.3677749864278556</v>
+        <v>0.3762840351893083</v>
       </c>
       <c r="C12" s="4">
-        <v>0.3443413957338091</v>
+        <v>0.3440234414843364</v>
       </c>
       <c r="D12" s="4">
-        <v>0.3713457996549965</v>
+        <v>0.3742710385329218</v>
       </c>
       <c r="E12" s="4">
-        <v>81.60784596524114</v>
+        <v>79.98436960518089</v>
       </c>
       <c r="F12" s="4">
-        <v>86.35954656484901</v>
+        <v>85.22781046022438</v>
       </c>
       <c r="G12" s="5">
-        <v>1415</v>
+        <v>1458</v>
       </c>
       <c r="H12" s="5">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="I12" s="5">
         <v>215</v>
       </c>
       <c r="J12" s="5">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="K12" s="5">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L12" s="5">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="M12" s="5">
         <v>0</v>
@@ -16341,40 +15661,40 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
-        <v>0.1595681118716065</v>
+        <v>0.1739369348634342</v>
       </c>
       <c r="C13" s="4">
-        <v>0.1415958169670919</v>
+        <v>0.1418649578846773</v>
       </c>
       <c r="D13" s="4">
-        <v>0.1538648508159032</v>
+        <v>0.1556391903155472</v>
       </c>
       <c r="E13" s="4">
-        <v>84.42446690214553</v>
+        <v>82.7668107741539</v>
       </c>
       <c r="F13" s="4">
-        <v>89.59467138472961</v>
+        <v>88.49531664889551</v>
       </c>
       <c r="G13" s="5">
-        <v>1248</v>
+        <v>1284</v>
       </c>
       <c r="H13" s="5">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="I13" s="5">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J13" s="5">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="K13" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L13" s="5">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="M13" s="5">
         <v>0</v>
@@ -16382,7 +15702,7 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>0.5635003243524863</v>
@@ -16455,7 +15775,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -16476,13 +15796,13 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -16513,7 +15833,7 @@
     </row>
     <row r="3" spans="1:13" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.2503890395677964</v>
@@ -16554,7 +15874,7 @@
     </row>
     <row r="4" spans="1:13" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.3606323594169972</v>
@@ -16595,7 +15915,7 @@
     </row>
     <row r="5" spans="1:13" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>4.14499929519538</v>
@@ -16636,7 +15956,7 @@
     </row>
     <row r="6" spans="1:13" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.2162333507237473</v>
@@ -16677,7 +15997,7 @@
     </row>
     <row r="7" spans="1:13" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>0.3241650045963963</v>
@@ -16718,7 +16038,7 @@
     </row>
     <row r="8" spans="1:13" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.3617780818539864</v>
@@ -16759,7 +16079,7 @@
     </row>
     <row r="9" spans="1:13" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
         <v>0.5579190021878485</v>
@@ -16800,7 +16120,7 @@
     </row>
     <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
         <v>0.6622303418708158</v>
@@ -16841,7 +16161,7 @@
     </row>
     <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
         <v>0.2562105367471211</v>
@@ -16882,7 +16202,7 @@
     </row>
     <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
         <v>0.3163090684370721</v>
@@ -16923,7 +16243,7 @@
     </row>
     <row r="13" spans="1:13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
         <v>0.1470224995124127</v>
@@ -16964,7 +16284,7 @@
     </row>
     <row r="14" spans="1:13" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>0.3957310803266271</v>

--- a/public/downloads/MamunHighT2019.xlsx
+++ b/public/downloads/MamunHighT2019.xlsx
@@ -2016,22 +2016,22 @@
         <v>33</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4622208123901648</v>
+        <v>-0.4097580805328391</v>
       </c>
       <c r="O3" s="5">
         <v>7613</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1993107551526461</v>
+        <v>0.1946063528927138</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.15597520394435</v>
+        <v>0.1453359670673336</v>
       </c>
       <c r="R3" s="5">
-        <v>7594</v>
+        <v>7593</v>
       </c>
       <c r="S3" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -2075,22 +2075,22 @@
         <v>14</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4406415218486747</v>
+        <v>-0.4087055563813919</v>
       </c>
       <c r="O4" s="5">
         <v>6475</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2964500132326778</v>
+        <v>0.2968704821080106</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2035114840041928</v>
+        <v>0.2019365796607396</v>
       </c>
       <c r="R4" s="5">
-        <v>6458</v>
+        <v>6460</v>
       </c>
       <c r="S4" s="5">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -2134,22 +2134,22 @@
         <v>1704</v>
       </c>
       <c r="N5" s="4">
-        <v>6.096634171088166</v>
+        <v>0.4451997582238505</v>
       </c>
       <c r="O5" s="5">
         <v>5912</v>
       </c>
       <c r="P5" s="4">
-        <v>9.124538969662293</v>
+        <v>7.405096202913802</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.8224417681894021</v>
+        <v>0.2046466620498632</v>
       </c>
       <c r="R5" s="5">
-        <v>302</v>
+        <v>4209</v>
       </c>
       <c r="S5" s="5">
-        <v>5610</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -2193,16 +2193,16 @@
         <v>6</v>
       </c>
       <c r="N6" s="4">
-        <v>0.551745826324369</v>
+        <v>0.5498916808646186</v>
       </c>
       <c r="O6" s="5">
         <v>5071</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1909959458862936</v>
+        <v>0.1908500422077216</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1327864545286027</v>
+        <v>0.1327810514694004</v>
       </c>
       <c r="R6" s="5">
         <v>5068</v>
@@ -2252,16 +2252,16 @@
         <v>21</v>
       </c>
       <c r="N7" s="4">
-        <v>0.9990490152460195</v>
+        <v>0.9960832466922511</v>
       </c>
       <c r="O7" s="5">
         <v>4479</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2611906501439424</v>
+        <v>0.2608837269397416</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.14077552031239</v>
+        <v>0.1407590501280885</v>
       </c>
       <c r="R7" s="5">
         <v>4479</v>
@@ -2311,16 +2311,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.1799592409212113</v>
+        <v>0.1835989389900305</v>
       </c>
       <c r="O8" s="5">
         <v>1225</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3313357116823465</v>
+        <v>0.3322248251405457</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1222222317546137</v>
+        <v>0.1222009114151837</v>
       </c>
       <c r="R8" s="5">
         <v>1225</v>
@@ -2370,16 +2370,16 @@
         <v>5</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.7887069615622395</v>
+        <v>-0.7887147631327025</v>
       </c>
       <c r="O9" s="5">
         <v>1277</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2745104524507528</v>
+        <v>0.2745093508169262</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1145320390478994</v>
+        <v>0.1145320329386038</v>
       </c>
       <c r="R9" s="5">
         <v>1277</v>
@@ -2429,22 +2429,22 @@
         <v>228</v>
       </c>
       <c r="N10" s="4">
-        <v>1.499640064102606</v>
+        <v>-0.1515866373537165</v>
       </c>
       <c r="O10" s="5">
         <v>1027</v>
       </c>
       <c r="P10" s="4">
-        <v>2.984604993887927</v>
+        <v>2.203848833055868</v>
       </c>
       <c r="Q10" s="4">
-        <v>1.633500171103074</v>
+        <v>0.06640902215401912</v>
       </c>
       <c r="R10" s="5">
-        <v>860</v>
+        <v>798</v>
       </c>
       <c r="S10" s="5">
-        <v>167</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="25" customHeight="1">
@@ -2488,16 +2488,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.6233314030310725</v>
+        <v>0.6220781076535502</v>
       </c>
       <c r="O11" s="5">
         <v>1280</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2217629793899031</v>
+        <v>0.2216152793217567</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1039806119472422</v>
+        <v>0.1039774390484625</v>
       </c>
       <c r="R11" s="5">
         <v>1280</v>
@@ -2547,16 +2547,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.3298445465619954</v>
+        <v>0.3338701756337628</v>
       </c>
       <c r="O12" s="5">
         <v>1113</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2437928767560633</v>
+        <v>0.2445795276122868</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1039752611608078</v>
+        <v>0.1039459957792678</v>
       </c>
       <c r="R12" s="5">
         <v>1113</v>
@@ -2606,16 +2606,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.08268700468435312</v>
+        <v>0.1183821638368556</v>
       </c>
       <c r="O13" s="5">
         <v>1105</v>
       </c>
       <c r="P13" s="4">
-        <v>0.150537373813594</v>
+        <v>0.1511574888927003</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1063893640171226</v>
+        <v>0.102851896295479</v>
       </c>
       <c r="R13" s="5">
         <v>1105</v>
@@ -2665,16 +2665,16 @@
         <v>8</v>
       </c>
       <c r="N14" s="4">
-        <v>0.3061075013458369</v>
+        <v>0.04706831680516643</v>
       </c>
       <c r="O14" s="5">
         <v>991</v>
       </c>
       <c r="P14" s="4">
-        <v>0.7465944975540562</v>
+        <v>0.5601352816904849</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.2652698924536461</v>
+        <v>0.07601481681513085</v>
       </c>
       <c r="R14" s="5">
         <v>983</v>
@@ -2847,16 +2847,16 @@
         <v>20</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1785589994603581</v>
+        <v>-0.1644257663092787</v>
       </c>
       <c r="O3" s="5">
         <v>7544</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1613224428491902</v>
+        <v>0.1620193915279653</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1099589775095757</v>
+        <v>0.1091612464656232</v>
       </c>
       <c r="R3" s="5">
         <v>7527</v>
@@ -2906,16 +2906,16 @@
         <v>12</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1610806885948118</v>
+        <v>-0.1684220360775726</v>
       </c>
       <c r="O4" s="5">
         <v>6294</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3042134950902775</v>
+        <v>0.3035312441821231</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1995410669103583</v>
+        <v>0.1994490794131958</v>
       </c>
       <c r="R4" s="5">
         <v>6279</v>
@@ -2965,22 +2965,22 @@
         <v>1155</v>
       </c>
       <c r="N5" s="4">
-        <v>2.44974540737678</v>
+        <v>0.1566981504076352</v>
       </c>
       <c r="O5" s="5">
         <v>5431</v>
       </c>
       <c r="P5" s="4">
-        <v>4.814959771759785</v>
+        <v>4.097736044830594</v>
       </c>
       <c r="Q5" s="4">
-        <v>1.267614213472746</v>
+        <v>0.2058629037364675</v>
       </c>
       <c r="R5" s="5">
-        <v>395</v>
+        <v>4287</v>
       </c>
       <c r="S5" s="5">
-        <v>5036</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -3024,16 +3024,16 @@
         <v>3</v>
       </c>
       <c r="N6" s="4">
-        <v>0.04021139185188471</v>
+        <v>0.03422550528915735</v>
       </c>
       <c r="O6" s="5">
         <v>4945</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2176269234104922</v>
+        <v>0.2170495895419493</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1487804998862695</v>
+        <v>0.1487121654784616</v>
       </c>
       <c r="R6" s="5">
         <v>4942</v>
@@ -3083,22 +3083,22 @@
         <v>2</v>
       </c>
       <c r="N7" s="4">
-        <v>0.1755921682648792</v>
+        <v>0.1611044833853157</v>
       </c>
       <c r="O7" s="5">
         <v>4334</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2941795902860937</v>
+        <v>0.2920846285376197</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1538470337378014</v>
+        <v>0.1529520342037315</v>
       </c>
       <c r="R7" s="5">
-        <v>4334</v>
+        <v>4333</v>
       </c>
       <c r="S7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="25" customHeight="1">
@@ -3142,16 +3142,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.0702623304331163</v>
+        <v>-0.06415077497615584</v>
       </c>
       <c r="O8" s="5">
         <v>1203</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3366475195393827</v>
+        <v>0.3381585786714503</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1258785189961434</v>
+        <v>0.1258229526687815</v>
       </c>
       <c r="R8" s="5">
         <v>1203</v>
@@ -3201,16 +3201,16 @@
         <v>1</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.3660194908690217</v>
+        <v>-0.3764033914694664</v>
       </c>
       <c r="O9" s="5">
         <v>1275</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2914305738543569</v>
+        <v>0.2895748223732172</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1145533576175384</v>
+        <v>0.1140855781862307</v>
       </c>
       <c r="R9" s="5">
         <v>1275</v>
@@ -3260,22 +3260,22 @@
         <v>94</v>
       </c>
       <c r="N10" s="4">
-        <v>0.4641452131673969</v>
+        <v>0.06493072336536443</v>
       </c>
       <c r="O10" s="5">
         <v>936</v>
       </c>
       <c r="P10" s="4">
-        <v>0.9333539545428702</v>
+        <v>0.6571909729076724</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.4562063210421977</v>
+        <v>0.08261522050620249</v>
       </c>
       <c r="R10" s="5">
-        <v>850</v>
+        <v>843</v>
       </c>
       <c r="S10" s="5">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="25" customHeight="1">
@@ -3319,16 +3319,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.0183625911841727</v>
+        <v>-0.03536568711390942</v>
       </c>
       <c r="O11" s="5">
         <v>1252</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2512600924657378</v>
+        <v>0.2483373189100583</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1160813457594616</v>
+        <v>0.1152995340663285</v>
       </c>
       <c r="R11" s="5">
         <v>1252</v>
@@ -3378,16 +3378,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.08013496859007026</v>
+        <v>-0.07103239588383303</v>
       </c>
       <c r="O12" s="5">
         <v>1027</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2862714333339071</v>
+        <v>0.2884682074352791</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1159082920658107</v>
+        <v>0.1157247556325462</v>
       </c>
       <c r="R12" s="5">
         <v>1027</v>
@@ -3437,16 +3437,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.05441604421197038</v>
+        <v>-0.02917228155283169</v>
       </c>
       <c r="O13" s="5">
         <v>1121</v>
       </c>
       <c r="P13" s="4">
-        <v>0.1415763717966011</v>
+        <v>0.1412626201652421</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.09673381370701094</v>
+        <v>0.09383175842499526</v>
       </c>
       <c r="R13" s="5">
         <v>1121</v>
@@ -3496,16 +3496,16 @@
         <v>4</v>
       </c>
       <c r="N14" s="4">
-        <v>0.05848601027172353</v>
+        <v>-0.006775970040393986</v>
       </c>
       <c r="O14" s="5">
         <v>979</v>
       </c>
       <c r="P14" s="4">
-        <v>0.4190895414852081</v>
+        <v>0.3945985591641696</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.09978321456600998</v>
+        <v>0.07978611941520192</v>
       </c>
       <c r="R14" s="5">
         <v>975</v>
@@ -3678,16 +3678,16 @@
         <v>20</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1669050550434823</v>
+        <v>-0.1584397987630091</v>
       </c>
       <c r="O3" s="5">
         <v>7679</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1862178001157763</v>
+        <v>0.1868891150314555</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1407548034164317</v>
+        <v>0.1405542370424456</v>
       </c>
       <c r="R3" s="5">
         <v>7661</v>
@@ -3737,22 +3737,22 @@
         <v>10</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.07496011680843591</v>
+        <v>-0.1154404674623466</v>
       </c>
       <c r="O4" s="5">
         <v>6376</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3888571689905231</v>
+        <v>0.3835545056932194</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.285142941935269</v>
+        <v>0.2825140520674344</v>
       </c>
       <c r="R4" s="5">
-        <v>6365</v>
+        <v>6363</v>
       </c>
       <c r="S4" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -3796,22 +3796,22 @@
         <v>909</v>
       </c>
       <c r="N5" s="4">
-        <v>1.229344830218929</v>
+        <v>0.3087813308914455</v>
       </c>
       <c r="O5" s="5">
         <v>5328</v>
       </c>
       <c r="P5" s="4">
-        <v>2.742164483421686</v>
+        <v>2.560323300308345</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.9868685656717056</v>
+        <v>0.2934772355058031</v>
       </c>
       <c r="R5" s="5">
-        <v>4592</v>
+        <v>4463</v>
       </c>
       <c r="S5" s="5">
-        <v>736</v>
+        <v>865</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -3855,16 +3855,16 @@
         <v>3</v>
       </c>
       <c r="N6" s="4">
-        <v>0.2261580950117152</v>
+        <v>0.2200363294676784</v>
       </c>
       <c r="O6" s="5">
         <v>5064</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2500646407369806</v>
+        <v>0.249424879727937</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1768706470755535</v>
+        <v>0.1768048738447618</v>
       </c>
       <c r="R6" s="5">
         <v>5061</v>
@@ -3914,16 +3914,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.3376668657655307</v>
+        <v>-0.3602831188049755</v>
       </c>
       <c r="O7" s="5">
         <v>4590</v>
       </c>
       <c r="P7" s="4">
-        <v>0.3174356373344652</v>
+        <v>0.3150897322315537</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2207271086801677</v>
+        <v>0.2200331184330288</v>
       </c>
       <c r="R7" s="5">
         <v>4590</v>
@@ -3973,16 +3973,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.01527742638920702</v>
+        <v>0.0007704505475487622</v>
       </c>
       <c r="O8" s="5">
         <v>1259</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3584123080321111</v>
+        <v>0.3620089874278327</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.17595851451799</v>
+        <v>0.1755584702609696</v>
       </c>
       <c r="R8" s="5">
         <v>1259</v>
@@ -4032,16 +4032,16 @@
         <v>3</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.4204380493548791</v>
+        <v>-0.4305608140603141</v>
       </c>
       <c r="O9" s="5">
         <v>1308</v>
       </c>
       <c r="P9" s="4">
-        <v>0.3612075070484828</v>
+        <v>0.359690878561705</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1846837019481245</v>
+        <v>0.1844727013197621</v>
       </c>
       <c r="R9" s="5">
         <v>1308</v>
@@ -4091,16 +4091,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.005917525462550454</v>
+        <v>0.007935172154326153</v>
       </c>
       <c r="O10" s="5">
         <v>863</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1284748131986841</v>
+        <v>0.1284029348059701</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.06020408609831164</v>
+        <v>0.06017493248076854</v>
       </c>
       <c r="R10" s="5">
         <v>863</v>
@@ -4150,16 +4150,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.5356190028791811</v>
+        <v>-0.536729241954184</v>
       </c>
       <c r="O11" s="5">
         <v>1304</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2761335781995997</v>
+        <v>0.2760274698768847</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.15375303152767</v>
+        <v>0.1537512237040474</v>
       </c>
       <c r="R11" s="5">
         <v>1304</v>
@@ -4209,16 +4209,16 @@
         <v>2</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.5948856177191342</v>
+        <v>-0.5887049464892371</v>
       </c>
       <c r="O12" s="5">
         <v>1151</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2450510247455145</v>
+        <v>0.2461419799144834</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1268819847816809</v>
+        <v>0.1267764823539441</v>
       </c>
       <c r="R12" s="5">
         <v>1151</v>
@@ -4268,16 +4268,16 @@
         <v>2</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.5665078519844994</v>
+        <v>-0.5466266589470408</v>
       </c>
       <c r="O13" s="5">
         <v>1023</v>
       </c>
       <c r="P13" s="4">
-        <v>0.1768106745840601</v>
+        <v>0.1788109350776673</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1281019071926599</v>
+        <v>0.1266592257619373</v>
       </c>
       <c r="R13" s="5">
         <v>1023</v>
@@ -4327,16 +4327,16 @@
         <v>1</v>
       </c>
       <c r="N14" s="4">
-        <v>0.001123527023172224</v>
+        <v>-0.008177762634872465</v>
       </c>
       <c r="O14" s="5">
         <v>947</v>
       </c>
       <c r="P14" s="4">
-        <v>0.357088939233671</v>
+        <v>0.3553670647563296</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1267951868478434</v>
+        <v>0.1265229369200603</v>
       </c>
       <c r="R14" s="5">
         <v>946</v>
@@ -4509,16 +4509,16 @@
         <v>5</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.02603109066396008</v>
+        <v>-0.03161963813136337</v>
       </c>
       <c r="O3" s="5">
         <v>7633</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2097635104649592</v>
+        <v>0.2090946183802844</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1213380026144763</v>
+        <v>0.1212395201691608</v>
       </c>
       <c r="R3" s="5">
         <v>7628</v>
@@ -4568,16 +4568,16 @@
         <v>19</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.004378295029471579</v>
+        <v>-0.01871423552754692</v>
       </c>
       <c r="O4" s="5">
         <v>6335</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3696933371939217</v>
+        <v>0.3680437839155666</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2438449593860895</v>
+        <v>0.2435626849405773</v>
       </c>
       <c r="R4" s="5">
         <v>6316</v>
@@ -4627,22 +4627,22 @@
         <v>134</v>
       </c>
       <c r="N5" s="4">
-        <v>0.5444619620516855</v>
+        <v>0.4437855688660477</v>
       </c>
       <c r="O5" s="5">
         <v>6377</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4690558069495077</v>
+        <v>0.4529784514660373</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3705659325099964</v>
+        <v>0.3584410701448816</v>
       </c>
       <c r="R5" s="5">
-        <v>6343</v>
+        <v>6335</v>
       </c>
       <c r="S5" s="5">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -4686,16 +4686,16 @@
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>0.3090799667025766</v>
+        <v>0.3159936047009029</v>
       </c>
       <c r="O6" s="5">
         <v>4956</v>
       </c>
       <c r="P6" s="4">
-        <v>0.220338678800396</v>
+        <v>0.22098557331468</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1269075977020174</v>
+        <v>0.1267798988218084</v>
       </c>
       <c r="R6" s="5">
         <v>4954</v>
@@ -4745,16 +4745,16 @@
         <v>3</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.1017838988938198</v>
+        <v>-0.09542131383447838</v>
       </c>
       <c r="O7" s="5">
         <v>4448</v>
       </c>
       <c r="P7" s="4">
-        <v>0.3194790179411989</v>
+        <v>0.3200779727347429</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1875188165524414</v>
+        <v>0.1874426785908635</v>
       </c>
       <c r="R7" s="5">
         <v>4445</v>
@@ -4804,16 +4804,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.182940411903403</v>
+        <v>0.2028101948824137</v>
       </c>
       <c r="O8" s="5">
         <v>1348</v>
       </c>
       <c r="P8" s="4">
-        <v>0.273268370477918</v>
+        <v>0.2765947073891138</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.11955202092705</v>
+        <v>0.1182900766100679</v>
       </c>
       <c r="R8" s="5">
         <v>1348</v>
@@ -4863,16 +4863,16 @@
         <v>3</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.1288310994430225</v>
+        <v>-0.1139175151023935</v>
       </c>
       <c r="O9" s="5">
         <v>1327</v>
       </c>
       <c r="P9" s="4">
-        <v>0.3260442989099794</v>
+        <v>0.327571364678941</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1798612341791823</v>
+        <v>0.1793107912373826</v>
       </c>
       <c r="R9" s="5">
         <v>1324</v>
@@ -4922,16 +4922,16 @@
         <v>1</v>
       </c>
       <c r="N10" s="4">
-        <v>0.09656379862649934</v>
+        <v>0.1068773953846573</v>
       </c>
       <c r="O10" s="5">
         <v>1203</v>
       </c>
       <c r="P10" s="4">
-        <v>0.08822071124967119</v>
+        <v>0.0876861569090565</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.05470383626276572</v>
+        <v>0.05369223658168283</v>
       </c>
       <c r="R10" s="5">
         <v>1201</v>
@@ -4981,16 +4981,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.173167599422015</v>
+        <v>-0.1630377728597097</v>
       </c>
       <c r="O11" s="5">
         <v>1325</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2776124217576355</v>
+        <v>0.2784011712152775</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1911033432727826</v>
+        <v>0.1909146580789618</v>
       </c>
       <c r="R11" s="5">
         <v>1325</v>
@@ -5040,16 +5040,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.1096729010214559</v>
+        <v>-0.08554270062908387</v>
       </c>
       <c r="O12" s="5">
         <v>1217</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2378056141121175</v>
+        <v>0.2395967849478725</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1539740006566056</v>
+        <v>0.1525993054139613</v>
       </c>
       <c r="R12" s="5">
         <v>1217</v>
@@ -5099,16 +5099,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.03992959732831897</v>
+        <v>0.0574392346593271</v>
       </c>
       <c r="O13" s="5">
         <v>1101</v>
       </c>
       <c r="P13" s="4">
-        <v>0.1490744241765478</v>
+        <v>0.1496030644959501</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1155973508948887</v>
+        <v>0.1143732208899414</v>
       </c>
       <c r="R13" s="5">
         <v>1101</v>
@@ -5158,16 +5158,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.1555910292092137</v>
+        <v>0.16624585863363</v>
       </c>
       <c r="O14" s="5">
         <v>1081</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1932159674551839</v>
+        <v>0.1938651997048923</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1075389672405004</v>
+        <v>0.1069993502221987</v>
       </c>
       <c r="R14" s="5">
         <v>1081</v>
@@ -5340,22 +5340,22 @@
         <v>18</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1326102389335139</v>
+        <v>-0.1242207839982115</v>
       </c>
       <c r="O3" s="5">
         <v>7821</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1703010214239594</v>
+        <v>0.1708575207777638</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1307603101651744</v>
+        <v>0.1302870195016559</v>
       </c>
       <c r="R3" s="5">
-        <v>7806</v>
+        <v>7805</v>
       </c>
       <c r="S3" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -5399,16 +5399,16 @@
         <v>11</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1165623784221319</v>
+        <v>-0.1170199070305955</v>
       </c>
       <c r="O4" s="5">
         <v>6610</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2957927950682771</v>
+        <v>0.2957552019514823</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2094422907851555</v>
+        <v>0.2094414523941742</v>
       </c>
       <c r="R4" s="5">
         <v>6599</v>
@@ -5458,22 +5458,22 @@
         <v>927</v>
       </c>
       <c r="N5" s="4">
-        <v>1.221293984441355</v>
+        <v>0.2645672384664692</v>
       </c>
       <c r="O5" s="5">
         <v>5329</v>
       </c>
       <c r="P5" s="4">
-        <v>2.618922850774733</v>
+        <v>2.414167491789767</v>
       </c>
       <c r="Q5" s="4">
-        <v>1.001520785036205</v>
+        <v>0.2203419387383507</v>
       </c>
       <c r="R5" s="5">
-        <v>4624</v>
+        <v>4456</v>
       </c>
       <c r="S5" s="5">
-        <v>705</v>
+        <v>873</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -5517,16 +5517,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>0.1768315989791636</v>
+        <v>0.1751959378074801</v>
       </c>
       <c r="O6" s="5">
         <v>5121</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2098404754250651</v>
+        <v>0.2096946511714872</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.145981977008981</v>
+        <v>0.1459774523252634</v>
       </c>
       <c r="R6" s="5">
         <v>5118</v>
@@ -5576,16 +5576,16 @@
         <v>1</v>
       </c>
       <c r="N7" s="4">
-        <v>0.1179612150163215</v>
+        <v>0.1197707348221648</v>
       </c>
       <c r="O7" s="5">
         <v>4612</v>
       </c>
       <c r="P7" s="4">
-        <v>0.290871987565441</v>
+        <v>0.2910421441327787</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1810568272870925</v>
+        <v>0.1810511504831871</v>
       </c>
       <c r="R7" s="5">
         <v>4611</v>
@@ -5635,16 +5635,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.01132251291304686</v>
+        <v>0.03208648305334094</v>
       </c>
       <c r="O8" s="5">
         <v>1342</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2913304765808972</v>
+        <v>0.2948468935071415</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1311909500529561</v>
+        <v>0.130033082547038</v>
       </c>
       <c r="R8" s="5">
         <v>1342</v>
@@ -5694,16 +5694,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.3162420770612819</v>
+        <v>-0.3097302899349614</v>
       </c>
       <c r="O9" s="5">
         <v>1359</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2592186011568395</v>
+        <v>0.2597953416336001</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1405368356586196</v>
+        <v>0.1404239755829391</v>
       </c>
       <c r="R9" s="5">
         <v>1359</v>
@@ -5753,16 +5753,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.03206885043066009</v>
+        <v>0.04055299491397335</v>
       </c>
       <c r="O10" s="5">
         <v>994</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1011510530619258</v>
+        <v>0.1000521386813614</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.03773584321777262</v>
+        <v>0.03700021732795833</v>
       </c>
       <c r="R10" s="5">
         <v>994</v>
@@ -5812,16 +5812,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.0673720613301471</v>
+        <v>-0.08580200196398202</v>
       </c>
       <c r="O11" s="5">
         <v>1338</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2110326205994749</v>
+        <v>0.2091001150496019</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1368468757833123</v>
+        <v>0.1361607416289593</v>
       </c>
       <c r="R11" s="5">
         <v>1338</v>
@@ -5871,16 +5871,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.1065679019444717</v>
+        <v>-0.09836364832222699</v>
       </c>
       <c r="O12" s="5">
         <v>1234</v>
       </c>
       <c r="P12" s="4">
-        <v>0.192603208587518</v>
+        <v>0.1933973363175558</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1138443658276804</v>
+        <v>0.1135721056152771</v>
       </c>
       <c r="R12" s="5">
         <v>1234</v>
@@ -5930,16 +5930,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.07009051410631992</v>
+        <v>-0.04833764779776573</v>
       </c>
       <c r="O13" s="5">
         <v>1118</v>
       </c>
       <c r="P13" s="4">
-        <v>0.1410629294087146</v>
+        <v>0.1414304407445615</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.101085741374727</v>
+        <v>0.09899615500317302</v>
       </c>
       <c r="R13" s="5">
         <v>1118</v>
@@ -5989,16 +5989,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.03083697536333073</v>
+        <v>0.04254585512090614</v>
       </c>
       <c r="O14" s="5">
         <v>1048</v>
       </c>
       <c r="P14" s="4">
-        <v>0.2452657168637839</v>
+        <v>0.2456479349135655</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.09235416137941627</v>
+        <v>0.09169849362701185</v>
       </c>
       <c r="R14" s="5">
         <v>1048</v>
@@ -6171,16 +6171,16 @@
         <v>21</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2150462114519885</v>
+        <v>-0.2150968763173182</v>
       </c>
       <c r="O3" s="5">
         <v>7559</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2319520541493658</v>
+        <v>0.2319472588978246</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1833312209953759</v>
+        <v>0.1833313016077313</v>
       </c>
       <c r="R3" s="5">
         <v>7542</v>
@@ -6230,16 +6230,16 @@
         <v>13</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1339904620892965</v>
+        <v>-0.1572813785232015</v>
       </c>
       <c r="O4" s="5">
         <v>6343</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4662670294119076</v>
+        <v>0.4635808491139616</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3441483812073579</v>
+        <v>0.3434512440856889</v>
       </c>
       <c r="R4" s="5">
         <v>6328</v>
@@ -6289,22 +6289,22 @@
         <v>1260</v>
       </c>
       <c r="N5" s="4">
-        <v>1.43746030397498</v>
+        <v>0.3225746221723966</v>
       </c>
       <c r="O5" s="5">
         <v>5793</v>
       </c>
       <c r="P5" s="4">
-        <v>2.165244767921574</v>
+        <v>1.892118808200771</v>
       </c>
       <c r="Q5" s="4">
-        <v>1.188610841349206</v>
+        <v>0.4311811237134012</v>
       </c>
       <c r="R5" s="5">
-        <v>4705</v>
+        <v>4619</v>
       </c>
       <c r="S5" s="5">
-        <v>1088</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -6348,16 +6348,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>0.1402247446207671</v>
+        <v>0.1121704615626307</v>
       </c>
       <c r="O6" s="5">
         <v>4940</v>
       </c>
       <c r="P6" s="4">
-        <v>0.300620698976401</v>
+        <v>0.2971846741074556</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2297970316407172</v>
+        <v>0.2286203947720204</v>
       </c>
       <c r="R6" s="5">
         <v>4938</v>
@@ -6407,16 +6407,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.2854690679851228</v>
+        <v>-0.3025761981273671</v>
       </c>
       <c r="O7" s="5">
         <v>4364</v>
       </c>
       <c r="P7" s="4">
-        <v>0.3925231044035443</v>
+        <v>0.390515199292334</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2658963669370668</v>
+        <v>0.2655384861129094</v>
       </c>
       <c r="R7" s="5">
         <v>4363</v>
@@ -6466,16 +6466,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.2611248404131076</v>
+        <v>-0.1915946271199545</v>
       </c>
       <c r="O8" s="5">
         <v>1174</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3978092114930386</v>
+        <v>0.4114425284897927</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2409397636702064</v>
+        <v>0.2340530153989311</v>
       </c>
       <c r="R8" s="5">
         <v>1174</v>
@@ -6525,16 +6525,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.5616627707155587</v>
+        <v>-0.5688751708826327</v>
       </c>
       <c r="O9" s="5">
         <v>1311</v>
       </c>
       <c r="P9" s="4">
-        <v>0.3613354933886227</v>
+        <v>0.3603706133004291</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.199283883179757</v>
+        <v>0.1991493781823035</v>
       </c>
       <c r="R9" s="5">
         <v>1310</v>
@@ -6584,16 +6584,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.1851314767331362</v>
+        <v>-0.1753321174780567</v>
       </c>
       <c r="O10" s="5">
         <v>495</v>
       </c>
       <c r="P10" s="4">
-        <v>0.2097283776280112</v>
+        <v>0.2115844902766055</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1506058214477631</v>
+        <v>0.1504322261529378</v>
       </c>
       <c r="R10" s="5">
         <v>495</v>
@@ -6643,16 +6643,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.6886378051200778</v>
+        <v>-0.7097736709216065</v>
       </c>
       <c r="O11" s="5">
         <v>1283</v>
       </c>
       <c r="P11" s="4">
-        <v>0.3463774983186679</v>
+        <v>0.3434749167637472</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.2069296262743188</v>
+        <v>0.2060809718969063</v>
       </c>
       <c r="R11" s="5">
         <v>1283</v>
@@ -6702,16 +6702,16 @@
         <v>2</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.7744444949364974</v>
+        <v>-0.7854662619257553</v>
       </c>
       <c r="O12" s="5">
         <v>1096</v>
       </c>
       <c r="P12" s="4">
-        <v>0.3203935127735308</v>
+        <v>0.3181763010261014</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1695109741053435</v>
+        <v>0.1693582393856355</v>
       </c>
       <c r="R12" s="5">
         <v>1096</v>
@@ -6761,16 +6761,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.6783842998244527</v>
+        <v>-0.6766101622156544</v>
       </c>
       <c r="O13" s="5">
         <v>1062</v>
       </c>
       <c r="P13" s="4">
-        <v>0.2287749739472276</v>
+        <v>0.2289874611487538</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1771758525863603</v>
+        <v>0.1771698762473217</v>
       </c>
       <c r="R13" s="5">
         <v>1062</v>
@@ -6820,16 +6820,16 @@
         <v>8</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.05772747298739324</v>
+        <v>-0.09964822573801513</v>
       </c>
       <c r="O14" s="5">
         <v>922</v>
       </c>
       <c r="P14" s="4">
-        <v>15.10842220047735</v>
+        <v>15.09755914696258</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1666699263385819</v>
+        <v>0.1622026931719735</v>
       </c>
       <c r="R14" s="5">
         <v>914</v>
@@ -7002,22 +7002,22 @@
         <v>10</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.08870063882536226</v>
+        <v>-0.09742734741679016</v>
       </c>
       <c r="O3" s="5">
         <v>7042</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2241223594467683</v>
+        <v>0.2235368213058274</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1497711439117281</v>
+        <v>0.1498575199631944</v>
       </c>
       <c r="R3" s="5">
-        <v>7031</v>
+        <v>7032</v>
       </c>
       <c r="S3" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -7061,22 +7061,22 @@
         <v>78</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.004131341530828481</v>
+        <v>-0.09757414973553935</v>
       </c>
       <c r="O4" s="5">
         <v>5900</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4959616291366684</v>
+        <v>0.4842888611287772</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2961775467618891</v>
+        <v>0.2795726786181333</v>
       </c>
       <c r="R4" s="5">
-        <v>5822</v>
+        <v>5816</v>
       </c>
       <c r="S4" s="5">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -7120,16 +7120,16 @@
         <v>58</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1553209713437945</v>
+        <v>0.1382534339985142</v>
       </c>
       <c r="O5" s="5">
         <v>6014</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3914460366509413</v>
+        <v>0.3905445327176513</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2337760388932484</v>
+        <v>0.2330579368059301</v>
       </c>
       <c r="R5" s="5">
         <v>5963</v>
@@ -7179,16 +7179,16 @@
         <v>6</v>
       </c>
       <c r="N6" s="4">
-        <v>0.1850020318346981</v>
+        <v>0.1672248765807325</v>
       </c>
       <c r="O6" s="5">
         <v>4642</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2894135171474184</v>
+        <v>0.2881484144664301</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.190685337650847</v>
+        <v>0.1899955115492317</v>
       </c>
       <c r="R6" s="5">
         <v>4636</v>
@@ -7238,22 +7238,22 @@
         <v>35</v>
       </c>
       <c r="N7" s="4">
-        <v>0.2859411966552683</v>
+        <v>0.2087947115436464</v>
       </c>
       <c r="O7" s="5">
         <v>4139</v>
       </c>
       <c r="P7" s="4">
-        <v>0.4417646892824103</v>
+        <v>0.4312404936314092</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2635862427622925</v>
+        <v>0.2517058808839719</v>
       </c>
       <c r="R7" s="5">
-        <v>4114</v>
+        <v>4112</v>
       </c>
       <c r="S7" s="5">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="25" customHeight="1">
@@ -7297,16 +7297,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.02887592480300439</v>
+        <v>0.04781913088591239</v>
       </c>
       <c r="O8" s="5">
         <v>1228</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3275396297461032</v>
+        <v>0.3316026034411975</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1377407435823017</v>
+        <v>0.1369716384477777</v>
       </c>
       <c r="R8" s="5">
         <v>1228</v>
@@ -7356,16 +7356,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.2853156454692377</v>
+        <v>-0.2827443650050174</v>
       </c>
       <c r="O9" s="5">
         <v>1278</v>
       </c>
       <c r="P9" s="4">
-        <v>0.3269145685351466</v>
+        <v>0.3272293175684343</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1656083954504989</v>
+        <v>0.1655897122744568</v>
       </c>
       <c r="R9" s="5">
         <v>1278</v>
@@ -7415,16 +7415,16 @@
         <v>3</v>
       </c>
       <c r="N10" s="4">
-        <v>0.02032199273887142</v>
+        <v>0.04457261096779064</v>
       </c>
       <c r="O10" s="5">
         <v>1145</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1170693998743128</v>
+        <v>0.11953276009767</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.05881339033304589</v>
+        <v>0.05473430503608191</v>
       </c>
       <c r="R10" s="5">
         <v>1142</v>
@@ -7474,16 +7474,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.08581330932583787</v>
+        <v>0.02256086942783497</v>
       </c>
       <c r="O11" s="5">
         <v>1233</v>
       </c>
       <c r="P11" s="4">
-        <v>0.3578186731250382</v>
+        <v>0.3466105757442108</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.2297250292665324</v>
+        <v>0.2230919671512613</v>
       </c>
       <c r="R11" s="5">
         <v>1233</v>
@@ -7533,16 +7533,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.003590029098994433</v>
+        <v>-0.005343885787826963</v>
       </c>
       <c r="O12" s="5">
         <v>1106</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2620782811833203</v>
+        <v>0.2617911522656465</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1473059481349412</v>
+        <v>0.147298505551956</v>
       </c>
       <c r="R12" s="5">
         <v>1106</v>
@@ -7592,16 +7592,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.02303790700944144</v>
+        <v>-0.006469863687350141</v>
       </c>
       <c r="O13" s="5">
         <v>1073</v>
       </c>
       <c r="P13" s="4">
-        <v>0.171194947595206</v>
+        <v>0.1722429724000892</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1113508815362241</v>
+        <v>0.1101141696507706</v>
       </c>
       <c r="R13" s="5">
         <v>1073</v>
@@ -7651,16 +7651,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.03201053692208763</v>
+        <v>0.04452154300780542</v>
       </c>
       <c r="O14" s="5">
         <v>1010</v>
       </c>
       <c r="P14" s="4">
-        <v>0.2655111484216501</v>
+        <v>0.2670053788444446</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1113587737756264</v>
+        <v>0.1108332525391677</v>
       </c>
       <c r="R14" s="5">
         <v>1010</v>
@@ -7833,22 +7833,22 @@
         <v>35</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3676262095306016</v>
+        <v>-0.3338707447810805</v>
       </c>
       <c r="O3" s="5">
         <v>7099</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3448214776296238</v>
+        <v>0.3478097211757403</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3010578921741177</v>
+        <v>0.2993055675956149</v>
       </c>
       <c r="R3" s="5">
-        <v>7080</v>
+        <v>7079</v>
       </c>
       <c r="S3" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -7892,22 +7892,22 @@
         <v>28</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.01006090805870758</v>
+        <v>-0.1089033756379649</v>
       </c>
       <c r="O4" s="5">
         <v>6330</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5179532012776268</v>
+        <v>0.5054513325753317</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4330355980327755</v>
+        <v>0.4237755917282568</v>
       </c>
       <c r="R4" s="5">
-        <v>6302</v>
+        <v>6295</v>
       </c>
       <c r="S4" s="5">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -7951,22 +7951,22 @@
         <v>534</v>
       </c>
       <c r="N5" s="4">
-        <v>1.43578677131343</v>
+        <v>0.3402616355926398</v>
       </c>
       <c r="O5" s="5">
         <v>4708</v>
       </c>
       <c r="P5" s="4">
-        <v>6.120719254887383</v>
+        <v>6.046185775898173</v>
       </c>
       <c r="Q5" s="4">
-        <v>1.082020837691653</v>
+        <v>0.4325615834510037</v>
       </c>
       <c r="R5" s="5">
-        <v>4188</v>
+        <v>4204</v>
       </c>
       <c r="S5" s="5">
-        <v>520</v>
+        <v>504</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -8010,16 +8010,16 @@
         <v>4</v>
       </c>
       <c r="N6" s="4">
-        <v>0.2861861015351774</v>
+        <v>0.2512126151668213</v>
       </c>
       <c r="O6" s="5">
         <v>5018</v>
       </c>
       <c r="P6" s="4">
-        <v>0.316754285090613</v>
+        <v>0.3132745948583745</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2689952482794641</v>
+        <v>0.2676118767569414</v>
       </c>
       <c r="R6" s="5">
         <v>5015</v>
@@ -8069,22 +8069,22 @@
         <v>3</v>
       </c>
       <c r="N7" s="4">
-        <v>0.3894680449196923</v>
+        <v>0.3236633954975332</v>
       </c>
       <c r="O7" s="5">
         <v>4415</v>
       </c>
       <c r="P7" s="4">
-        <v>0.4116833008357039</v>
+        <v>0.4031707182771656</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.3138652827413738</v>
+        <v>0.3095979392467146</v>
       </c>
       <c r="R7" s="5">
-        <v>4415</v>
+        <v>4414</v>
       </c>
       <c r="S7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="25" customHeight="1">
@@ -8128,16 +8128,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.1467039490191946</v>
+        <v>-0.1241259924273663</v>
       </c>
       <c r="O8" s="5">
         <v>1206</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3591210266346441</v>
+        <v>0.3637772554165382</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.167380969364974</v>
+        <v>0.1661902949528844</v>
       </c>
       <c r="R8" s="5">
         <v>1206</v>
@@ -8187,16 +8187,16 @@
         <v>2</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.5656514255444773</v>
+        <v>-0.5615491819617091</v>
       </c>
       <c r="O9" s="5">
         <v>1324</v>
       </c>
       <c r="P9" s="4">
-        <v>0.3224768310689449</v>
+        <v>0.3229080857416456</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.195580200847171</v>
+        <v>0.1955184970513456</v>
       </c>
       <c r="R9" s="5">
         <v>1324</v>
@@ -8246,16 +8246,16 @@
         <v>21</v>
       </c>
       <c r="N10" s="4">
-        <v>0.11588656289738</v>
+        <v>0.04410248121951099</v>
       </c>
       <c r="O10" s="5">
         <v>492</v>
       </c>
       <c r="P10" s="4">
-        <v>0.5648660858260298</v>
+        <v>0.5290973605892382</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.203112841415186</v>
+        <v>0.1806934988764139</v>
       </c>
       <c r="R10" s="5">
         <v>472</v>
@@ -8305,16 +8305,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.1428016106298574</v>
+        <v>-0.1559903142170072</v>
       </c>
       <c r="O11" s="5">
         <v>1293</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2939153385328615</v>
+        <v>0.2922382614713309</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1865187538295558</v>
+        <v>0.1861767082397004</v>
       </c>
       <c r="R11" s="5">
         <v>1293</v>
@@ -8364,16 +8364,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.3349295945816769</v>
+        <v>-0.3439235675369332</v>
       </c>
       <c r="O12" s="5">
         <v>1056</v>
       </c>
       <c r="P12" s="4">
-        <v>0.3266252787711059</v>
+        <v>0.3246195526443802</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1842158666964626</v>
+        <v>0.1840137930377437</v>
       </c>
       <c r="R12" s="5">
         <v>1056</v>
@@ -8423,16 +8423,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.3318068651016928</v>
+        <v>-0.3025196316485506</v>
       </c>
       <c r="O13" s="5">
         <v>1057</v>
       </c>
       <c r="P13" s="4">
-        <v>0.2408534393589693</v>
+        <v>0.2424665800532817</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.2055536459038335</v>
+        <v>0.203880249577055</v>
       </c>
       <c r="R13" s="5">
         <v>1057</v>
@@ -8482,16 +8482,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.09757082077815517</v>
+        <v>-0.05728940474625688</v>
       </c>
       <c r="O14" s="5">
         <v>926</v>
       </c>
       <c r="P14" s="4">
-        <v>0.5701527249337826</v>
+        <v>0.5730463723362775</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.2024512890510809</v>
+        <v>0.1995881299440657</v>
       </c>
       <c r="R14" s="5">
         <v>926</v>
@@ -8664,22 +8664,22 @@
         <v>21</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2553242384438471</v>
+        <v>-0.2311794174851798</v>
       </c>
       <c r="O3" s="5">
         <v>7891</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1655958176257978</v>
+        <v>0.1660102518869505</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1258428593468545</v>
+        <v>0.1234990185842154</v>
       </c>
       <c r="R3" s="5">
-        <v>7875</v>
+        <v>7873</v>
       </c>
       <c r="S3" s="5">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -8723,16 +8723,16 @@
         <v>12</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1456255362412984</v>
+        <v>-0.1660127719266455</v>
       </c>
       <c r="O4" s="5">
         <v>6617</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3297112996408082</v>
+        <v>0.3275026756385613</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2372417357350657</v>
+        <v>0.2365953140468249</v>
       </c>
       <c r="R4" s="5">
         <v>6605</v>
@@ -8782,22 +8782,22 @@
         <v>1210</v>
       </c>
       <c r="N5" s="4">
-        <v>3.532991665064982</v>
+        <v>-0.6719062088695864</v>
       </c>
       <c r="O5" s="5">
         <v>5544</v>
       </c>
       <c r="P5" s="4">
-        <v>8.013259928580872</v>
+        <v>6.840198084286523</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.9587508646391355</v>
+        <v>0.2621987257385747</v>
       </c>
       <c r="R5" s="5">
-        <v>225</v>
+        <v>4322</v>
       </c>
       <c r="S5" s="5">
-        <v>5319</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -8841,16 +8841,16 @@
         <v>4</v>
       </c>
       <c r="N6" s="4">
-        <v>0.2783447690401747</v>
+        <v>0.2719134405403114</v>
       </c>
       <c r="O6" s="5">
         <v>5182</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2177239237139386</v>
+        <v>0.217119624209483</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1599729983730059</v>
+        <v>0.1598961283521275</v>
       </c>
       <c r="R6" s="5">
         <v>5179</v>
@@ -8900,16 +8900,16 @@
         <v>4</v>
       </c>
       <c r="N7" s="4">
-        <v>0.3541438806290051</v>
+        <v>0.3336159833019821</v>
       </c>
       <c r="O7" s="5">
         <v>4615</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2926548343990079</v>
+        <v>0.290083511302968</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1902544584532883</v>
+        <v>0.1895137621178878</v>
       </c>
       <c r="R7" s="5">
         <v>4614</v>
@@ -8959,16 +8959,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.0142066047506112</v>
+        <v>0.02155551725026328</v>
       </c>
       <c r="O8" s="5">
         <v>1287</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3029702810708449</v>
+        <v>0.3044949684114665</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1261459238670102</v>
+        <v>0.1259934760248122</v>
       </c>
       <c r="R8" s="5">
         <v>1287</v>
@@ -9018,16 +9018,16 @@
         <v>2</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.5135699030341743</v>
+        <v>-0.5269697284477006</v>
       </c>
       <c r="O9" s="5">
         <v>1324</v>
       </c>
       <c r="P9" s="4">
-        <v>0.3192146527927411</v>
+        <v>0.317215474326656</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1495395205954921</v>
+        <v>0.1490492243915104</v>
       </c>
       <c r="R9" s="5">
         <v>1324</v>
@@ -9077,22 +9077,22 @@
         <v>51</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.2887995111522279</v>
+        <v>-1.11098196148923</v>
       </c>
       <c r="O10" s="5">
         <v>465</v>
       </c>
       <c r="P10" s="4">
-        <v>1.434131733307207</v>
+        <v>0.9973760521593458</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.9049185475143645</v>
+        <v>0.1520863617753833</v>
       </c>
       <c r="R10" s="5">
-        <v>407</v>
+        <v>382</v>
       </c>
       <c r="S10" s="5">
-        <v>58</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="25" customHeight="1">
@@ -9136,16 +9136,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.0318073953952101</v>
+        <v>0.0134871689009497</v>
       </c>
       <c r="O11" s="5">
         <v>1314</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2568250116631794</v>
+        <v>0.2539989966628917</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.143388357924002</v>
+        <v>0.1423509380264955</v>
       </c>
       <c r="R11" s="5">
         <v>1314</v>
@@ -9195,16 +9195,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.09259881297900954</v>
+        <v>-0.1061712375098907</v>
       </c>
       <c r="O12" s="5">
         <v>1164</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2491970221441993</v>
+        <v>0.2461721956847898</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1183865710080149</v>
+        <v>0.1177567587135828</v>
       </c>
       <c r="R12" s="5">
         <v>1164</v>
@@ -9254,16 +9254,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.2371335008788765</v>
+        <v>-0.2161681166794018</v>
       </c>
       <c r="O13" s="5">
         <v>1136</v>
       </c>
       <c r="P13" s="4">
-        <v>0.1481159829099295</v>
+        <v>0.1485054438672927</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1023776459201238</v>
+        <v>0.1005611144655899</v>
       </c>
       <c r="R13" s="5">
         <v>1136</v>
@@ -9313,16 +9313,16 @@
         <v>2</v>
       </c>
       <c r="N14" s="4">
-        <v>-1.008703796210161</v>
+        <v>-1.046929783472931</v>
       </c>
       <c r="O14" s="5">
         <v>999</v>
       </c>
       <c r="P14" s="4">
-        <v>0.5347652157833825</v>
+        <v>0.524645331468034</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1173009327454261</v>
+        <v>0.111038724833139</v>
       </c>
       <c r="R14" s="5">
         <v>997</v>
@@ -9495,22 +9495,22 @@
         <v>27</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2750915452882425</v>
+        <v>-0.2521416006663841</v>
       </c>
       <c r="O3" s="5">
         <v>7887</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1678308608594069</v>
+        <v>0.1681750661804052</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.127905719907788</v>
+        <v>0.1266457389181704</v>
       </c>
       <c r="R3" s="5">
-        <v>7867</v>
+        <v>7869</v>
       </c>
       <c r="S3" s="5">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -9554,16 +9554,16 @@
         <v>13</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1293359281047159</v>
+        <v>-0.1321444214592589</v>
       </c>
       <c r="O4" s="5">
         <v>6700</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2805219573840095</v>
+        <v>0.2803065319515838</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1905826846156016</v>
+        <v>0.1905665816320052</v>
       </c>
       <c r="R4" s="5">
         <v>6686</v>
@@ -9613,22 +9613,22 @@
         <v>840</v>
       </c>
       <c r="N5" s="4">
-        <v>2.135441603653126</v>
+        <v>-0.1478671486174932</v>
       </c>
       <c r="O5" s="5">
         <v>5229</v>
       </c>
       <c r="P5" s="4">
-        <v>6.540084749726971</v>
+        <v>5.9409981745072</v>
       </c>
       <c r="Q5" s="4">
-        <v>1.594374493797421</v>
+        <v>0.1621091420953099</v>
       </c>
       <c r="R5" s="5">
-        <v>415</v>
+        <v>4386</v>
       </c>
       <c r="S5" s="5">
-        <v>4814</v>
+        <v>843</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -9672,16 +9672,16 @@
         <v>6</v>
       </c>
       <c r="N6" s="4">
-        <v>0.3820182344221296</v>
+        <v>0.3681954661348454</v>
       </c>
       <c r="O6" s="5">
         <v>5240</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1987740675684285</v>
+        <v>0.1974209292011609</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1431310435001448</v>
+        <v>0.1427700231782671</v>
       </c>
       <c r="R6" s="5">
         <v>5237</v>
@@ -9731,16 +9731,16 @@
         <v>8</v>
       </c>
       <c r="N7" s="4">
-        <v>0.5515219861351307</v>
+        <v>0.534462160553332</v>
       </c>
       <c r="O7" s="5">
         <v>4634</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2697962681424346</v>
+        <v>0.2676825235922696</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1628532633701511</v>
+        <v>0.1622404520934565</v>
       </c>
       <c r="R7" s="5">
         <v>4633</v>
@@ -9790,16 +9790,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.147275002390493</v>
+        <v>0.1572004566439809</v>
       </c>
       <c r="O8" s="5">
         <v>1178</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3329457416638203</v>
+        <v>0.3354595845263517</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1211096027409657</v>
+        <v>0.1207968638539971</v>
       </c>
       <c r="R8" s="5">
         <v>1178</v>
@@ -9849,16 +9849,16 @@
         <v>2</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.4410777424909612</v>
+        <v>-0.4317588083147257</v>
       </c>
       <c r="O9" s="5">
         <v>1329</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2647429497823078</v>
+        <v>0.265497832395707</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1158721016991546</v>
+        <v>0.1156253855262959</v>
       </c>
       <c r="R9" s="5">
         <v>1329</v>
@@ -9908,22 +9908,22 @@
         <v>20</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.4341354423060408</v>
+        <v>-0.6048237748692387</v>
       </c>
       <c r="O10" s="5">
         <v>739</v>
       </c>
       <c r="P10" s="4">
-        <v>0.4737559383964448</v>
+        <v>0.3968144081027161</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.2036613229960518</v>
+        <v>0.07495435101396009</v>
       </c>
       <c r="R10" s="5">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="S10" s="5">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="25" customHeight="1">
@@ -9967,16 +9967,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.2537809974758207</v>
+        <v>0.25126827396506</v>
       </c>
       <c r="O11" s="5">
         <v>1316</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2196832792421975</v>
+        <v>0.2194324324697523</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1162213549980485</v>
+        <v>0.1161974028032442</v>
       </c>
       <c r="R11" s="5">
         <v>1316</v>
@@ -10026,16 +10026,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.08822643625880136</v>
+        <v>0.08175662097818304</v>
       </c>
       <c r="O12" s="5">
         <v>1157</v>
       </c>
       <c r="P12" s="4">
-        <v>0.238401416978186</v>
+        <v>0.2372345091368903</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1165263592978436</v>
+        <v>0.1164398408449615</v>
       </c>
       <c r="R12" s="5">
         <v>1157</v>
@@ -10085,16 +10085,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.0545996402269485</v>
+        <v>-0.03047922360388888</v>
       </c>
       <c r="O13" s="5">
         <v>1126</v>
       </c>
       <c r="P13" s="4">
-        <v>0.1541544974344257</v>
+        <v>0.1546306950026937</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1115307538859024</v>
+        <v>0.1094033202372894</v>
       </c>
       <c r="R13" s="5">
         <v>1126</v>
@@ -10144,16 +10144,16 @@
         <v>1</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.4086887027922051</v>
+        <v>-0.4114365523571948</v>
       </c>
       <c r="O14" s="5">
         <v>1003</v>
       </c>
       <c r="P14" s="4">
-        <v>0.355521090445728</v>
+        <v>0.3551395287805305</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.08453973766270635</v>
+        <v>0.08448983070795059</v>
       </c>
       <c r="R14" s="5">
         <v>1002</v>
@@ -10272,13 +10272,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="3">
-        <v>71.29403944161312</v>
+        <v>80.53179703079991</v>
       </c>
       <c r="C3" s="3">
         <v>6.432528251717261</v>
       </c>
       <c r="D3" s="3">
-        <v>22.27343230666962</v>
+        <v>13.03567471748283</v>
       </c>
       <c r="E3" s="3">
         <v>3.037890538444493</v>
@@ -10287,16 +10287,16 @@
         <v>7.906049191225349</v>
       </c>
       <c r="G3" s="3">
-        <v>11.32949257699978</v>
+        <v>2.091734987812985</v>
       </c>
       <c r="H3" s="4">
-        <v>1.633335432256409</v>
+        <v>1.485021572412943</v>
       </c>
       <c r="I3" s="4">
-        <v>0.1927106207242855</v>
+        <v>0.1914238980729901</v>
       </c>
       <c r="J3" s="4">
-        <v>1.856653738068353</v>
+        <v>1.715251988467777</v>
       </c>
       <c r="K3" s="4">
         <v>81.358024663444</v>
@@ -10322,13 +10322,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="3">
-        <v>76.83580766674054</v>
+        <v>77.27454021715046</v>
       </c>
       <c r="C4" s="3">
         <v>8.364724130290274</v>
       </c>
       <c r="D4" s="3">
-        <v>14.7994682029692</v>
+        <v>14.36073565255927</v>
       </c>
       <c r="E4" s="3">
         <v>4.557943718147574</v>
@@ -10337,16 +10337,16 @@
         <v>8.519831597606913</v>
       </c>
       <c r="G4" s="3">
-        <v>1.721692887214713</v>
+        <v>1.282960336804786</v>
       </c>
       <c r="H4" s="4">
-        <v>1.048125433898635</v>
+        <v>1.015773471193054</v>
       </c>
       <c r="I4" s="4">
-        <v>0.3177828537985549</v>
+        <v>0.2289445153065146</v>
       </c>
       <c r="J4" s="4">
-        <v>1.227348972012322</v>
+        <v>1.203956899519205</v>
       </c>
       <c r="K4" s="4">
         <v>77.97735717375801</v>
@@ -10372,13 +10372,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="3">
-        <v>74.88810104143585</v>
+        <v>74.88145357855085</v>
       </c>
       <c r="C5" s="3">
         <v>8.94083758032351</v>
       </c>
       <c r="D5" s="3">
-        <v>16.17106137824064</v>
+        <v>16.17770884112564</v>
       </c>
       <c r="E5" s="3">
         <v>3.421227564812763</v>
@@ -10387,16 +10387,16 @@
         <v>11.57323288278307</v>
       </c>
       <c r="G5" s="3">
-        <v>1.176600930644804</v>
+        <v>1.183248393529803</v>
       </c>
       <c r="H5" s="4">
-        <v>0.5061288074702381</v>
+        <v>0.5061217780046956</v>
       </c>
       <c r="I5" s="4">
-        <v>0.3619832256713598</v>
+        <v>0.3613215903604232</v>
       </c>
       <c r="J5" s="4">
-        <v>0.4186957290993788</v>
+        <v>0.4178619494637735</v>
       </c>
       <c r="K5" s="4">
         <v>69.65816439582701</v>
@@ -10422,13 +10422,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="3">
-        <v>71.54221138931975</v>
+        <v>80.23709284289829</v>
       </c>
       <c r="C6" s="3">
         <v>6.308442277863949</v>
       </c>
       <c r="D6" s="3">
-        <v>22.14934633281631</v>
+        <v>13.45446487923776</v>
       </c>
       <c r="E6" s="3">
         <v>2.419676490139597</v>
@@ -10437,16 +10437,16 @@
         <v>8.134278750276977</v>
       </c>
       <c r="G6" s="3">
-        <v>11.59539109239974</v>
+        <v>2.900509638821183</v>
       </c>
       <c r="H6" s="4">
-        <v>0.9889684837732201</v>
+        <v>0.8515308235012544</v>
       </c>
       <c r="I6" s="4">
-        <v>0.1862782775275385</v>
+        <v>0.1814078801133126</v>
       </c>
       <c r="J6" s="4">
-        <v>1.192101414253842</v>
+        <v>1.069460225324903</v>
       </c>
       <c r="K6" s="4">
         <v>78.96917295613126</v>
@@ -10472,13 +10472,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="3">
-        <v>73.54974518058941</v>
+        <v>73.43452249058276</v>
       </c>
       <c r="C7" s="3">
         <v>10.54509195656991</v>
       </c>
       <c r="D7" s="3">
-        <v>15.90516286284068</v>
+        <v>16.02038555284733</v>
       </c>
       <c r="E7" s="3">
         <v>2.816308442277864</v>
@@ -10487,16 +10487,16 @@
         <v>11.89895856414802</v>
       </c>
       <c r="G7" s="3">
-        <v>1.189895856414802</v>
+        <v>1.305118546421449</v>
       </c>
       <c r="H7" s="4">
-        <v>0.6440052212876667</v>
+        <v>0.6247513033640307</v>
       </c>
       <c r="I7" s="4">
-        <v>0.3662736340645302</v>
+        <v>0.3219934530503796</v>
       </c>
       <c r="J7" s="4">
-        <v>0.7094184219301137</v>
+        <v>0.706273391918233</v>
       </c>
       <c r="K7" s="4">
         <v>71.2731617353345</v>
@@ -10522,13 +10522,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="3">
-        <v>70.33902060713494</v>
+        <v>78.86106802570352</v>
       </c>
       <c r="C8" s="3">
         <v>5.342344338577442</v>
       </c>
       <c r="D8" s="3">
-        <v>24.31863505428761</v>
+        <v>15.79658763571903</v>
       </c>
       <c r="E8" s="3">
         <v>2.346554398404609</v>
@@ -10537,16 +10537,16 @@
         <v>9.067139375138488</v>
       </c>
       <c r="G8" s="3">
-        <v>12.90494128074452</v>
+        <v>4.382893862175936</v>
       </c>
       <c r="H8" s="4">
-        <v>1.797115429748462</v>
+        <v>1.483881934356169</v>
       </c>
       <c r="I8" s="4">
-        <v>0.2009373607255966</v>
+        <v>0.1505732819706205</v>
       </c>
       <c r="J8" s="4">
-        <v>1.831939811696899</v>
+        <v>1.524180782684468</v>
       </c>
       <c r="K8" s="4">
         <v>82.28331758140882</v>
@@ -10572,13 +10572,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>69.08929758475514</v>
+        <v>77.69554619986705</v>
       </c>
       <c r="C9" s="3">
         <v>5.931752714380679</v>
       </c>
       <c r="D9" s="3">
-        <v>24.97894970086417</v>
+        <v>16.37270108575227</v>
       </c>
       <c r="E9" s="3">
         <v>3.252825171726125</v>
@@ -10587,16 +10587,16 @@
         <v>10.29027254597828</v>
       </c>
       <c r="G9" s="3">
-        <v>11.43585198315976</v>
+        <v>2.829603368047862</v>
       </c>
       <c r="H9" s="4">
-        <v>1.018767624979328</v>
+        <v>0.8912630187676693</v>
       </c>
       <c r="I9" s="4">
-        <v>0.1648074129003999</v>
+        <v>0.1473550761334813</v>
       </c>
       <c r="J9" s="4">
-        <v>1.05475147791528</v>
+        <v>0.9396132546739088</v>
       </c>
       <c r="K9" s="4">
         <v>81.00238238437406</v>
@@ -10622,13 +10622,13 @@
         <v>24</v>
       </c>
       <c r="B10" s="3">
-        <v>80.04210059827166</v>
+        <v>79.75182805229338</v>
       </c>
       <c r="C10" s="3">
         <v>8.092178152005317</v>
       </c>
       <c r="D10" s="3">
-        <v>11.86572124972302</v>
+        <v>12.15599379570131</v>
       </c>
       <c r="E10" s="3">
         <v>1.5976069133614</v>
@@ -10637,16 +10637,16 @@
         <v>8.564148016840239</v>
       </c>
       <c r="G10" s="3">
-        <v>1.703966319521383</v>
+        <v>1.994238865499668</v>
       </c>
       <c r="H10" s="4">
-        <v>0.6807970985949576</v>
+        <v>0.6501312240875952</v>
       </c>
       <c r="I10" s="4">
-        <v>0.2891737506654534</v>
+        <v>0.2000138112019788</v>
       </c>
       <c r="J10" s="4">
-        <v>0.8243282044768284</v>
+        <v>0.8020671983297644</v>
       </c>
       <c r="K10" s="4">
         <v>80.00521773078825</v>
@@ -10672,13 +10672,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="3">
-        <v>84.82827387547086</v>
+        <v>84.81054730777753</v>
       </c>
       <c r="C11" s="3">
         <v>5.014402836250831</v>
       </c>
       <c r="D11" s="3">
-        <v>10.15732328827831</v>
+        <v>10.17504985597164</v>
       </c>
       <c r="E11" s="3">
         <v>0.7888322623532019</v>
@@ -10687,16 +10687,16 @@
         <v>9.217815200531797</v>
       </c>
       <c r="G11" s="3">
-        <v>0.1506758253933082</v>
+        <v>0.1684023930866386</v>
       </c>
       <c r="H11" s="4">
-        <v>0.2961196424989588</v>
+        <v>0.2935262459680276</v>
       </c>
       <c r="I11" s="4">
-        <v>0.1940162588381352</v>
+        <v>0.19168503879397</v>
       </c>
       <c r="J11" s="4">
-        <v>0.2108852618072654</v>
+        <v>0.2094840659920649</v>
       </c>
       <c r="K11" s="4">
         <v>82.52629064034214</v>
@@ -10722,13 +10722,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>82.40859738533126</v>
+        <v>82.03412364280966</v>
       </c>
       <c r="C12" s="3">
         <v>6.3970751163306</v>
       </c>
       <c r="D12" s="3">
-        <v>11.19432749833813</v>
+        <v>11.56880124085974</v>
       </c>
       <c r="E12" s="3">
         <v>1.276312873919787</v>
@@ -10737,16 +10737,16 @@
         <v>8.289386217593618</v>
       </c>
       <c r="G12" s="3">
-        <v>1.628628406824729</v>
+        <v>2.003102149346333</v>
       </c>
       <c r="H12" s="4">
-        <v>0.6188516508856597</v>
+        <v>0.5856250138272233</v>
       </c>
       <c r="I12" s="4">
-        <v>0.2568844313678673</v>
+        <v>0.1592027722791618</v>
       </c>
       <c r="J12" s="4">
-        <v>0.7363521871858749</v>
+        <v>0.7070423508899032</v>
       </c>
       <c r="K12" s="4">
         <v>79.41969683951575</v>
@@ -10772,13 +10772,13 @@
         <v>27</v>
       </c>
       <c r="B13" s="3">
-        <v>78.01905606027033</v>
+        <v>77.82849545756703</v>
       </c>
       <c r="C13" s="3">
         <v>9.388433414580103</v>
       </c>
       <c r="D13" s="3">
-        <v>12.59251052514957</v>
+        <v>12.78307112785287</v>
       </c>
       <c r="E13" s="3">
         <v>1.081320629293153</v>
@@ -10787,16 +10787,16 @@
         <v>9.002880567250166</v>
       </c>
       <c r="G13" s="3">
-        <v>2.508309328606249</v>
+        <v>2.69886993130955</v>
       </c>
       <c r="H13" s="4">
-        <v>1.037919753954726</v>
+        <v>0.9923046339939461</v>
       </c>
       <c r="I13" s="4">
-        <v>0.3651791957439398</v>
+        <v>0.2628315610099619</v>
       </c>
       <c r="J13" s="4">
-        <v>0.5993144073894099</v>
+        <v>0.5665049071910893</v>
       </c>
       <c r="K13" s="4">
         <v>78.27126246022446</v>
@@ -10822,13 +10822,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="3">
-        <v>78.96299578994017</v>
+        <v>78.94748504320852</v>
       </c>
       <c r="C14" s="3">
         <v>5.645911810325726</v>
       </c>
       <c r="D14" s="3">
-        <v>15.3910923997341</v>
+        <v>15.40660314646577</v>
       </c>
       <c r="E14" s="3">
         <v>1.805894083758032</v>
@@ -10837,16 +10837,16 @@
         <v>13.19964546864613</v>
       </c>
       <c r="G14" s="3">
-        <v>0.3855528473299358</v>
+        <v>0.4010635940615999</v>
       </c>
       <c r="H14" s="4">
-        <v>0.3395715309469314</v>
+        <v>0.3359248118340503</v>
       </c>
       <c r="I14" s="4">
-        <v>0.2038917215589485</v>
+        <v>0.1991568964193431</v>
       </c>
       <c r="J14" s="4">
-        <v>0.2537383236938028</v>
+        <v>0.2550900740279763</v>
       </c>
       <c r="K14" s="4">
         <v>74.00986869376607</v>
@@ -10872,13 +10872,13 @@
         <v>29</v>
       </c>
       <c r="B15" s="3">
-        <v>76.07799689785065</v>
+        <v>76.09350764458232</v>
       </c>
       <c r="C15" s="3">
         <v>9.90471969864835</v>
       </c>
       <c r="D15" s="3">
-        <v>14.017283403501</v>
+        <v>14.00177265676933</v>
       </c>
       <c r="E15" s="3">
         <v>4.101484600044317</v>
@@ -10887,16 +10887,16 @@
         <v>8.608464436073564</v>
       </c>
       <c r="G15" s="3">
-        <v>1.307334367383115</v>
+        <v>1.291823620651451</v>
       </c>
       <c r="H15" s="4">
-        <v>1.328952026097613</v>
+        <v>1.31284225375834</v>
       </c>
       <c r="I15" s="4">
-        <v>0.3938903004168213</v>
+        <v>0.3113923189234321</v>
       </c>
       <c r="J15" s="4">
-        <v>1.577674462620914</v>
+        <v>1.572340556347812</v>
       </c>
       <c r="K15" s="4">
         <v>75.20531842251644</v>
@@ -10922,13 +10922,13 @@
         <v>30</v>
       </c>
       <c r="B16" s="3">
-        <v>71.18768003545314</v>
+        <v>80.20607134943496</v>
       </c>
       <c r="C16" s="3">
         <v>6.640815422113894</v>
       </c>
       <c r="D16" s="3">
-        <v>22.17150454243297</v>
+        <v>13.15311322845114</v>
       </c>
       <c r="E16" s="3">
         <v>2.98027919344117</v>
@@ -10937,16 +10937,16 @@
         <v>7.201418125415467</v>
       </c>
       <c r="G16" s="3">
-        <v>11.98980722357634</v>
+        <v>2.971415909594505</v>
       </c>
       <c r="H16" s="4">
-        <v>1.564883500170313</v>
+        <v>1.357365681573833</v>
       </c>
       <c r="I16" s="4">
-        <v>0.1795422430077257</v>
+        <v>0.1750811963345027</v>
       </c>
       <c r="J16" s="4">
-        <v>1.663620292432299</v>
+        <v>1.458329522277632</v>
       </c>
       <c r="K16" s="4">
         <v>81.29466801123282</v>
@@ -10972,13 +10972,13 @@
         <v>31</v>
       </c>
       <c r="B17" s="3">
-        <v>72.34655439840461</v>
+        <v>81.14779525814313</v>
       </c>
       <c r="C17" s="3">
         <v>6.031464657655661</v>
       </c>
       <c r="D17" s="3">
-        <v>21.62198094393973</v>
+        <v>12.8207400842012</v>
       </c>
       <c r="E17" s="3">
         <v>3.551961001551075</v>
@@ -10987,16 +10987,16 @@
         <v>7.239087081763794</v>
       </c>
       <c r="G17" s="3">
-        <v>10.83093286062486</v>
+        <v>2.029692000886329</v>
       </c>
       <c r="H17" s="4">
-        <v>1.271856365940899</v>
+        <v>1.171111447106997</v>
       </c>
       <c r="I17" s="4">
-        <v>0.1649099981702735</v>
+        <v>0.1454099226189935</v>
       </c>
       <c r="J17" s="4">
-        <v>1.416575998889797</v>
+        <v>1.315492449027545</v>
       </c>
       <c r="K17" s="4">
         <v>82.27096098798481</v>
@@ -11022,13 +11022,13 @@
         <v>32</v>
       </c>
       <c r="B18" s="3">
-        <v>74.01949922446266</v>
+        <v>74.09262131619765</v>
       </c>
       <c r="C18" s="3">
         <v>8.883226235320187</v>
       </c>
       <c r="D18" s="3">
-        <v>17.09727454021715</v>
+        <v>17.02415244848216</v>
       </c>
       <c r="E18" s="3">
         <v>2.674495900731221</v>
@@ -11037,16 +11037,16 @@
         <v>12.25127409705296</v>
       </c>
       <c r="G18" s="3">
-        <v>2.171504542432971</v>
+        <v>2.098382450697983</v>
       </c>
       <c r="H18" s="4">
-        <v>0.7037316368454707</v>
+        <v>0.6810115054701918</v>
       </c>
       <c r="I18" s="4">
-        <v>0.4396627899669184</v>
+        <v>0.3897475013309185</v>
       </c>
       <c r="J18" s="4">
-        <v>0.7107792935954985</v>
+        <v>0.7052524838492559</v>
       </c>
       <c r="K18" s="4">
         <v>71.29201807024602</v>
@@ -11072,13 +11072,13 @@
         <v>33</v>
       </c>
       <c r="B19" s="3">
-        <v>69.96454686461334</v>
+        <v>78.47551517837358</v>
       </c>
       <c r="C19" s="3">
         <v>7.270108575227122</v>
       </c>
       <c r="D19" s="3">
-        <v>22.76534456015954</v>
+        <v>14.25437624639929</v>
       </c>
       <c r="E19" s="3">
         <v>3.972966984267671</v>
@@ -11087,16 +11087,16 @@
         <v>6.970972745402171</v>
       </c>
       <c r="G19" s="3">
-        <v>11.8214048304897</v>
+        <v>3.310436516729448</v>
       </c>
       <c r="H19" s="4">
-        <v>1.054351890591081</v>
+        <v>0.9246907481360896</v>
       </c>
       <c r="I19" s="4">
-        <v>0.2278157624009969</v>
+        <v>0.2213500167255658</v>
       </c>
       <c r="J19" s="4">
-        <v>1.107926093325012</v>
+        <v>0.9858119710854358</v>
       </c>
       <c r="K19" s="4">
         <v>78.44404223023133</v>
@@ -11122,13 +11122,13 @@
         <v>34</v>
       </c>
       <c r="B20" s="3">
-        <v>69.90028805672502</v>
+        <v>76.7781963217372</v>
       </c>
       <c r="C20" s="3">
         <v>5.820961666297364</v>
       </c>
       <c r="D20" s="3">
-        <v>24.27875027697762</v>
+        <v>17.40084201196543</v>
       </c>
       <c r="E20" s="3">
         <v>3.527586970972745</v>
@@ -11137,16 +11137,16 @@
         <v>8.821183248393529</v>
       </c>
       <c r="G20" s="3">
-        <v>11.92998005761135</v>
+        <v>5.052071792599159</v>
       </c>
       <c r="H20" s="4">
-        <v>1.579520972184216</v>
+        <v>1.442094799271566</v>
       </c>
       <c r="I20" s="4">
-        <v>0.2207372721232872</v>
+        <v>0.1695136600575981</v>
       </c>
       <c r="J20" s="4">
-        <v>1.705554404842038</v>
+        <v>1.56558077817992</v>
       </c>
       <c r="K20" s="4">
         <v>80.244816561679</v>
@@ -11172,13 +11172,13 @@
         <v>35</v>
       </c>
       <c r="B21" s="3">
-        <v>80.54287613560824</v>
+        <v>80.47861732771993</v>
       </c>
       <c r="C21" s="3">
         <v>6.592067360957235</v>
       </c>
       <c r="D21" s="3">
-        <v>12.86505650343452</v>
+        <v>12.92931531132285</v>
       </c>
       <c r="E21" s="3">
         <v>3.450033237314425</v>
@@ -11187,16 +11187,16 @@
         <v>8.032350986040328</v>
       </c>
       <c r="G21" s="3">
-        <v>1.38267228007977</v>
+        <v>1.446931087968092</v>
       </c>
       <c r="H21" s="4">
-        <v>0.9069267189672561</v>
+        <v>0.8745452424074964</v>
       </c>
       <c r="I21" s="4">
-        <v>0.2464438933843689</v>
+        <v>0.1524165500634752</v>
       </c>
       <c r="J21" s="4">
-        <v>1.136265070887214</v>
+        <v>1.107027848628631</v>
       </c>
       <c r="K21" s="4">
         <v>80.18983103988323</v>
@@ -11222,13 +11222,13 @@
         <v>36</v>
       </c>
       <c r="B22" s="3">
-        <v>81.81032572568137</v>
+        <v>81.71504542432972</v>
       </c>
       <c r="C22" s="3">
         <v>6.388211832483935</v>
       </c>
       <c r="D22" s="3">
-        <v>11.8014624418347</v>
+        <v>11.89674274318635</v>
       </c>
       <c r="E22" s="3">
         <v>1.914469310879681</v>
@@ -11237,16 +11237,16 @@
         <v>7.476179924662087</v>
       </c>
       <c r="G22" s="3">
-        <v>2.410813206292932</v>
+        <v>2.506093507644582</v>
       </c>
       <c r="H22" s="4">
-        <v>0.7013630254810962</v>
+        <v>0.6364917090438854</v>
       </c>
       <c r="I22" s="4">
-        <v>0.2977428810144177</v>
+        <v>0.145138572066723</v>
       </c>
       <c r="J22" s="4">
-        <v>0.7292539696698129</v>
+        <v>0.6676764650701805</v>
       </c>
       <c r="K22" s="4">
         <v>81.98544265922636</v>
@@ -11272,13 +11272,13 @@
         <v>37</v>
       </c>
       <c r="B23" s="3">
-        <v>84.98559716374918</v>
+        <v>84.41834699756259</v>
       </c>
       <c r="C23" s="3">
         <v>4.230002215820962</v>
       </c>
       <c r="D23" s="3">
-        <v>10.78440062042987</v>
+        <v>11.35165078661644</v>
       </c>
       <c r="E23" s="3">
         <v>1.644139153556393</v>
@@ -11287,16 +11287,16 @@
         <v>8.949700864170175</v>
       </c>
       <c r="G23" s="3">
-        <v>0.1905606027033016</v>
+        <v>0.7578107688898738</v>
       </c>
       <c r="H23" s="4">
-        <v>0.3036292318404983</v>
+        <v>0.2837267978004819</v>
       </c>
       <c r="I23" s="4">
-        <v>0.2041417254104683</v>
+        <v>0.159231147719393</v>
       </c>
       <c r="J23" s="4">
-        <v>0.2247725074712303</v>
+        <v>0.1887412758790654</v>
       </c>
       <c r="K23" s="4">
         <v>84.21236835084136</v>
@@ -11322,13 +11322,13 @@
         <v>38</v>
       </c>
       <c r="B24" s="3">
-        <v>84.32528251717261</v>
+        <v>84.28761356082428</v>
       </c>
       <c r="C24" s="3">
         <v>4.504764015067583</v>
       </c>
       <c r="D24" s="3">
-        <v>11.16995346775981</v>
+        <v>11.20762242410813</v>
       </c>
       <c r="E24" s="3">
         <v>1.945490804343009</v>
@@ -11337,16 +11337,16 @@
         <v>9.131398183026812</v>
       </c>
       <c r="G24" s="3">
-        <v>0.09306448038998449</v>
+        <v>0.1307334367383116</v>
       </c>
       <c r="H24" s="4">
-        <v>0.268997352630669</v>
+        <v>0.2636188610718653</v>
       </c>
       <c r="I24" s="4">
-        <v>0.1639588839029833</v>
+        <v>0.1515742827488351</v>
       </c>
       <c r="J24" s="4">
-        <v>0.1854711929814004</v>
+        <v>0.1698482056815735</v>
       </c>
       <c r="K24" s="4">
         <v>83.19692166696072</v>
@@ -11372,13 +11372,13 @@
         <v>39</v>
       </c>
       <c r="B25" s="3">
-        <v>83.89984489253268</v>
+        <v>83.86439175714602</v>
       </c>
       <c r="C25" s="3">
         <v>4.515843119875914</v>
       </c>
       <c r="D25" s="3">
-        <v>11.5843119875914</v>
+        <v>11.61976512297806</v>
       </c>
       <c r="E25" s="3">
         <v>1.781520053179703</v>
@@ -11387,16 +11387,16 @@
         <v>9.703079991136716</v>
       </c>
       <c r="G25" s="3">
-        <v>0.09971194327498339</v>
+        <v>0.1351650786616441</v>
       </c>
       <c r="H25" s="4">
-        <v>0.2732791347465323</v>
+        <v>0.2686163237504265</v>
       </c>
       <c r="I25" s="4">
-        <v>0.1623766566415059</v>
+        <v>0.1503245714578575</v>
       </c>
       <c r="J25" s="4">
-        <v>0.183605481432703</v>
+        <v>0.1678554377670024</v>
       </c>
       <c r="K25" s="4">
         <v>83.37541735063185</v>
@@ -11583,16 +11583,16 @@
         <v>22</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.280022619773598</v>
+        <v>-0.2567532262192174</v>
       </c>
       <c r="O3" s="5">
         <v>6879</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3286975756628071</v>
+        <v>0.3308720598923773</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2789335756709514</v>
+        <v>0.2780914494622594</v>
       </c>
       <c r="R3" s="5">
         <v>6861</v>
@@ -11642,22 +11642,22 @@
         <v>123</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4539924659474557</v>
+        <v>-0.5027393417858548</v>
       </c>
       <c r="O4" s="5">
         <v>5857</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6257599459678644</v>
+        <v>0.6207009705590441</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5043788986013553</v>
+        <v>0.5012462320030321</v>
       </c>
       <c r="R4" s="5">
-        <v>5771</v>
+        <v>5766</v>
       </c>
       <c r="S4" s="5">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -11701,22 +11701,22 @@
         <v>1037</v>
       </c>
       <c r="N5" s="4">
-        <v>1.55527119785986</v>
+        <v>0.7411290937945409</v>
       </c>
       <c r="O5" s="5">
         <v>5126</v>
       </c>
       <c r="P5" s="4">
-        <v>2.015302023500064</v>
+        <v>1.880309415656892</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.9991451107091527</v>
+        <v>0.6163806771971382</v>
       </c>
       <c r="R5" s="5">
-        <v>4266</v>
+        <v>4304</v>
       </c>
       <c r="S5" s="5">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -11760,22 +11760,22 @@
         <v>4</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.1702511863466951</v>
+        <v>-0.2051574567340708</v>
       </c>
       <c r="O6" s="5">
         <v>4737</v>
       </c>
       <c r="P6" s="4">
-        <v>0.4050998530892129</v>
+        <v>0.402106804565956</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.3520163347882349</v>
+        <v>0.3514086054916933</v>
       </c>
       <c r="R6" s="5">
-        <v>4733</v>
+        <v>4734</v>
       </c>
       <c r="S6" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="25" customHeight="1">
@@ -11819,16 +11819,16 @@
         <v>3</v>
       </c>
       <c r="N7" s="4">
-        <v>0.04962185105655619</v>
+        <v>0.02786100231878663</v>
       </c>
       <c r="O7" s="5">
         <v>4211</v>
       </c>
       <c r="P7" s="4">
-        <v>0.5264573257560744</v>
+        <v>0.524030524529533</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.4255601570596704</v>
+        <v>0.4252440709956533</v>
       </c>
       <c r="R7" s="5">
         <v>4208</v>
@@ -11878,16 +11878,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.5491369577036098</v>
+        <v>-0.5082225001061715</v>
       </c>
       <c r="O8" s="5">
         <v>1120</v>
       </c>
       <c r="P8" s="4">
-        <v>0.466186093275451</v>
+        <v>0.4745830053902996</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2951107229760263</v>
+        <v>0.292744497407595</v>
       </c>
       <c r="R8" s="5">
         <v>1120</v>
@@ -11937,16 +11937,16 @@
         <v>13</v>
       </c>
       <c r="N9" s="4">
-        <v>-1.001568941503616</v>
+        <v>-1.023372980472232</v>
       </c>
       <c r="O9" s="5">
         <v>1235</v>
       </c>
       <c r="P9" s="4">
-        <v>0.5101184961277795</v>
+        <v>0.5079431904279363</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.3608233047075256</v>
+        <v>0.3603453118565995</v>
       </c>
       <c r="R9" s="5">
         <v>1235</v>
@@ -11996,22 +11996,22 @@
         <v>2</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.0929679390638817</v>
+        <v>-0.06526142313475702</v>
       </c>
       <c r="O10" s="5">
         <v>1018</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1742973663732433</v>
+        <v>0.1765049412826387</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1124813413565623</v>
+        <v>0.1070674784938975</v>
       </c>
       <c r="R10" s="5">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="S10" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="25" customHeight="1">
@@ -12055,16 +12055,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.6294939418065532</v>
+        <v>-0.6445572175908012</v>
       </c>
       <c r="O11" s="5">
         <v>1236</v>
       </c>
       <c r="P11" s="4">
-        <v>0.4368784745133098</v>
+        <v>0.435527102628232</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.3122774666456289</v>
+        <v>0.3120620990182431</v>
       </c>
       <c r="R11" s="5">
         <v>1236</v>
@@ -12114,16 +12114,16 @@
         <v>1</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.8720430789607618</v>
+        <v>-0.8451682035402541</v>
       </c>
       <c r="O12" s="5">
         <v>1070</v>
       </c>
       <c r="P12" s="4">
-        <v>0.4061156697407819</v>
+        <v>0.4092196983073458</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.2729602987370118</v>
+        <v>0.2717231630380553</v>
       </c>
       <c r="R12" s="5">
         <v>1070</v>
@@ -12173,16 +12173,16 @@
         <v>1</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.8810360843999726</v>
+        <v>-0.8198076975205311</v>
       </c>
       <c r="O13" s="5">
         <v>1017</v>
       </c>
       <c r="P13" s="4">
-        <v>0.3238390440968456</v>
+        <v>0.3247194643268017</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.2778280791042719</v>
+        <v>0.2734740511470247</v>
       </c>
       <c r="R13" s="5">
         <v>1017</v>
@@ -12232,16 +12232,16 @@
         <v>8</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.1456642714419306</v>
+        <v>-0.1475247213865032</v>
       </c>
       <c r="O14" s="5">
         <v>879</v>
       </c>
       <c r="P14" s="4">
-        <v>0.5166939029827587</v>
+        <v>0.516394797958627</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.3353274127609943</v>
+        <v>0.3353058702254214</v>
       </c>
       <c r="R14" s="5">
         <v>871</v>
@@ -12414,22 +12414,22 @@
         <v>19</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1741979360885885</v>
+        <v>-0.155254251204525</v>
       </c>
       <c r="O3" s="5">
         <v>7528</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2019954004492589</v>
+        <v>0.2029468108770857</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1640351565050782</v>
+        <v>0.1630129107820937</v>
       </c>
       <c r="R3" s="5">
-        <v>7512</v>
+        <v>7511</v>
       </c>
       <c r="S3" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -12473,22 +12473,22 @@
         <v>16</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1718567598144292</v>
+        <v>-0.1599388259000989</v>
       </c>
       <c r="O4" s="5">
         <v>6508</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3806572515407105</v>
+        <v>0.3812414939702135</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2964263718312586</v>
+        <v>0.2965369499732842</v>
       </c>
       <c r="R4" s="5">
-        <v>6491</v>
+        <v>6492</v>
       </c>
       <c r="S4" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -12532,22 +12532,22 @@
         <v>1446</v>
       </c>
       <c r="N5" s="4">
-        <v>3.035416001755351</v>
+        <v>0.2689670270758029</v>
       </c>
       <c r="O5" s="5">
         <v>5675</v>
       </c>
       <c r="P5" s="4">
-        <v>4.764997376799871</v>
+        <v>3.984456542911615</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.9475256165442947</v>
+        <v>0.2642708680911567</v>
       </c>
       <c r="R5" s="5">
-        <v>409</v>
+        <v>4251</v>
       </c>
       <c r="S5" s="5">
-        <v>5266</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -12591,16 +12591,16 @@
         <v>5</v>
       </c>
       <c r="N6" s="4">
-        <v>0.2391036001938555</v>
+        <v>0.2375736195753575</v>
       </c>
       <c r="O6" s="5">
         <v>5084</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2473910345020789</v>
+        <v>0.247263750771396</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1904667242563479</v>
+        <v>0.1904610423765269</v>
       </c>
       <c r="R6" s="5">
         <v>5082</v>
@@ -12650,16 +12650,16 @@
         <v>2</v>
       </c>
       <c r="N7" s="4">
-        <v>0.1038942767213957</v>
+        <v>0.1117212618346457</v>
       </c>
       <c r="O7" s="5">
         <v>4544</v>
       </c>
       <c r="P7" s="4">
-        <v>0.3621777598036353</v>
+        <v>0.3627873880615534</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.246353480000025</v>
+        <v>0.2462751588013889</v>
       </c>
       <c r="R7" s="5">
         <v>4543</v>
@@ -12709,16 +12709,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.01494244339833995</v>
+        <v>0.01814798553539276</v>
       </c>
       <c r="O8" s="5">
         <v>1178</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3845708756873436</v>
+        <v>0.3853306652208788</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1987577298892151</v>
+        <v>0.1987400097717203</v>
       </c>
       <c r="R8" s="5">
         <v>1178</v>
@@ -12768,16 +12768,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.4924479998794239</v>
+        <v>-0.4889534985986757</v>
       </c>
       <c r="O9" s="5">
         <v>1212</v>
       </c>
       <c r="P9" s="4">
-        <v>0.4776097663449032</v>
+        <v>0.4781140396692851</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2164930843372885</v>
+        <v>0.2164781689452217</v>
       </c>
       <c r="R9" s="5">
         <v>1212</v>
@@ -12827,22 +12827,22 @@
         <v>26</v>
       </c>
       <c r="N10" s="4">
-        <v>0.09556238406093595</v>
+        <v>-0.0677977556750875</v>
       </c>
       <c r="O10" s="5">
         <v>744</v>
       </c>
       <c r="P10" s="4">
-        <v>0.7189015416773779</v>
+        <v>0.6610883317263321</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.2280994110683257</v>
+        <v>0.1285921713874361</v>
       </c>
       <c r="R10" s="5">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="S10" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="25" customHeight="1">
@@ -12886,16 +12886,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.1526602045151616</v>
+        <v>-0.1628041569256595</v>
       </c>
       <c r="O11" s="5">
         <v>1285</v>
       </c>
       <c r="P11" s="4">
-        <v>0.3629524387276046</v>
+        <v>0.3620466235016191</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.2200373696865881</v>
+        <v>0.2198468373194973</v>
       </c>
       <c r="R11" s="5">
         <v>1285</v>
@@ -12945,16 +12945,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.2320666023670385</v>
+        <v>-0.2454785200598621</v>
       </c>
       <c r="O12" s="5">
         <v>1160</v>
       </c>
       <c r="P12" s="4">
-        <v>0.3373851834212527</v>
+        <v>0.3352087634867854</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.22373838690072</v>
+        <v>0.2234877493985392</v>
       </c>
       <c r="R12" s="5">
         <v>1160</v>
@@ -13004,16 +13004,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.2112127063519823</v>
+        <v>-0.2044539875861062</v>
       </c>
       <c r="O13" s="5">
         <v>1089</v>
       </c>
       <c r="P13" s="4">
-        <v>0.2411106690187902</v>
+        <v>0.2415696920544501</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1923568587081862</v>
+        <v>0.1922474367390131</v>
       </c>
       <c r="R13" s="5">
         <v>1089</v>
@@ -13063,16 +13063,16 @@
         <v>8</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.001500585109801192</v>
+        <v>-0.06464784866045648</v>
       </c>
       <c r="O14" s="5">
         <v>903</v>
       </c>
       <c r="P14" s="4">
-        <v>0.4955952452297264</v>
+        <v>0.4757058322197835</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1675781279792281</v>
+        <v>0.1561284145234893</v>
       </c>
       <c r="R14" s="5">
         <v>895</v>
@@ -13245,16 +13245,16 @@
         <v>37</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6073852656440943</v>
+        <v>-0.5247661315670769</v>
       </c>
       <c r="O3" s="5">
         <v>7667</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2331474485217284</v>
+        <v>0.224392125837909</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1912333686338589</v>
+        <v>0.1744844764422523</v>
       </c>
       <c r="R3" s="5">
         <v>7641</v>
@@ -13304,22 +13304,22 @@
         <v>387</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.100643096967779</v>
+        <v>-0.9504259097429895</v>
       </c>
       <c r="O4" s="5">
         <v>6539</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4528726646901831</v>
+        <v>0.4342758879385438</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3534958351821362</v>
+        <v>0.3230014014141742</v>
       </c>
       <c r="R4" s="5">
-        <v>6521</v>
+        <v>6524</v>
       </c>
       <c r="S4" s="5">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -13363,22 +13363,22 @@
         <v>1985</v>
       </c>
       <c r="N5" s="4">
-        <v>2.750465031627849</v>
+        <v>0.2278109819855558</v>
       </c>
       <c r="O5" s="5">
         <v>5309</v>
       </c>
       <c r="P5" s="4">
-        <v>7.650640065214233</v>
+        <v>6.957834467157547</v>
       </c>
       <c r="Q5" s="4">
-        <v>1.211472719555894</v>
+        <v>0.1097439491264845</v>
       </c>
       <c r="R5" s="5">
-        <v>117</v>
+        <v>3250</v>
       </c>
       <c r="S5" s="5">
-        <v>5192</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -13422,16 +13422,16 @@
         <v>4</v>
       </c>
       <c r="N6" s="4">
-        <v>0.3935533092066186</v>
+        <v>0.3964261056352711</v>
       </c>
       <c r="O6" s="5">
         <v>5086</v>
       </c>
       <c r="P6" s="4">
-        <v>0.201030837096543</v>
+        <v>0.2012222734672496</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1241231878063918</v>
+        <v>0.1240994784235896</v>
       </c>
       <c r="R6" s="5">
         <v>5081</v>
@@ -13481,16 +13481,16 @@
         <v>24</v>
       </c>
       <c r="N7" s="4">
-        <v>1.049595178620989</v>
+        <v>1.049720465837709</v>
       </c>
       <c r="O7" s="5">
         <v>4521</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2788697445332224</v>
+        <v>0.2788803349976495</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1393520721505967</v>
+        <v>0.1393520998751413</v>
       </c>
       <c r="R7" s="5">
         <v>4519</v>
@@ -13540,16 +13540,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.1303272613201003</v>
+        <v>-0.1236517822663927</v>
       </c>
       <c r="O8" s="5">
         <v>1140</v>
       </c>
       <c r="P8" s="4">
-        <v>0.4087357581335883</v>
+        <v>0.4106593423194186</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1125002412144782</v>
+        <v>0.1123967093508293</v>
       </c>
       <c r="R8" s="5">
         <v>1140</v>
@@ -13599,16 +13599,16 @@
         <v>20</v>
       </c>
       <c r="N9" s="4">
-        <v>-1.494198062417383</v>
+        <v>-1.497373667777538</v>
       </c>
       <c r="O9" s="5">
         <v>1223</v>
       </c>
       <c r="P9" s="4">
-        <v>0.3668855007861908</v>
+        <v>0.3663275286812365</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1122392576531501</v>
+        <v>0.1121957662697004</v>
       </c>
       <c r="R9" s="5">
         <v>1223</v>
@@ -13658,22 +13658,22 @@
         <v>155</v>
       </c>
       <c r="N10" s="4">
-        <v>0.514575557266076</v>
+        <v>-0.6806736350644087</v>
       </c>
       <c r="O10" s="5">
         <v>974</v>
       </c>
       <c r="P10" s="4">
-        <v>2.486320513985665</v>
+        <v>1.933648314827974</v>
       </c>
       <c r="Q10" s="4">
-        <v>1.21859456812606</v>
+        <v>0.08334833824044556</v>
       </c>
       <c r="R10" s="5">
-        <v>836</v>
+        <v>804</v>
       </c>
       <c r="S10" s="5">
-        <v>138</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="25" customHeight="1">
@@ -13717,16 +13717,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.5062984055865667</v>
+        <v>0.4941602997805319</v>
       </c>
       <c r="O11" s="5">
         <v>1263</v>
       </c>
       <c r="P11" s="4">
-        <v>0.316616344038581</v>
+        <v>0.3148574239965195</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1197508170434739</v>
+        <v>0.119378347115537</v>
       </c>
       <c r="R11" s="5">
         <v>1263</v>
@@ -13776,16 +13776,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.0303172907667934</v>
+        <v>0.02812265635378708</v>
       </c>
       <c r="O12" s="5">
         <v>1165</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2249357278953857</v>
+        <v>0.2245465126461965</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1111710124657164</v>
+        <v>0.111149690846207</v>
       </c>
       <c r="R12" s="5">
         <v>1165</v>
@@ -13835,16 +13835,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.4114316325277264</v>
+        <v>-0.3759558079892429</v>
       </c>
       <c r="O13" s="5">
         <v>1066</v>
       </c>
       <c r="P13" s="4">
-        <v>0.185264445236296</v>
+        <v>0.1869199818740124</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1159122008221808</v>
+        <v>0.1119288253067589</v>
       </c>
       <c r="R13" s="5">
         <v>1066</v>
@@ -13894,16 +13894,16 @@
         <v>3</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.2148761830120478</v>
+        <v>-0.2919561488405407</v>
       </c>
       <c r="O14" s="5">
         <v>977</v>
       </c>
       <c r="P14" s="4">
-        <v>0.5413651533871213</v>
+        <v>0.5127225183506338</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1091246123138847</v>
+        <v>0.08651105239680378</v>
       </c>
       <c r="R14" s="5">
         <v>974</v>
@@ -14076,16 +14076,16 @@
         <v>31</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3854810880261149</v>
+        <v>-0.3488912226508063</v>
       </c>
       <c r="O3" s="5">
         <v>7798</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1828314453008553</v>
+        <v>0.1824777699944403</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1415865166288685</v>
+        <v>0.1376801876531228</v>
       </c>
       <c r="R3" s="5">
         <v>7781</v>
@@ -14135,16 +14135,16 @@
         <v>10</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2296137759827076</v>
+        <v>-0.2226169816622132</v>
       </c>
       <c r="O4" s="5">
         <v>6558</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2978024402539428</v>
+        <v>0.2983064273500695</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2062184966216748</v>
+        <v>0.2061253301166902</v>
       </c>
       <c r="R4" s="5">
         <v>6548</v>
@@ -14194,22 +14194,22 @@
         <v>623</v>
       </c>
       <c r="N5" s="4">
-        <v>1.006926588297492</v>
+        <v>0.1059050120749703</v>
       </c>
       <c r="O5" s="5">
         <v>4903</v>
       </c>
       <c r="P5" s="4">
-        <v>4.310555518326466</v>
+        <v>4.115501874343794</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.951560959628305</v>
+        <v>0.1682404737794546</v>
       </c>
       <c r="R5" s="5">
-        <v>4310</v>
+        <v>4281</v>
       </c>
       <c r="S5" s="5">
-        <v>593</v>
+        <v>622</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -14253,16 +14253,16 @@
         <v>5</v>
       </c>
       <c r="N6" s="4">
-        <v>0.1253551763101455</v>
+        <v>0.1173430480120601</v>
       </c>
       <c r="O6" s="5">
         <v>5117</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2026660633903604</v>
+        <v>0.2018032712230028</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1380147880537159</v>
+        <v>0.1378410770825701</v>
       </c>
       <c r="R6" s="5">
         <v>5114</v>
@@ -14312,16 +14312,16 @@
         <v>3</v>
       </c>
       <c r="N7" s="4">
-        <v>0.2904768940801154</v>
+        <v>0.2695535943266805</v>
       </c>
       <c r="O7" s="5">
         <v>4588</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2723497526313984</v>
+        <v>0.2697833751137031</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1651096223790142</v>
+        <v>0.1643062273773739</v>
       </c>
       <c r="R7" s="5">
         <v>4587</v>
@@ -14371,16 +14371,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.1767839353655892</v>
+        <v>-0.1679300413098872</v>
       </c>
       <c r="O8" s="5">
         <v>1273</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3045366849687667</v>
+        <v>0.3065527750093395</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1185920261826506</v>
+        <v>0.1183491680109643</v>
       </c>
       <c r="R8" s="5">
         <v>1273</v>
@@ -14430,16 +14430,16 @@
         <v>2</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.5582967411771695</v>
+        <v>-0.5577646188385188</v>
       </c>
       <c r="O9" s="5">
         <v>1332</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2987245799329517</v>
+        <v>0.2987870669047478</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1339545654965661</v>
+        <v>0.1339541482231025</v>
       </c>
       <c r="R9" s="5">
         <v>1332</v>
@@ -14489,16 +14489,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.3471715809098913</v>
+        <v>-0.3286184027236914</v>
       </c>
       <c r="O10" s="5">
         <v>878</v>
       </c>
       <c r="P10" s="4">
-        <v>0.163643829304828</v>
+        <v>0.1611649282708091</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.06778688367400054</v>
+        <v>0.06587732244365244</v>
       </c>
       <c r="R10" s="5">
         <v>878</v>
@@ -14548,16 +14548,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.0552277449705721</v>
+        <v>-0.07336521126310913</v>
       </c>
       <c r="O11" s="5">
         <v>1290</v>
       </c>
       <c r="P11" s="4">
-        <v>0.272270286649258</v>
+        <v>0.2697449524511502</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1341311335550514</v>
+        <v>0.1334567657788067</v>
       </c>
       <c r="R11" s="5">
         <v>1290</v>
@@ -14607,16 +14607,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.2632637640179311</v>
+        <v>-0.2779522828414542</v>
       </c>
       <c r="O12" s="5">
         <v>1127</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2814503203954798</v>
+        <v>0.2780728072550431</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1310449601191775</v>
+        <v>0.1305817517039331</v>
       </c>
       <c r="R12" s="5">
         <v>1127</v>
@@ -14666,16 +14666,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.5152508797693519</v>
+        <v>-0.4958089749416956</v>
       </c>
       <c r="O13" s="5">
         <v>1119</v>
       </c>
       <c r="P13" s="4">
-        <v>0.1437029537944124</v>
+        <v>0.1447173320890453</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1048946299974218</v>
+        <v>0.1036595754419065</v>
       </c>
       <c r="R13" s="5">
         <v>1119</v>
@@ -14725,16 +14725,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.2255022981181959</v>
+        <v>-0.2083088185198676</v>
       </c>
       <c r="O14" s="5">
         <v>990</v>
       </c>
       <c r="P14" s="4">
-        <v>0.360966706898822</v>
+        <v>0.3621875026784437</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1157439809677557</v>
+        <v>0.1148443058395129</v>
       </c>
       <c r="R14" s="5">
         <v>990</v>
@@ -14907,16 +14907,16 @@
         <v>17</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1545017131590343</v>
+        <v>-0.138166962612587</v>
       </c>
       <c r="O3" s="5">
         <v>7876</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1545213657005332</v>
+        <v>0.1550334223493663</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.113314372296983</v>
+        <v>0.1123507129073005</v>
       </c>
       <c r="R3" s="5">
         <v>7860</v>
@@ -14966,16 +14966,16 @@
         <v>9</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.154262220893988</v>
+        <v>-0.1502166817717807</v>
       </c>
       <c r="O4" s="5">
         <v>6601</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2965388423509546</v>
+        <v>0.2968480897775731</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.195048243562154</v>
+        <v>0.1950255517862308</v>
       </c>
       <c r="R4" s="5">
         <v>6592</v>
@@ -15025,22 +15025,22 @@
         <v>1145</v>
       </c>
       <c r="N5" s="4">
-        <v>1.677361795188454</v>
+        <v>0.2145435585991322</v>
       </c>
       <c r="O5" s="5">
         <v>5522</v>
       </c>
       <c r="P5" s="4">
-        <v>3.16533415528838</v>
+        <v>2.76727081605027</v>
       </c>
       <c r="Q5" s="4">
-        <v>1.479203065922624</v>
+        <v>0.2226924333590441</v>
       </c>
       <c r="R5" s="5">
-        <v>4468</v>
+        <v>4425</v>
       </c>
       <c r="S5" s="5">
-        <v>1054</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -15084,16 +15084,16 @@
         <v>3</v>
       </c>
       <c r="N6" s="4">
-        <v>0.1609676339563623</v>
+        <v>0.1635572599643069</v>
       </c>
       <c r="O6" s="5">
         <v>5160</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1846031921086585</v>
+        <v>0.1848063791790233</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1250802475309223</v>
+        <v>0.1250626681656689</v>
       </c>
       <c r="R6" s="5">
         <v>5157</v>
@@ -15143,16 +15143,16 @@
         <v>2</v>
       </c>
       <c r="N7" s="4">
-        <v>0.1387462392332736</v>
+        <v>0.1324203846334058</v>
       </c>
       <c r="O7" s="5">
         <v>4595</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2591774722874333</v>
+        <v>0.2585335129998393</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1532433511816275</v>
+        <v>0.1531717002223215</v>
       </c>
       <c r="R7" s="5">
         <v>4594</v>
@@ -15202,16 +15202,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.01290036556469446</v>
+        <v>0.02945502667250821</v>
       </c>
       <c r="O8" s="5">
         <v>1223</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3197793543836457</v>
+        <v>0.323779603403273</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1204093899789723</v>
+        <v>0.1197607804737669</v>
       </c>
       <c r="R8" s="5">
         <v>1223</v>
@@ -15261,16 +15261,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.3426278607542479</v>
+        <v>-0.3304328889471435</v>
       </c>
       <c r="O9" s="5">
         <v>1358</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2558543405574714</v>
+        <v>0.256615991428103</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1230445493120849</v>
+        <v>0.1225080528224168</v>
       </c>
       <c r="R9" s="5">
         <v>1358</v>
@@ -15320,16 +15320,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.0547433655202265</v>
+        <v>0.07042305320112519</v>
       </c>
       <c r="O10" s="5">
         <v>967</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1006063651735969</v>
+        <v>0.0992060990394552</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.04259762884570534</v>
+        <v>0.0397636629413332</v>
       </c>
       <c r="R10" s="5">
         <v>967</v>
@@ -15379,16 +15379,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.05860716953532351</v>
+        <v>-0.0606486106389923</v>
       </c>
       <c r="O11" s="5">
         <v>1337</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2086768848240199</v>
+        <v>0.2084920255727042</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1201106594364904</v>
+        <v>0.1200940992661749</v>
       </c>
       <c r="R11" s="5">
         <v>1337</v>
@@ -15438,16 +15438,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.0764631526811216</v>
+        <v>-0.0733774512619334</v>
       </c>
       <c r="O12" s="5">
         <v>1206</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2168188715239194</v>
+        <v>0.2172470744869497</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.106047778719674</v>
+        <v>0.1059901173713606</v>
       </c>
       <c r="R12" s="5">
         <v>1206</v>
@@ -15497,16 +15497,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.06718592238731168</v>
+        <v>-0.04914295021816883</v>
       </c>
       <c r="O13" s="5">
         <v>1132</v>
       </c>
       <c r="P13" s="4">
-        <v>0.1422127210137521</v>
+        <v>0.1426329086000882</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.09969364368973704</v>
+        <v>0.09832604374132675</v>
       </c>
       <c r="R13" s="5">
         <v>1132</v>
@@ -15556,16 +15556,16 @@
         <v>5</v>
       </c>
       <c r="N14" s="4">
-        <v>0.05982560038088352</v>
+        <v>0.03401528381175467</v>
       </c>
       <c r="O14" s="5">
         <v>1032</v>
       </c>
       <c r="P14" s="4">
-        <v>0.3005290664840768</v>
+        <v>0.2957262617403961</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.09888604212899373</v>
+        <v>0.09612699667427359</v>
       </c>
       <c r="R14" s="5">
         <v>1027</v>
@@ -15738,16 +15738,16 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.03042774257141167</v>
+        <v>-0.01799048663909986</v>
       </c>
       <c r="O3" s="5">
         <v>7581</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1457751550433231</v>
+        <v>0.1462836252226436</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.07185223496475987</v>
+        <v>0.07089131871503487</v>
       </c>
       <c r="R3" s="5">
         <v>7577</v>
@@ -15797,22 +15797,22 @@
         <v>22</v>
       </c>
       <c r="N4" s="4">
-        <v>0.04591956300487168</v>
+        <v>0.07696842487624522</v>
       </c>
       <c r="O4" s="5">
         <v>6472</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2793211066796873</v>
+        <v>0.2797724502007256</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1626812685721797</v>
+        <v>0.1592938090734634</v>
       </c>
       <c r="R4" s="5">
-        <v>6449</v>
+        <v>6447</v>
       </c>
       <c r="S4" s="5">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -15856,22 +15856,22 @@
         <v>134</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2798171246378553</v>
+        <v>0.1318946790963196</v>
       </c>
       <c r="O5" s="5">
         <v>6384</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7399839058166675</v>
+        <v>0.6157647678778982</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6670281831343037</v>
+        <v>0.4252740657785439</v>
       </c>
       <c r="R5" s="5">
-        <v>6327</v>
+        <v>6074</v>
       </c>
       <c r="S5" s="5">
-        <v>57</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -15915,16 +15915,16 @@
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>0.2748483290352034</v>
+        <v>0.296861760380069</v>
       </c>
       <c r="O6" s="5">
         <v>4975</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1859270937428629</v>
+        <v>0.1867368458344535</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.0923670474378573</v>
+        <v>0.09039642230482936</v>
       </c>
       <c r="R6" s="5">
         <v>4974</v>
@@ -15974,22 +15974,22 @@
         <v>1</v>
       </c>
       <c r="N7" s="4">
-        <v>0.05695747025879039</v>
+        <v>0.09186563401362946</v>
       </c>
       <c r="O7" s="5">
         <v>4489</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2597451103856777</v>
+        <v>0.2601780901292384</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1290928643539471</v>
+        <v>0.1243753739966121</v>
       </c>
       <c r="R7" s="5">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="S7" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="25" customHeight="1">
@@ -16033,16 +16033,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.2165356820540381</v>
+        <v>0.2508672371612879</v>
       </c>
       <c r="O8" s="5">
         <v>1315</v>
       </c>
       <c r="P8" s="4">
-        <v>0.296825758455502</v>
+        <v>0.3009328645710749</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1106263213400514</v>
+        <v>0.1051872967466623</v>
       </c>
       <c r="R8" s="5">
         <v>1315</v>
@@ -16092,16 +16092,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.04786020747790198</v>
+        <v>0.008924692400810841</v>
       </c>
       <c r="O9" s="5">
         <v>1277</v>
       </c>
       <c r="P9" s="4">
-        <v>0.3358261803310393</v>
+        <v>0.3360603427217166</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1556483899232728</v>
+        <v>0.1451943006200953</v>
       </c>
       <c r="R9" s="5">
         <v>1277</v>
@@ -16151,16 +16151,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.08773051004940145</v>
+        <v>0.1055854300049113</v>
       </c>
       <c r="O10" s="5">
         <v>1348</v>
       </c>
       <c r="P10" s="4">
-        <v>0.08097492912930243</v>
+        <v>0.07951799609513295</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.04976772806214773</v>
+        <v>0.04592938584397412</v>
       </c>
       <c r="R10" s="5">
         <v>1348</v>
@@ -16210,16 +16210,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.02510070873623097</v>
+        <v>0.03656570129712122</v>
       </c>
       <c r="O11" s="5">
         <v>1291</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2888482159240173</v>
+        <v>0.2876823601485406</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1698737785241818</v>
+        <v>0.1598459902244856</v>
       </c>
       <c r="R11" s="5">
         <v>1291</v>
@@ -16269,16 +16269,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.03248874106117472</v>
+        <v>0.09248369249775124</v>
       </c>
       <c r="O12" s="5">
         <v>1141</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2825466868695185</v>
+        <v>0.2847231298284999</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1382876922865807</v>
+        <v>0.1255968376070428</v>
       </c>
       <c r="R12" s="5">
         <v>1141</v>
@@ -16328,16 +16328,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.1055414932293291</v>
+        <v>0.1528345712939938</v>
       </c>
       <c r="O13" s="5">
         <v>1112</v>
       </c>
       <c r="P13" s="4">
-        <v>0.1567378659762702</v>
+        <v>0.1526788598619993</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1075054698856176</v>
+        <v>0.0973833831156827</v>
       </c>
       <c r="R13" s="5">
         <v>1112</v>
@@ -16387,16 +16387,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.143942355439308</v>
+        <v>0.1562502264670229</v>
       </c>
       <c r="O14" s="5">
         <v>1055</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1617275677420726</v>
+        <v>0.1622994654201174</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.06544376849999702</v>
+        <v>0.06431664195413658</v>
       </c>
       <c r="R14" s="5">
         <v>1055</v>
@@ -16569,16 +16569,16 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.02665912976096848</v>
+        <v>-0.02141786234372489</v>
       </c>
       <c r="O3" s="5">
         <v>7565</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1630735743136142</v>
+        <v>0.1635113242257044</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.07983442359016002</v>
+        <v>0.07969637189902627</v>
       </c>
       <c r="R3" s="5">
         <v>7561</v>
@@ -16628,22 +16628,22 @@
         <v>20</v>
       </c>
       <c r="N4" s="4">
-        <v>0.04713416768390222</v>
+        <v>0.06389489928005787</v>
       </c>
       <c r="O4" s="5">
         <v>6385</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3031350212688925</v>
+        <v>0.3041407195268784</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1859315872673367</v>
+        <v>0.1847419056738017</v>
       </c>
       <c r="R4" s="5">
-        <v>6361</v>
+        <v>6359</v>
       </c>
       <c r="S4" s="5">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -16687,22 +16687,22 @@
         <v>17</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.04293669532801547</v>
+        <v>0.1413432961018657</v>
       </c>
       <c r="O5" s="5">
         <v>6337</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4512607255560511</v>
+        <v>0.4146552419402401</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3608433327173108</v>
+        <v>0.2985835136380928</v>
       </c>
       <c r="R5" s="5">
-        <v>6325</v>
+        <v>6311</v>
       </c>
       <c r="S5" s="5">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -16746,16 +16746,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.2728218757498075</v>
+        <v>0.2795587466661722</v>
       </c>
       <c r="O6" s="5">
         <v>4902</v>
       </c>
       <c r="P6" s="4">
-        <v>0.202836189379826</v>
+        <v>0.2034218638596338</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1008011324581678</v>
+        <v>0.1006037747561971</v>
       </c>
       <c r="R6" s="5">
         <v>4901</v>
@@ -16805,16 +16805,16 @@
         <v>1</v>
       </c>
       <c r="N7" s="4">
-        <v>0.02771721536978095</v>
+        <v>0.05384860989125073</v>
       </c>
       <c r="O7" s="5">
         <v>4416</v>
       </c>
       <c r="P7" s="4">
-        <v>0.284790730160357</v>
+        <v>0.2860700853191754</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1517729543294234</v>
+        <v>0.1499553851740459</v>
       </c>
       <c r="R7" s="5">
         <v>4415</v>
@@ -16864,16 +16864,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.2240785982340726</v>
+        <v>0.2623714142326889</v>
       </c>
       <c r="O8" s="5">
         <v>1304</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3031287680417479</v>
+        <v>0.3081129134423707</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.119621664039969</v>
+        <v>0.1146159486036342</v>
       </c>
       <c r="R8" s="5">
         <v>1304</v>
@@ -16923,16 +16923,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.06052935079528276</v>
+        <v>-0.01082888182919106</v>
       </c>
       <c r="O9" s="5">
         <v>1275</v>
       </c>
       <c r="P9" s="4">
-        <v>0.3322048536326241</v>
+        <v>0.333068997514215</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1595944286846736</v>
+        <v>0.1514864804016392</v>
       </c>
       <c r="R9" s="5">
         <v>1275</v>
@@ -16982,22 +16982,22 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.1185477425393637</v>
+        <v>0.1344002564802622</v>
       </c>
       <c r="O10" s="5">
         <v>1318</v>
       </c>
       <c r="P10" s="4">
-        <v>0.07649689892350679</v>
+        <v>0.07557086670092786</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.04905281639817989</v>
+        <v>0.04472311665489782</v>
       </c>
       <c r="R10" s="5">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="S10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="25" customHeight="1">
@@ -17041,16 +17041,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.06801243782481665</v>
+        <v>-0.01458473488675871</v>
       </c>
       <c r="O11" s="5">
         <v>1286</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2926095039153322</v>
+        <v>0.2914766222975059</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1783445255295821</v>
+        <v>0.1694124236138896</v>
       </c>
       <c r="R11" s="5">
         <v>1286</v>
@@ -17100,16 +17100,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.001395853352762737</v>
+        <v>0.05888001752458472</v>
       </c>
       <c r="O12" s="5">
         <v>1148</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2803029930771096</v>
+        <v>0.2827181362323275</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1444428631539893</v>
+        <v>0.1338643365688099</v>
       </c>
       <c r="R12" s="5">
         <v>1148</v>
@@ -17159,16 +17159,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.08714847457981793</v>
+        <v>0.1301736672393492</v>
       </c>
       <c r="O13" s="5">
         <v>1128</v>
       </c>
       <c r="P13" s="4">
-        <v>0.1485137869317746</v>
+        <v>0.1439709097528202</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1045698163070257</v>
+        <v>0.09486744235396574</v>
       </c>
       <c r="R13" s="5">
         <v>1128</v>
@@ -17218,16 +17218,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.1606927352922423</v>
+        <v>0.1702538876262452</v>
       </c>
       <c r="O14" s="5">
         <v>1034</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1719670838035285</v>
+        <v>0.1725651144291663</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.06730655845290159</v>
+        <v>0.0665836566070597</v>
       </c>
       <c r="R14" s="5">
         <v>1034</v>
@@ -17400,16 +17400,16 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0405436028297752</v>
+        <v>-0.03240638791706374</v>
       </c>
       <c r="O3" s="5">
         <v>7522</v>
       </c>
       <c r="P3" s="4">
-        <v>0.166395372158985</v>
+        <v>0.1670449621288402</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08104043666329537</v>
+        <v>0.08070207007297961</v>
       </c>
       <c r="R3" s="5">
         <v>7518</v>
@@ -17459,16 +17459,16 @@
         <v>23</v>
       </c>
       <c r="N4" s="4">
-        <v>0.06041350970565892</v>
+        <v>0.08598119837733975</v>
       </c>
       <c r="O4" s="5">
         <v>6337</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3094009073007152</v>
+        <v>0.3105719320861957</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1811691585388981</v>
+        <v>0.1794782779122429</v>
       </c>
       <c r="R4" s="5">
         <v>6311</v>
@@ -17518,22 +17518,22 @@
         <v>14</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.0153560118982409</v>
+        <v>0.1684999396204034</v>
       </c>
       <c r="O5" s="5">
         <v>6307</v>
       </c>
       <c r="P5" s="4">
-        <v>0.447256341612693</v>
+        <v>0.4144863567620924</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3512383518600393</v>
+        <v>0.2916336026561063</v>
       </c>
       <c r="R5" s="5">
-        <v>6294</v>
+        <v>6280</v>
       </c>
       <c r="S5" s="5">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -17577,16 +17577,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.2868823007507785</v>
+        <v>0.2936672114628323</v>
       </c>
       <c r="O6" s="5">
         <v>4885</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2113846097125456</v>
+        <v>0.2120303308662932</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1101962828619155</v>
+        <v>0.1100386938459912</v>
       </c>
       <c r="R6" s="5">
         <v>4884</v>
@@ -17636,22 +17636,22 @@
         <v>1</v>
       </c>
       <c r="N7" s="4">
-        <v>0.09085876266326935</v>
+        <v>0.1173253407623633</v>
       </c>
       <c r="O7" s="5">
         <v>4403</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2882497182398429</v>
+        <v>0.289880171987992</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1467588501557895</v>
+        <v>0.1444628168026527</v>
       </c>
       <c r="R7" s="5">
-        <v>4402</v>
+        <v>4401</v>
       </c>
       <c r="S7" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="25" customHeight="1">
@@ -17695,16 +17695,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.2113264888857294</v>
+        <v>0.2360292191996156</v>
       </c>
       <c r="O8" s="5">
         <v>1263</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3300961186388767</v>
+        <v>0.3347096066876069</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1155974635640266</v>
+        <v>0.1132609161387111</v>
       </c>
       <c r="R8" s="5">
         <v>1263</v>
@@ -17754,16 +17754,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.0695175551847763</v>
+        <v>-0.01690242787572771</v>
       </c>
       <c r="O9" s="5">
         <v>1274</v>
       </c>
       <c r="P9" s="4">
-        <v>0.3345401732090888</v>
+        <v>0.3352907017411196</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1628804766144358</v>
+        <v>0.1546373239883304</v>
       </c>
       <c r="R9" s="5">
         <v>1274</v>
@@ -17813,22 +17813,22 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.1004141360607184</v>
+        <v>0.1171549422270957</v>
       </c>
       <c r="O10" s="5">
         <v>1324</v>
       </c>
       <c r="P10" s="4">
-        <v>0.08002982856581309</v>
+        <v>0.07892725833329156</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.05100931748625055</v>
+        <v>0.0462892087062241</v>
       </c>
       <c r="R10" s="5">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="S10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="25" customHeight="1">
@@ -17872,16 +17872,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.01431008865911351</v>
+        <v>0.04328773416452059</v>
       </c>
       <c r="O11" s="5">
         <v>1284</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2979225857887666</v>
+        <v>0.2969750434606305</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1773712914920887</v>
+        <v>0.1686196694306361</v>
       </c>
       <c r="R11" s="5">
         <v>1284</v>
@@ -17931,16 +17931,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.03166048019476307</v>
+        <v>0.08405662939270542</v>
       </c>
       <c r="O12" s="5">
         <v>1142</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2843383155112982</v>
+        <v>0.2862565931364321</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1426922250595831</v>
+        <v>0.1321684038359681</v>
       </c>
       <c r="R12" s="5">
         <v>1142</v>
@@ -17990,16 +17990,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.09951478304244021</v>
+        <v>0.1424644990364961</v>
       </c>
       <c r="O13" s="5">
         <v>1125</v>
       </c>
       <c r="P13" s="4">
-        <v>0.1581393395898608</v>
+        <v>0.1541187236580385</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1068204169363861</v>
+        <v>0.0972032014460787</v>
       </c>
       <c r="R13" s="5">
         <v>1125</v>
@@ -18049,16 +18049,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.1554787268109578</v>
+        <v>0.1692270606718864</v>
       </c>
       <c r="O14" s="5">
         <v>1043</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1683875755342626</v>
+        <v>0.1686600904425497</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.06593095476759057</v>
+        <v>0.06454003675207173</v>
       </c>
       <c r="R14" s="5">
         <v>1043</v>
@@ -19279,13 +19279,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="5">
-        <v>32175</v>
+        <v>36344</v>
       </c>
       <c r="C3" s="5">
         <v>2903</v>
       </c>
       <c r="D3" s="5">
-        <v>10052</v>
+        <v>5883</v>
       </c>
       <c r="E3" s="5">
         <v>1371</v>
@@ -19294,7 +19294,7 @@
         <v>3568</v>
       </c>
       <c r="G3" s="5">
-        <v>5113</v>
+        <v>944</v>
       </c>
       <c r="H3" s="5">
         <v>1371</v>
@@ -19323,13 +19323,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="5">
-        <v>34676</v>
+        <v>34874</v>
       </c>
       <c r="C4" s="5">
         <v>3775</v>
       </c>
       <c r="D4" s="5">
-        <v>6679</v>
+        <v>6481</v>
       </c>
       <c r="E4" s="5">
         <v>2057</v>
@@ -19338,7 +19338,7 @@
         <v>3845</v>
       </c>
       <c r="G4" s="5">
-        <v>777</v>
+        <v>579</v>
       </c>
       <c r="H4" s="5">
         <v>2055</v>
@@ -19367,13 +19367,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="5">
-        <v>33797</v>
+        <v>33794</v>
       </c>
       <c r="C5" s="5">
         <v>4035</v>
       </c>
       <c r="D5" s="5">
-        <v>7298</v>
+        <v>7301</v>
       </c>
       <c r="E5" s="5">
         <v>1544</v>
@@ -19382,7 +19382,7 @@
         <v>5223</v>
       </c>
       <c r="G5" s="5">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="H5" s="5">
         <v>1544</v>
@@ -19411,13 +19411,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <v>32287</v>
+        <v>36211</v>
       </c>
       <c r="C6" s="5">
         <v>2847</v>
       </c>
       <c r="D6" s="5">
-        <v>9996</v>
+        <v>6072</v>
       </c>
       <c r="E6" s="5">
         <v>1092</v>
@@ -19426,7 +19426,7 @@
         <v>3671</v>
       </c>
       <c r="G6" s="5">
-        <v>5233</v>
+        <v>1309</v>
       </c>
       <c r="H6" s="5">
         <v>1092</v>
@@ -19455,13 +19455,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="5">
-        <v>33193</v>
+        <v>33141</v>
       </c>
       <c r="C7" s="5">
         <v>4759</v>
       </c>
       <c r="D7" s="5">
-        <v>7178</v>
+        <v>7230</v>
       </c>
       <c r="E7" s="5">
         <v>1271</v>
@@ -19470,7 +19470,7 @@
         <v>5370</v>
       </c>
       <c r="G7" s="5">
-        <v>537</v>
+        <v>589</v>
       </c>
       <c r="H7" s="5">
         <v>1271</v>
@@ -19499,13 +19499,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="5">
-        <v>31744</v>
+        <v>35590</v>
       </c>
       <c r="C8" s="5">
         <v>2411</v>
       </c>
       <c r="D8" s="5">
-        <v>10975</v>
+        <v>7129</v>
       </c>
       <c r="E8" s="5">
         <v>1059</v>
@@ -19514,7 +19514,7 @@
         <v>4092</v>
       </c>
       <c r="G8" s="5">
-        <v>5824</v>
+        <v>1978</v>
       </c>
       <c r="H8" s="5">
         <v>1059</v>
@@ -19543,13 +19543,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>31180</v>
+        <v>35064</v>
       </c>
       <c r="C9" s="5">
         <v>2677</v>
       </c>
       <c r="D9" s="5">
-        <v>11273</v>
+        <v>7389</v>
       </c>
       <c r="E9" s="5">
         <v>1468</v>
@@ -19558,7 +19558,7 @@
         <v>4644</v>
       </c>
       <c r="G9" s="5">
-        <v>5161</v>
+        <v>1277</v>
       </c>
       <c r="H9" s="5">
         <v>1468</v>
@@ -19587,13 +19587,13 @@
         <v>24</v>
       </c>
       <c r="B10" s="5">
-        <v>36123</v>
+        <v>35992</v>
       </c>
       <c r="C10" s="5">
         <v>3652</v>
       </c>
       <c r="D10" s="5">
-        <v>5355</v>
+        <v>5486</v>
       </c>
       <c r="E10" s="5">
         <v>721</v>
@@ -19602,7 +19602,7 @@
         <v>3865</v>
       </c>
       <c r="G10" s="5">
-        <v>769</v>
+        <v>900</v>
       </c>
       <c r="H10" s="5">
         <v>721</v>
@@ -19631,13 +19631,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="5">
-        <v>38283</v>
+        <v>38275</v>
       </c>
       <c r="C11" s="5">
         <v>2263</v>
       </c>
       <c r="D11" s="5">
-        <v>4584</v>
+        <v>4592</v>
       </c>
       <c r="E11" s="5">
         <v>356</v>
@@ -19646,7 +19646,7 @@
         <v>4160</v>
       </c>
       <c r="G11" s="5">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H11" s="5">
         <v>356</v>
@@ -19675,13 +19675,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>37191</v>
+        <v>37022</v>
       </c>
       <c r="C12" s="5">
         <v>2887</v>
       </c>
       <c r="D12" s="5">
-        <v>5052</v>
+        <v>5221</v>
       </c>
       <c r="E12" s="5">
         <v>576</v>
@@ -19690,7 +19690,7 @@
         <v>3741</v>
       </c>
       <c r="G12" s="5">
-        <v>735</v>
+        <v>904</v>
       </c>
       <c r="H12" s="5">
         <v>576</v>
@@ -19719,13 +19719,13 @@
         <v>27</v>
       </c>
       <c r="B13" s="5">
-        <v>35210</v>
+        <v>35124</v>
       </c>
       <c r="C13" s="5">
         <v>4237</v>
       </c>
       <c r="D13" s="5">
-        <v>5683</v>
+        <v>5769</v>
       </c>
       <c r="E13" s="5">
         <v>488</v>
@@ -19734,7 +19734,7 @@
         <v>4063</v>
       </c>
       <c r="G13" s="5">
-        <v>1132</v>
+        <v>1218</v>
       </c>
       <c r="H13" s="5">
         <v>488</v>
@@ -19763,13 +19763,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="5">
-        <v>35636</v>
+        <v>35629</v>
       </c>
       <c r="C14" s="5">
         <v>2548</v>
       </c>
       <c r="D14" s="5">
-        <v>6946</v>
+        <v>6953</v>
       </c>
       <c r="E14" s="5">
         <v>815</v>
@@ -19778,7 +19778,7 @@
         <v>5957</v>
       </c>
       <c r="G14" s="5">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="H14" s="5">
         <v>813</v>
@@ -19807,13 +19807,13 @@
         <v>29</v>
       </c>
       <c r="B15" s="5">
-        <v>34334</v>
+        <v>34341</v>
       </c>
       <c r="C15" s="5">
         <v>4470</v>
       </c>
       <c r="D15" s="5">
-        <v>6326</v>
+        <v>6319</v>
       </c>
       <c r="E15" s="5">
         <v>1851</v>
@@ -19822,7 +19822,7 @@
         <v>3885</v>
       </c>
       <c r="G15" s="5">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="H15" s="5">
         <v>1851</v>
@@ -19851,13 +19851,13 @@
         <v>30</v>
       </c>
       <c r="B16" s="5">
-        <v>32127</v>
+        <v>36197</v>
       </c>
       <c r="C16" s="5">
         <v>2997</v>
       </c>
       <c r="D16" s="5">
-        <v>10006</v>
+        <v>5936</v>
       </c>
       <c r="E16" s="5">
         <v>1345</v>
@@ -19866,7 +19866,7 @@
         <v>3250</v>
       </c>
       <c r="G16" s="5">
-        <v>5411</v>
+        <v>1341</v>
       </c>
       <c r="H16" s="5">
         <v>1345</v>
@@ -19895,13 +19895,13 @@
         <v>31</v>
       </c>
       <c r="B17" s="5">
-        <v>32650</v>
+        <v>36622</v>
       </c>
       <c r="C17" s="5">
         <v>2722</v>
       </c>
       <c r="D17" s="5">
-        <v>9758</v>
+        <v>5786</v>
       </c>
       <c r="E17" s="5">
         <v>1603</v>
@@ -19910,7 +19910,7 @@
         <v>3267</v>
       </c>
       <c r="G17" s="5">
-        <v>4888</v>
+        <v>916</v>
       </c>
       <c r="H17" s="5">
         <v>1603</v>
@@ -19939,13 +19939,13 @@
         <v>32</v>
       </c>
       <c r="B18" s="5">
-        <v>33405</v>
+        <v>33438</v>
       </c>
       <c r="C18" s="5">
         <v>4009</v>
       </c>
       <c r="D18" s="5">
-        <v>7716</v>
+        <v>7683</v>
       </c>
       <c r="E18" s="5">
         <v>1207</v>
@@ -19954,7 +19954,7 @@
         <v>5529</v>
       </c>
       <c r="G18" s="5">
-        <v>980</v>
+        <v>947</v>
       </c>
       <c r="H18" s="5">
         <v>1207</v>
@@ -19983,13 +19983,13 @@
         <v>33</v>
       </c>
       <c r="B19" s="5">
-        <v>31575</v>
+        <v>35416</v>
       </c>
       <c r="C19" s="5">
         <v>3281</v>
       </c>
       <c r="D19" s="5">
-        <v>10274</v>
+        <v>6433</v>
       </c>
       <c r="E19" s="5">
         <v>1793</v>
@@ -19998,7 +19998,7 @@
         <v>3146</v>
       </c>
       <c r="G19" s="5">
-        <v>5335</v>
+        <v>1494</v>
       </c>
       <c r="H19" s="5">
         <v>1792</v>
@@ -20027,13 +20027,13 @@
         <v>34</v>
       </c>
       <c r="B20" s="5">
-        <v>31546</v>
+        <v>34650</v>
       </c>
       <c r="C20" s="5">
         <v>2627</v>
       </c>
       <c r="D20" s="5">
-        <v>10957</v>
+        <v>7853</v>
       </c>
       <c r="E20" s="5">
         <v>1592</v>
@@ -20042,7 +20042,7 @@
         <v>3981</v>
       </c>
       <c r="G20" s="5">
-        <v>5384</v>
+        <v>2280</v>
       </c>
       <c r="H20" s="5">
         <v>1592</v>
@@ -20071,13 +20071,13 @@
         <v>35</v>
       </c>
       <c r="B21" s="5">
-        <v>36349</v>
+        <v>36320</v>
       </c>
       <c r="C21" s="5">
         <v>2975</v>
       </c>
       <c r="D21" s="5">
-        <v>5806</v>
+        <v>5835</v>
       </c>
       <c r="E21" s="5">
         <v>1557</v>
@@ -20086,7 +20086,7 @@
         <v>3625</v>
       </c>
       <c r="G21" s="5">
-        <v>624</v>
+        <v>653</v>
       </c>
       <c r="H21" s="5">
         <v>1557</v>
@@ -20115,13 +20115,13 @@
         <v>36</v>
       </c>
       <c r="B22" s="5">
-        <v>36921</v>
+        <v>36878</v>
       </c>
       <c r="C22" s="5">
         <v>2883</v>
       </c>
       <c r="D22" s="5">
-        <v>5326</v>
+        <v>5369</v>
       </c>
       <c r="E22" s="5">
         <v>864</v>
@@ -20130,7 +20130,7 @@
         <v>3374</v>
       </c>
       <c r="G22" s="5">
-        <v>1088</v>
+        <v>1131</v>
       </c>
       <c r="H22" s="5">
         <v>864</v>
@@ -20159,13 +20159,13 @@
         <v>37</v>
       </c>
       <c r="B23" s="5">
-        <v>38354</v>
+        <v>38098</v>
       </c>
       <c r="C23" s="5">
         <v>1909</v>
       </c>
       <c r="D23" s="5">
-        <v>4867</v>
+        <v>5123</v>
       </c>
       <c r="E23" s="5">
         <v>742</v>
@@ -20174,7 +20174,7 @@
         <v>4039</v>
       </c>
       <c r="G23" s="5">
-        <v>86</v>
+        <v>342</v>
       </c>
       <c r="H23" s="5">
         <v>742</v>
@@ -20203,13 +20203,13 @@
         <v>38</v>
       </c>
       <c r="B24" s="5">
-        <v>38056</v>
+        <v>38039</v>
       </c>
       <c r="C24" s="5">
         <v>2033</v>
       </c>
       <c r="D24" s="5">
-        <v>5041</v>
+        <v>5058</v>
       </c>
       <c r="E24" s="5">
         <v>878</v>
@@ -20218,7 +20218,7 @@
         <v>4121</v>
       </c>
       <c r="G24" s="5">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="H24" s="5">
         <v>877</v>
@@ -20247,13 +20247,13 @@
         <v>39</v>
       </c>
       <c r="B25" s="5">
-        <v>37864</v>
+        <v>37848</v>
       </c>
       <c r="C25" s="5">
         <v>2038</v>
       </c>
       <c r="D25" s="5">
-        <v>5228</v>
+        <v>5244</v>
       </c>
       <c r="E25" s="5">
         <v>804</v>
@@ -20262,7 +20262,7 @@
         <v>4379</v>
       </c>
       <c r="G25" s="5">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="H25" s="5">
         <v>804</v>
@@ -20445,22 +20445,22 @@
         <v>33</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4954515584076766</v>
+        <v>-0.4355181993483228</v>
       </c>
       <c r="O3" s="5">
         <v>7849</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2038734804046587</v>
+        <v>0.1986108602765691</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1647289753827454</v>
+        <v>0.1543423260286286</v>
       </c>
       <c r="R3" s="5">
-        <v>7825</v>
+        <v>7829</v>
       </c>
       <c r="S3" s="5">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -20504,22 +20504,22 @@
         <v>99</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.7978818480067343</v>
+        <v>-0.7220220261329615</v>
       </c>
       <c r="O4" s="5">
         <v>6635</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3865238921594715</v>
+        <v>0.385025144673986</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3064171918498056</v>
+        <v>0.2992648137015401</v>
       </c>
       <c r="R4" s="5">
-        <v>6618</v>
+        <v>6619</v>
       </c>
       <c r="S4" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -20563,22 +20563,22 @@
         <v>866</v>
       </c>
       <c r="N5" s="4">
-        <v>2.997795134278833</v>
+        <v>-0.5860314482440288</v>
       </c>
       <c r="O5" s="5">
         <v>5175</v>
       </c>
       <c r="P5" s="4">
-        <v>8.422338431067729</v>
+        <v>7.537539819361466</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.9316822650066466</v>
+        <v>0.2530483370570455</v>
       </c>
       <c r="R5" s="5">
-        <v>133</v>
+        <v>4297</v>
       </c>
       <c r="S5" s="5">
-        <v>5042</v>
+        <v>878</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -20622,16 +20622,16 @@
         <v>6</v>
       </c>
       <c r="N6" s="4">
-        <v>0.1610333721817252</v>
+        <v>0.1580931443313887</v>
       </c>
       <c r="O6" s="5">
         <v>5153</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2020701174077177</v>
+        <v>0.2017845630858522</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1392601988566329</v>
+        <v>0.1392394708391502</v>
       </c>
       <c r="R6" s="5">
         <v>5148</v>
@@ -20681,16 +20681,16 @@
         <v>28</v>
       </c>
       <c r="N7" s="4">
-        <v>1.19692375326605</v>
+        <v>1.193913899883128</v>
       </c>
       <c r="O7" s="5">
         <v>4611</v>
       </c>
       <c r="P7" s="4">
-        <v>0.290429659125109</v>
+        <v>0.2901341561175839</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1964976477928196</v>
+        <v>0.1964862489607682</v>
       </c>
       <c r="R7" s="5">
         <v>4611</v>
@@ -20740,16 +20740,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.2799848209329939</v>
+        <v>-0.2521297026162017</v>
       </c>
       <c r="O8" s="5">
         <v>1337</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2785665205927734</v>
+        <v>0.2823119172131041</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1207519286218648</v>
+        <v>0.1184024237953633</v>
       </c>
       <c r="R8" s="5">
         <v>1337</v>
@@ -20799,16 +20799,16 @@
         <v>10</v>
       </c>
       <c r="N9" s="4">
-        <v>-1.164879742846634</v>
+        <v>-1.159800218218216</v>
       </c>
       <c r="O9" s="5">
         <v>1348</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2685246280519566</v>
+        <v>0.2689854758794648</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1430489845932239</v>
+        <v>0.1429561061265624</v>
       </c>
       <c r="R9" s="5">
         <v>1348</v>
@@ -20858,16 +20858,16 @@
         <v>23</v>
       </c>
       <c r="N10" s="4">
-        <v>-1.15458645759163</v>
+        <v>-1.368437323200766</v>
       </c>
       <c r="O10" s="5">
         <v>503</v>
       </c>
       <c r="P10" s="4">
-        <v>1.115054775100504</v>
+        <v>1.041516150712312</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.2479191960119084</v>
+        <v>0.1088228992663666</v>
       </c>
       <c r="R10" s="5">
         <v>479</v>
@@ -20917,16 +20917,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.6846704852872316</v>
+        <v>0.680436232489626</v>
       </c>
       <c r="O11" s="5">
         <v>1333</v>
       </c>
       <c r="P11" s="4">
-        <v>0.234439683510942</v>
+        <v>0.2340248241393355</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1477565496353762</v>
+        <v>0.1477096986899139</v>
       </c>
       <c r="R11" s="5">
         <v>1333</v>
@@ -20976,16 +20976,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.3417948003531608</v>
+        <v>0.3679481466249968</v>
       </c>
       <c r="O12" s="5">
         <v>1220</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2168025752845647</v>
+        <v>0.2190953838744404</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1333817507178565</v>
+        <v>0.1319619163360707</v>
       </c>
       <c r="R12" s="5">
         <v>1220</v>
@@ -21035,16 +21035,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.03448480193444346</v>
+        <v>0.06963619568290369</v>
       </c>
       <c r="O13" s="5">
         <v>1125</v>
       </c>
       <c r="P13" s="4">
-        <v>0.2096934099510077</v>
+        <v>0.2111393008963051</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1612154440591519</v>
+        <v>0.1588624659841661</v>
       </c>
       <c r="R13" s="5">
         <v>1125</v>
@@ -21094,16 +21094,16 @@
         <v>1</v>
       </c>
       <c r="N14" s="4">
-        <v>-1.010548244091493</v>
+        <v>-1.04872462118081</v>
       </c>
       <c r="O14" s="5">
         <v>999</v>
       </c>
       <c r="P14" s="4">
-        <v>0.5578292941037873</v>
+        <v>0.5485645876953149</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.122879628300881</v>
+        <v>0.1182693427720513</v>
       </c>
       <c r="R14" s="5">
         <v>998</v>
@@ -21276,16 +21276,16 @@
         <v>25</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2577584048604898</v>
+        <v>-0.2360144107097142</v>
       </c>
       <c r="O3" s="5">
         <v>7646</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2072116824064396</v>
+        <v>0.2083940305696913</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1714639010855776</v>
+        <v>0.1703819470254687</v>
       </c>
       <c r="R3" s="5">
         <v>7627</v>
@@ -21335,16 +21335,16 @@
         <v>7</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1558330403091523</v>
+        <v>-0.16723425224518</v>
       </c>
       <c r="O4" s="5">
         <v>6322</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4484242646325825</v>
+        <v>0.4470848003551369</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3117444546555377</v>
+        <v>0.3115521034522503</v>
       </c>
       <c r="R4" s="5">
         <v>6311</v>
@@ -21394,22 +21394,22 @@
         <v>543</v>
       </c>
       <c r="N5" s="4">
-        <v>1.44341655274437</v>
+        <v>0.3580252183020889</v>
       </c>
       <c r="O5" s="5">
         <v>4614</v>
       </c>
       <c r="P5" s="4">
-        <v>4.723148358157692</v>
+        <v>4.525268141752743</v>
       </c>
       <c r="Q5" s="4">
-        <v>1.12738013379984</v>
+        <v>0.335386409239583</v>
       </c>
       <c r="R5" s="5">
-        <v>3883</v>
+        <v>4082</v>
       </c>
       <c r="S5" s="5">
-        <v>731</v>
+        <v>532</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -21453,16 +21453,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>0.2380126214739629</v>
+        <v>0.2300299382604294</v>
       </c>
       <c r="O6" s="5">
         <v>4946</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2931874887335587</v>
+        <v>0.2922956463684993</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2150610973906102</v>
+        <v>0.2149532931235969</v>
       </c>
       <c r="R6" s="5">
         <v>4943</v>
@@ -21512,16 +21512,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.2060632889123346</v>
+        <v>0.1990766145254383</v>
       </c>
       <c r="O7" s="5">
         <v>4358</v>
       </c>
       <c r="P7" s="4">
-        <v>0.3843653261084689</v>
+        <v>0.3834542298179636</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2083162039464366</v>
+        <v>0.2082334973388538</v>
       </c>
       <c r="R7" s="5">
         <v>4358</v>
@@ -21571,16 +21571,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.2274600021093584</v>
+        <v>-0.2044509601774962</v>
       </c>
       <c r="O8" s="5">
         <v>1165</v>
       </c>
       <c r="P8" s="4">
-        <v>0.296694238818996</v>
+        <v>0.3012200545044792</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1761615104585192</v>
+        <v>0.1753424609938065</v>
       </c>
       <c r="R8" s="5">
         <v>1165</v>
@@ -21630,16 +21630,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.5285835083800116</v>
+        <v>-0.510220733513961</v>
       </c>
       <c r="O9" s="5">
         <v>1191</v>
       </c>
       <c r="P9" s="4">
-        <v>0.4660941241707178</v>
+        <v>0.46925418137953</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2306790161708193</v>
+        <v>0.2301588302284273</v>
       </c>
       <c r="R9" s="5">
         <v>1191</v>
@@ -21689,22 +21689,22 @@
         <v>14</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.02153538499089859</v>
+        <v>-0.0725180805383161</v>
       </c>
       <c r="O10" s="5">
         <v>996</v>
       </c>
       <c r="P10" s="4">
-        <v>0.2117424754502272</v>
+        <v>0.2056080161985832</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.09430886286323906</v>
+        <v>0.08032094419423344</v>
       </c>
       <c r="R10" s="5">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="S10" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="25" customHeight="1">
@@ -21748,16 +21748,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.1377114241319211</v>
+        <v>-0.147152336137907</v>
       </c>
       <c r="O11" s="5">
         <v>1252</v>
       </c>
       <c r="P11" s="4">
-        <v>0.4152253589160753</v>
+        <v>0.4138703089652692</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.2336688554239062</v>
+        <v>0.2335273680063695</v>
       </c>
       <c r="R11" s="5">
         <v>1252</v>
@@ -21807,16 +21807,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.4986820410044125</v>
+        <v>-0.4926338135256287</v>
       </c>
       <c r="O12" s="5">
         <v>1095</v>
       </c>
       <c r="P12" s="4">
-        <v>0.3338816343266464</v>
+        <v>0.3349536119387405</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.2119276860082561</v>
+        <v>0.2118771272328164</v>
       </c>
       <c r="R12" s="5">
         <v>1095</v>
@@ -21866,16 +21866,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.3723372934372821</v>
+        <v>-0.3556122559676567</v>
       </c>
       <c r="O13" s="5">
         <v>952</v>
       </c>
       <c r="P13" s="4">
-        <v>0.244060739255327</v>
+        <v>0.2471748328119239</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.155951526695985</v>
+        <v>0.1552737251013203</v>
       </c>
       <c r="R13" s="5">
         <v>952</v>
@@ -21925,16 +21925,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.036554533887349</v>
+        <v>0.03963055758424616</v>
       </c>
       <c r="O14" s="5">
         <v>916</v>
       </c>
       <c r="P14" s="4">
-        <v>0.4682723234206209</v>
+        <v>0.4687721485230905</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1637611069216377</v>
+        <v>0.1637433992373398</v>
       </c>
       <c r="R14" s="5">
         <v>916</v>
@@ -22107,16 +22107,16 @@
         <v>30</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3255402605999173</v>
+        <v>-0.3024847258948569</v>
       </c>
       <c r="O3" s="5">
         <v>6520</v>
       </c>
       <c r="P3" s="4">
-        <v>0.32584800271508</v>
+        <v>0.3279984980204212</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2677084520263006</v>
+        <v>0.2670291083599465</v>
       </c>
       <c r="R3" s="5">
         <v>6503</v>
@@ -22166,16 +22166,16 @@
         <v>89</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2676332313356066</v>
+        <v>-0.2877781224615319</v>
       </c>
       <c r="O4" s="5">
         <v>5855</v>
       </c>
       <c r="P4" s="4">
-        <v>0.620462358554282</v>
+        <v>0.6178764679043037</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4521878066882317</v>
+        <v>0.4518402098881584</v>
       </c>
       <c r="R4" s="5">
         <v>5780</v>
@@ -22225,22 +22225,22 @@
         <v>696</v>
       </c>
       <c r="N5" s="4">
-        <v>0.8422416881633807</v>
+        <v>0.8243863328172552</v>
       </c>
       <c r="O5" s="5">
         <v>5915</v>
       </c>
       <c r="P5" s="4">
-        <v>0.8491453625223468</v>
+        <v>0.8477063777486739</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6034597511715908</v>
+        <v>0.6025521263922835</v>
       </c>
       <c r="R5" s="5">
-        <v>5485</v>
+        <v>5482</v>
       </c>
       <c r="S5" s="5">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -22284,16 +22284,16 @@
         <v>3</v>
       </c>
       <c r="N6" s="4">
-        <v>0.2114753292937058</v>
+        <v>0.2446878877016729</v>
       </c>
       <c r="O6" s="5">
         <v>4643</v>
       </c>
       <c r="P6" s="4">
-        <v>0.3812642841333883</v>
+        <v>0.3844399278542437</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2912151928962664</v>
+        <v>0.289960407151206</v>
       </c>
       <c r="R6" s="5">
         <v>4640</v>
@@ -22343,16 +22343,16 @@
         <v>2</v>
       </c>
       <c r="N7" s="4">
-        <v>0.263257208190192</v>
+        <v>0.2550940483924933</v>
       </c>
       <c r="O7" s="5">
         <v>4028</v>
       </c>
       <c r="P7" s="4">
-        <v>0.5860737692503265</v>
+        <v>0.5848644651925982</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.4103602630752819</v>
+        <v>0.4103173967590063</v>
       </c>
       <c r="R7" s="5">
         <v>4027</v>
@@ -22402,16 +22402,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.1919783854306176</v>
+        <v>-0.1752227204061683</v>
       </c>
       <c r="O8" s="5">
         <v>1169</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3840608883834947</v>
+        <v>0.3869439416820414</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2414204953758282</v>
+        <v>0.2410510160350291</v>
       </c>
       <c r="R8" s="5">
         <v>1169</v>
@@ -22461,16 +22461,16 @@
         <v>3</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.7354755481426259</v>
+        <v>-0.7353132820344399</v>
       </c>
       <c r="O9" s="5">
         <v>1129</v>
       </c>
       <c r="P9" s="4">
-        <v>0.5511189909059566</v>
+        <v>0.5511529438913665</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2379097174223108</v>
+        <v>0.2379095736967943</v>
       </c>
       <c r="R9" s="5">
         <v>1129</v>
@@ -22520,16 +22520,16 @@
         <v>4</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.1631474145890683</v>
+        <v>-0.1453924400974529</v>
       </c>
       <c r="O10" s="5">
         <v>958</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1700928992468048</v>
+        <v>0.1738036485856157</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.09368101245838283</v>
+        <v>0.09230995533176556</v>
       </c>
       <c r="R10" s="5">
         <v>957</v>
@@ -22579,16 +22579,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.4974542078678665</v>
+        <v>-0.514722669098802</v>
       </c>
       <c r="O11" s="5">
         <v>1200</v>
       </c>
       <c r="P11" s="4">
-        <v>0.4403894894916745</v>
+        <v>0.4377384162154269</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.2603038305587444</v>
+        <v>0.2599753855410497</v>
       </c>
       <c r="R11" s="5">
         <v>1200</v>
@@ -22638,16 +22638,16 @@
         <v>1</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.8564230370495944</v>
+        <v>-0.8588490809261771</v>
       </c>
       <c r="O12" s="5">
         <v>1037</v>
       </c>
       <c r="P12" s="4">
-        <v>0.3621160507328415</v>
+        <v>0.3616123847049827</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.2314043993745295</v>
+        <v>0.2314009062247928</v>
       </c>
       <c r="R12" s="5">
         <v>1037</v>
@@ -22697,16 +22697,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.7834754509499093</v>
+        <v>-0.768761718842228</v>
       </c>
       <c r="O13" s="5">
         <v>982</v>
       </c>
       <c r="P13" s="4">
-        <v>0.2425486862979185</v>
+        <v>0.2445040264356463</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1930056811713469</v>
+        <v>0.1926855976903231</v>
       </c>
       <c r="R13" s="5">
         <v>982</v>
@@ -22756,16 +22756,16 @@
         <v>6</v>
       </c>
       <c r="N14" s="4">
-        <v>0.286898516160817</v>
+        <v>0.2547592640959238</v>
       </c>
       <c r="O14" s="5">
         <v>892</v>
       </c>
       <c r="P14" s="4">
-        <v>0.3665682715757317</v>
+        <v>0.3583448228967073</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.2064432269053794</v>
+        <v>0.2044372567250486</v>
       </c>
       <c r="R14" s="5">
         <v>888</v>
@@ -22938,16 +22938,16 @@
         <v>21</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2156792086484522</v>
+        <v>-0.1966165097483383</v>
       </c>
       <c r="O3" s="5">
         <v>7593</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1750531996694503</v>
+        <v>0.1759037461186198</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.130101919361367</v>
+        <v>0.1289397800410676</v>
       </c>
       <c r="R3" s="5">
         <v>7577</v>
@@ -22997,16 +22997,16 @@
         <v>10</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1996076597604101</v>
+        <v>-0.1942684310397453</v>
       </c>
       <c r="O4" s="5">
         <v>6461</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3242724584775575</v>
+        <v>0.3246116712203159</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2342677574241249</v>
+        <v>0.2342274871433845</v>
       </c>
       <c r="R4" s="5">
         <v>6450</v>
@@ -23056,22 +23056,22 @@
         <v>1274</v>
       </c>
       <c r="N5" s="4">
-        <v>2.673740430027501</v>
+        <v>0.1314052454619627</v>
       </c>
       <c r="O5" s="5">
         <v>5712</v>
       </c>
       <c r="P5" s="4">
-        <v>4.752310712763547</v>
+        <v>3.920161847243664</v>
       </c>
       <c r="Q5" s="4">
-        <v>1.026348376006197</v>
+        <v>0.2608141234600894</v>
       </c>
       <c r="R5" s="5">
-        <v>533</v>
+        <v>4460</v>
       </c>
       <c r="S5" s="5">
-        <v>5179</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -23115,16 +23115,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>0.08784387967227152</v>
+        <v>0.09284488627048404</v>
       </c>
       <c r="O6" s="5">
         <v>5096</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2237154182363031</v>
+        <v>0.2240047234595249</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1805092833373824</v>
+        <v>0.1804512540546828</v>
       </c>
       <c r="R6" s="5">
         <v>5094</v>
@@ -23174,16 +23174,16 @@
         <v>2</v>
       </c>
       <c r="N7" s="4">
-        <v>0.2211496789634452</v>
+        <v>0.2127474581602655</v>
       </c>
       <c r="O7" s="5">
         <v>4496</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2936714618801922</v>
+        <v>0.2928615340868788</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1951060809206627</v>
+        <v>0.195015851177008</v>
       </c>
       <c r="R7" s="5">
         <v>4495</v>
@@ -23233,16 +23233,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.1054618406875441</v>
+        <v>-0.09154097845851084</v>
       </c>
       <c r="O8" s="5">
         <v>1299</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3015564747922621</v>
+        <v>0.3039429534511552</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1403855359531639</v>
+        <v>0.139784576484821</v>
       </c>
       <c r="R8" s="5">
         <v>1299</v>
@@ -23292,16 +23292,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.4973362680967325</v>
+        <v>-0.4977618267539583</v>
       </c>
       <c r="O9" s="5">
         <v>1315</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2815806184151561</v>
+        <v>0.2815452523356795</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.152260717175157</v>
+        <v>0.1522603935564063</v>
       </c>
       <c r="R9" s="5">
         <v>1315</v>
@@ -23351,22 +23351,22 @@
         <v>21</v>
       </c>
       <c r="N10" s="4">
-        <v>0.05594741356105901</v>
+        <v>-0.06439091591880697</v>
       </c>
       <c r="O10" s="5">
         <v>854</v>
       </c>
       <c r="P10" s="4">
-        <v>0.3463063678965347</v>
+        <v>0.2946408451509929</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.2025035109500663</v>
+        <v>0.1482543432566691</v>
       </c>
       <c r="R10" s="5">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="S10" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="25" customHeight="1">
@@ -23410,16 +23410,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.1233477070982088</v>
+        <v>-0.1378520422058784</v>
       </c>
       <c r="O11" s="5">
         <v>1327</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2422613147379246</v>
+        <v>0.2409192796404185</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1498667018542231</v>
+        <v>0.149398608041861</v>
       </c>
       <c r="R11" s="5">
         <v>1327</v>
@@ -23469,16 +23469,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.175316211794344</v>
+        <v>-0.167784617554446</v>
       </c>
       <c r="O12" s="5">
         <v>1204</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2151365353773387</v>
+        <v>0.2159782452285961</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1245926917474741</v>
+        <v>0.1244104689524833</v>
       </c>
       <c r="R12" s="5">
         <v>1204</v>
@@ -23528,16 +23528,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.1560471313446316</v>
+        <v>-0.13560598324338</v>
       </c>
       <c r="O13" s="5">
         <v>1126</v>
       </c>
       <c r="P13" s="4">
-        <v>0.1792051936714311</v>
+        <v>0.1801760396928333</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.128315000862663</v>
+        <v>0.1272896136941984</v>
       </c>
       <c r="R13" s="5">
         <v>1126</v>
@@ -23587,22 +23587,22 @@
         <v>4</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.1210263200261921</v>
+        <v>-0.1403482395807032</v>
       </c>
       <c r="O14" s="5">
         <v>1037</v>
       </c>
       <c r="P14" s="4">
-        <v>0.3056756517307023</v>
+        <v>0.3030221901479105</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1249594666152859</v>
+        <v>0.1217285147300589</v>
       </c>
       <c r="R14" s="5">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="S14" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -23769,16 +23769,16 @@
         <v>23</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3047037636179238</v>
+        <v>-0.2997103733296456</v>
       </c>
       <c r="O3" s="5">
         <v>7069</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2809508790644784</v>
+        <v>0.2814186904577004</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2258008856228097</v>
+        <v>0.2257667489808071</v>
       </c>
       <c r="R3" s="5">
         <v>7058</v>
@@ -23828,22 +23828,22 @@
         <v>76</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1792685120756771</v>
+        <v>-0.2376071207036148</v>
       </c>
       <c r="O4" s="5">
         <v>5822</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6372962844108288</v>
+        <v>0.6284826441886572</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.461199487858413</v>
+        <v>0.4575514317844622</v>
       </c>
       <c r="R4" s="5">
-        <v>5738</v>
+        <v>5735</v>
       </c>
       <c r="S4" s="5">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -23887,22 +23887,22 @@
         <v>590</v>
       </c>
       <c r="N5" s="4">
-        <v>1.193106396569767</v>
+        <v>0.517192511045323</v>
       </c>
       <c r="O5" s="5">
         <v>4855</v>
       </c>
       <c r="P5" s="4">
-        <v>1.785290541525198</v>
+        <v>1.674317926412135</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.7871216720196984</v>
+        <v>0.4620563427731321</v>
       </c>
       <c r="R5" s="5">
-        <v>4419</v>
+        <v>4370</v>
       </c>
       <c r="S5" s="5">
-        <v>436</v>
+        <v>485</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -23946,16 +23946,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>0.1923952858294906</v>
+        <v>0.1976979856989942</v>
       </c>
       <c r="O6" s="5">
         <v>4768</v>
       </c>
       <c r="P6" s="4">
-        <v>0.3553375567493792</v>
+        <v>0.3558301627783795</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2899810660777298</v>
+        <v>0.2899525110338708</v>
       </c>
       <c r="R6" s="5">
         <v>4766</v>
@@ -24005,16 +24005,16 @@
         <v>1</v>
       </c>
       <c r="N7" s="4">
-        <v>0.1341992194423035</v>
+        <v>0.1284370843104625</v>
       </c>
       <c r="O7" s="5">
         <v>4120</v>
       </c>
       <c r="P7" s="4">
-        <v>0.5108591965500339</v>
+        <v>0.5100806026082916</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.3564866977282629</v>
+        <v>0.3564649142991408</v>
       </c>
       <c r="R7" s="5">
         <v>4119</v>
@@ -24064,16 +24064,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.07977029473798766</v>
+        <v>-0.04838159851453838</v>
       </c>
       <c r="O8" s="5">
         <v>1049</v>
       </c>
       <c r="P8" s="4">
-        <v>0.4156390864904088</v>
+        <v>0.4234639701435077</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2250482805806507</v>
+        <v>0.2232576155668028</v>
       </c>
       <c r="R8" s="5">
         <v>1049</v>
@@ -24123,16 +24123,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.5385881012922696</v>
+        <v>-0.5430939290081369</v>
       </c>
       <c r="O9" s="5">
         <v>1205</v>
       </c>
       <c r="P9" s="4">
-        <v>0.4941999760921142</v>
+        <v>0.49349142695514</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2701513263871206</v>
+        <v>0.2701139404600028</v>
       </c>
       <c r="R9" s="5">
         <v>1205</v>
@@ -24182,16 +24182,16 @@
         <v>2</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.0795455066930682</v>
+        <v>-0.06523093543171399</v>
       </c>
       <c r="O10" s="5">
         <v>796</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1496836190935849</v>
+        <v>0.1531221401807789</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.09664990954485726</v>
+        <v>0.09580043590131455</v>
       </c>
       <c r="R10" s="5">
         <v>796</v>
@@ -24241,16 +24241,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.2640338925572266</v>
+        <v>-0.2746249193715187</v>
       </c>
       <c r="O11" s="5">
         <v>1211</v>
       </c>
       <c r="P11" s="4">
-        <v>0.4297646977135011</v>
+        <v>0.4286090680628191</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.2652249011761747</v>
+        <v>0.2651214771535945</v>
       </c>
       <c r="R11" s="5">
         <v>1211</v>
@@ -24300,16 +24300,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.5518278457772006</v>
+        <v>-0.5453394902461355</v>
       </c>
       <c r="O12" s="5">
         <v>990</v>
       </c>
       <c r="P12" s="4">
-        <v>0.4038244156703749</v>
+        <v>0.4054208071964435</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.218424860272914</v>
+        <v>0.2183378608662998</v>
       </c>
       <c r="R12" s="5">
         <v>990</v>
@@ -24359,16 +24359,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.6209201227094352</v>
+        <v>-0.6026473515813393</v>
       </c>
       <c r="O13" s="5">
         <v>966</v>
       </c>
       <c r="P13" s="4">
-        <v>0.2918006116882759</v>
+        <v>0.2944265356292995</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.2219930035861393</v>
+        <v>0.2213712413462489</v>
       </c>
       <c r="R13" s="5">
         <v>966</v>
@@ -24418,16 +24418,16 @@
         <v>3</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.02003260896019795</v>
+        <v>-0.05583482268127682</v>
       </c>
       <c r="O14" s="5">
         <v>879</v>
       </c>
       <c r="P14" s="4">
-        <v>0.4480337702145235</v>
+        <v>0.4396842647169052</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.2266344233337098</v>
+        <v>0.2252101486935896</v>
       </c>
       <c r="R14" s="5">
         <v>876</v>
